--- a/engineering/drainage-design/retention_volume/Retention_1200_File3_Stress.xlsx
+++ b/engineering/drainage-design/retention_volume/Retention_1200_File3_Stress.xlsx
@@ -2175,11 +2175,11 @@
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>IF(F15&lt;=INDEX(Compose_0pct!$G$13:$G$64,1),INDEX(Compose_0pct!$A$13:$A$64,1),IF(F15&gt;=INDEX(Compose_0pct!$G$13:$G$64,ROWS(Compose_0pct!$G$13:$G$64)),INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$A$13:$A$64,MATCH(F15,Compose_0pct!$G$13:$G$64,1))+(F15-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F15,Compose_0pct!$G$13:$G$64,1)))/(INDEX(Compose_0pct!$G$13:$G$64,MATCH(F15,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F15,Compose_0pct!$G$13:$G$64,1)))*(INDEX(Compose_0pct!$A$13:$A$64,MATCH(F15,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(F15,Compose_0pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F15&lt;=INDEX(Compose_0pct!$G$15:$G$66,1),INDEX(Compose_0pct!$A$15:$A$66,1),IF(F15&gt;=INDEX(Compose_0pct!$G$15:$G$66,ROWS(Compose_0pct!$G$15:$G$66)),INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$A$15:$A$66,MATCH(F15,Compose_0pct!$G$15:$G$66,1))+(F15-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F15,Compose_0pct!$G$15:$G$66,1)))/(INDEX(Compose_0pct!$G$15:$G$66,MATCH(F15,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F15,Compose_0pct!$G$15:$G$66,1)))*(INDEX(Compose_0pct!$A$15:$A$66,MATCH(F15,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(F15,Compose_0pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$J$13:$J$64,1),IF(C16&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$J$13:$J$64,ROWS(Compose_0pct!$J$13:$J$64)),INDEX(Compose_0pct!$J$13:$J$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1))+(C16-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$J$13:$J$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$J$13:$J$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$J$15:$J$66,1),IF(C16&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$J$15:$J$66,ROWS(Compose_0pct!$J$15:$J$66)),INDEX(Compose_0pct!$J$15:$J$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1))+(C16-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$J$15:$J$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$J$15:$J$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E16" s="16">
@@ -2191,11 +2191,11 @@
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$H$13:$H$64,1),IF(C16&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$H$13:$H$64,ROWS(Compose_0pct!$H$13:$H$64)),INDEX(Compose_0pct!$H$13:$H$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1))+(C16-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$H$13:$H$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$H$13:$H$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$H$15:$H$66,1),IF(C16&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$H$15:$H$66,ROWS(Compose_0pct!$H$15:$H$66)),INDEX(Compose_0pct!$H$15:$H$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1))+(C16-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$H$15:$H$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$H$15:$H$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$I$13:$I$64,1),IF(C16&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$I$13:$I$64,ROWS(Compose_0pct!$I$13:$I$64)),INDEX(Compose_0pct!$I$13:$I$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1))+(C16-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$I$13:$I$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$I$13:$I$64,MATCH(C16,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$I$15:$I$66,1),IF(C16&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$I$15:$I$66,ROWS(Compose_0pct!$I$15:$I$66)),INDEX(Compose_0pct!$I$15:$I$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1))+(C16-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$I$15:$I$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$I$15:$I$66,MATCH(C16,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I16" s="21">
@@ -2213,11 +2213,11 @@
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>IF(F16&lt;=INDEX(Compose_0pct!$G$13:$G$64,1),INDEX(Compose_0pct!$A$13:$A$64,1),IF(F16&gt;=INDEX(Compose_0pct!$G$13:$G$64,ROWS(Compose_0pct!$G$13:$G$64)),INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$A$13:$A$64,MATCH(F16,Compose_0pct!$G$13:$G$64,1))+(F16-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F16,Compose_0pct!$G$13:$G$64,1)))/(INDEX(Compose_0pct!$G$13:$G$64,MATCH(F16,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F16,Compose_0pct!$G$13:$G$64,1)))*(INDEX(Compose_0pct!$A$13:$A$64,MATCH(F16,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(F16,Compose_0pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F16&lt;=INDEX(Compose_0pct!$G$15:$G$66,1),INDEX(Compose_0pct!$A$15:$A$66,1),IF(F16&gt;=INDEX(Compose_0pct!$G$15:$G$66,ROWS(Compose_0pct!$G$15:$G$66)),INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$A$15:$A$66,MATCH(F16,Compose_0pct!$G$15:$G$66,1))+(F16-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F16,Compose_0pct!$G$15:$G$66,1)))/(INDEX(Compose_0pct!$G$15:$G$66,MATCH(F16,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F16,Compose_0pct!$G$15:$G$66,1)))*(INDEX(Compose_0pct!$A$15:$A$66,MATCH(F16,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(F16,Compose_0pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$J$13:$J$64,1),IF(C17&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$J$13:$J$64,ROWS(Compose_0pct!$J$13:$J$64)),INDEX(Compose_0pct!$J$13:$J$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1))+(C17-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$J$13:$J$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$J$13:$J$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$J$15:$J$66,1),IF(C17&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$J$15:$J$66,ROWS(Compose_0pct!$J$15:$J$66)),INDEX(Compose_0pct!$J$15:$J$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1))+(C17-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$J$15:$J$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$J$15:$J$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E17" s="16">
@@ -2229,11 +2229,11 @@
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$H$13:$H$64,1),IF(C17&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$H$13:$H$64,ROWS(Compose_0pct!$H$13:$H$64)),INDEX(Compose_0pct!$H$13:$H$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1))+(C17-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$H$13:$H$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$H$13:$H$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$H$15:$H$66,1),IF(C17&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$H$15:$H$66,ROWS(Compose_0pct!$H$15:$H$66)),INDEX(Compose_0pct!$H$15:$H$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1))+(C17-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$H$15:$H$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$H$15:$H$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$I$13:$I$64,1),IF(C17&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$I$13:$I$64,ROWS(Compose_0pct!$I$13:$I$64)),INDEX(Compose_0pct!$I$13:$I$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1))+(C17-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$I$13:$I$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$I$13:$I$64,MATCH(C17,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$I$15:$I$66,1),IF(C17&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$I$15:$I$66,ROWS(Compose_0pct!$I$15:$I$66)),INDEX(Compose_0pct!$I$15:$I$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1))+(C17-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$I$15:$I$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$I$15:$I$66,MATCH(C17,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I17" s="21">
@@ -2251,11 +2251,11 @@
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>IF(F17&lt;=INDEX(Compose_0pct!$G$13:$G$64,1),INDEX(Compose_0pct!$A$13:$A$64,1),IF(F17&gt;=INDEX(Compose_0pct!$G$13:$G$64,ROWS(Compose_0pct!$G$13:$G$64)),INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$A$13:$A$64,MATCH(F17,Compose_0pct!$G$13:$G$64,1))+(F17-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F17,Compose_0pct!$G$13:$G$64,1)))/(INDEX(Compose_0pct!$G$13:$G$64,MATCH(F17,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F17,Compose_0pct!$G$13:$G$64,1)))*(INDEX(Compose_0pct!$A$13:$A$64,MATCH(F17,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(F17,Compose_0pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F17&lt;=INDEX(Compose_0pct!$G$15:$G$66,1),INDEX(Compose_0pct!$A$15:$A$66,1),IF(F17&gt;=INDEX(Compose_0pct!$G$15:$G$66,ROWS(Compose_0pct!$G$15:$G$66)),INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$A$15:$A$66,MATCH(F17,Compose_0pct!$G$15:$G$66,1))+(F17-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F17,Compose_0pct!$G$15:$G$66,1)))/(INDEX(Compose_0pct!$G$15:$G$66,MATCH(F17,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F17,Compose_0pct!$G$15:$G$66,1)))*(INDEX(Compose_0pct!$A$15:$A$66,MATCH(F17,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(F17,Compose_0pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$J$13:$J$64,1),IF(C18&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$J$13:$J$64,ROWS(Compose_0pct!$J$13:$J$64)),INDEX(Compose_0pct!$J$13:$J$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1))+(C18-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$J$13:$J$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$J$13:$J$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$J$15:$J$66,1),IF(C18&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$J$15:$J$66,ROWS(Compose_0pct!$J$15:$J$66)),INDEX(Compose_0pct!$J$15:$J$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1))+(C18-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$J$15:$J$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$J$15:$J$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E18" s="16">
@@ -2267,11 +2267,11 @@
         <v/>
       </c>
       <c r="G18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$H$13:$H$64,1),IF(C18&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$H$13:$H$64,ROWS(Compose_0pct!$H$13:$H$64)),INDEX(Compose_0pct!$H$13:$H$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1))+(C18-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$H$13:$H$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$H$13:$H$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$H$15:$H$66,1),IF(C18&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$H$15:$H$66,ROWS(Compose_0pct!$H$15:$H$66)),INDEX(Compose_0pct!$H$15:$H$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1))+(C18-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$H$15:$H$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$H$15:$H$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$I$13:$I$64,1),IF(C18&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$I$13:$I$64,ROWS(Compose_0pct!$I$13:$I$64)),INDEX(Compose_0pct!$I$13:$I$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1))+(C18-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$I$13:$I$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$I$13:$I$64,MATCH(C18,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$I$15:$I$66,1),IF(C18&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$I$15:$I$66,ROWS(Compose_0pct!$I$15:$I$66)),INDEX(Compose_0pct!$I$15:$I$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1))+(C18-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$I$15:$I$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$I$15:$I$66,MATCH(C18,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I18" s="21">
@@ -2289,11 +2289,11 @@
         <v/>
       </c>
       <c r="C19" s="17">
-        <f>IF(F18&lt;=INDEX(Compose_0pct!$G$13:$G$64,1),INDEX(Compose_0pct!$A$13:$A$64,1),IF(F18&gt;=INDEX(Compose_0pct!$G$13:$G$64,ROWS(Compose_0pct!$G$13:$G$64)),INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$A$13:$A$64,MATCH(F18,Compose_0pct!$G$13:$G$64,1))+(F18-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F18,Compose_0pct!$G$13:$G$64,1)))/(INDEX(Compose_0pct!$G$13:$G$64,MATCH(F18,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F18,Compose_0pct!$G$13:$G$64,1)))*(INDEX(Compose_0pct!$A$13:$A$64,MATCH(F18,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(F18,Compose_0pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F18&lt;=INDEX(Compose_0pct!$G$15:$G$66,1),INDEX(Compose_0pct!$A$15:$A$66,1),IF(F18&gt;=INDEX(Compose_0pct!$G$15:$G$66,ROWS(Compose_0pct!$G$15:$G$66)),INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$A$15:$A$66,MATCH(F18,Compose_0pct!$G$15:$G$66,1))+(F18-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F18,Compose_0pct!$G$15:$G$66,1)))/(INDEX(Compose_0pct!$G$15:$G$66,MATCH(F18,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F18,Compose_0pct!$G$15:$G$66,1)))*(INDEX(Compose_0pct!$A$15:$A$66,MATCH(F18,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(F18,Compose_0pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$J$13:$J$64,1),IF(C19&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$J$13:$J$64,ROWS(Compose_0pct!$J$13:$J$64)),INDEX(Compose_0pct!$J$13:$J$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1))+(C19-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$J$13:$J$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$J$13:$J$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$J$15:$J$66,1),IF(C19&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$J$15:$J$66,ROWS(Compose_0pct!$J$15:$J$66)),INDEX(Compose_0pct!$J$15:$J$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1))+(C19-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$J$15:$J$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$J$15:$J$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E19" s="16">
@@ -2305,11 +2305,11 @@
         <v/>
       </c>
       <c r="G19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$H$13:$H$64,1),IF(C19&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$H$13:$H$64,ROWS(Compose_0pct!$H$13:$H$64)),INDEX(Compose_0pct!$H$13:$H$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1))+(C19-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$H$13:$H$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$H$13:$H$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$H$15:$H$66,1),IF(C19&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$H$15:$H$66,ROWS(Compose_0pct!$H$15:$H$66)),INDEX(Compose_0pct!$H$15:$H$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1))+(C19-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$H$15:$H$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$H$15:$H$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$I$13:$I$64,1),IF(C19&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$I$13:$I$64,ROWS(Compose_0pct!$I$13:$I$64)),INDEX(Compose_0pct!$I$13:$I$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1))+(C19-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$I$13:$I$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$I$13:$I$64,MATCH(C19,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$I$15:$I$66,1),IF(C19&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$I$15:$I$66,ROWS(Compose_0pct!$I$15:$I$66)),INDEX(Compose_0pct!$I$15:$I$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1))+(C19-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$I$15:$I$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$I$15:$I$66,MATCH(C19,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I19" s="21">
@@ -2327,11 +2327,11 @@
         <v/>
       </c>
       <c r="C20" s="17">
-        <f>IF(F19&lt;=INDEX(Compose_0pct!$G$13:$G$64,1),INDEX(Compose_0pct!$A$13:$A$64,1),IF(F19&gt;=INDEX(Compose_0pct!$G$13:$G$64,ROWS(Compose_0pct!$G$13:$G$64)),INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$A$13:$A$64,MATCH(F19,Compose_0pct!$G$13:$G$64,1))+(F19-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F19,Compose_0pct!$G$13:$G$64,1)))/(INDEX(Compose_0pct!$G$13:$G$64,MATCH(F19,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F19,Compose_0pct!$G$13:$G$64,1)))*(INDEX(Compose_0pct!$A$13:$A$64,MATCH(F19,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(F19,Compose_0pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F19&lt;=INDEX(Compose_0pct!$G$15:$G$66,1),INDEX(Compose_0pct!$A$15:$A$66,1),IF(F19&gt;=INDEX(Compose_0pct!$G$15:$G$66,ROWS(Compose_0pct!$G$15:$G$66)),INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$A$15:$A$66,MATCH(F19,Compose_0pct!$G$15:$G$66,1))+(F19-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F19,Compose_0pct!$G$15:$G$66,1)))/(INDEX(Compose_0pct!$G$15:$G$66,MATCH(F19,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F19,Compose_0pct!$G$15:$G$66,1)))*(INDEX(Compose_0pct!$A$15:$A$66,MATCH(F19,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(F19,Compose_0pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D20" s="17">
-        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$J$13:$J$64,1),IF(C20&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$J$13:$J$64,ROWS(Compose_0pct!$J$13:$J$64)),INDEX(Compose_0pct!$J$13:$J$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1))+(C20-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$J$13:$J$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$J$13:$J$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$J$15:$J$66,1),IF(C20&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$J$15:$J$66,ROWS(Compose_0pct!$J$15:$J$66)),INDEX(Compose_0pct!$J$15:$J$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1))+(C20-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$J$15:$J$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$J$15:$J$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E20" s="16">
@@ -2343,11 +2343,11 @@
         <v/>
       </c>
       <c r="G20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$H$13:$H$64,1),IF(C20&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$H$13:$H$64,ROWS(Compose_0pct!$H$13:$H$64)),INDEX(Compose_0pct!$H$13:$H$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1))+(C20-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$H$13:$H$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$H$13:$H$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$H$15:$H$66,1),IF(C20&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$H$15:$H$66,ROWS(Compose_0pct!$H$15:$H$66)),INDEX(Compose_0pct!$H$15:$H$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1))+(C20-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$H$15:$H$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$H$15:$H$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$I$13:$I$64,1),IF(C20&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$I$13:$I$64,ROWS(Compose_0pct!$I$13:$I$64)),INDEX(Compose_0pct!$I$13:$I$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1))+(C20-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$I$13:$I$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$I$13:$I$64,MATCH(C20,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$I$15:$I$66,1),IF(C20&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$I$15:$I$66,ROWS(Compose_0pct!$I$15:$I$66)),INDEX(Compose_0pct!$I$15:$I$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1))+(C20-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$I$15:$I$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$I$15:$I$66,MATCH(C20,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I20" s="21">
@@ -2365,11 +2365,11 @@
         <v/>
       </c>
       <c r="C21" s="17">
-        <f>IF(F20&lt;=INDEX(Compose_0pct!$G$13:$G$64,1),INDEX(Compose_0pct!$A$13:$A$64,1),IF(F20&gt;=INDEX(Compose_0pct!$G$13:$G$64,ROWS(Compose_0pct!$G$13:$G$64)),INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$A$13:$A$64,MATCH(F20,Compose_0pct!$G$13:$G$64,1))+(F20-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F20,Compose_0pct!$G$13:$G$64,1)))/(INDEX(Compose_0pct!$G$13:$G$64,MATCH(F20,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F20,Compose_0pct!$G$13:$G$64,1)))*(INDEX(Compose_0pct!$A$13:$A$64,MATCH(F20,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(F20,Compose_0pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F20&lt;=INDEX(Compose_0pct!$G$15:$G$66,1),INDEX(Compose_0pct!$A$15:$A$66,1),IF(F20&gt;=INDEX(Compose_0pct!$G$15:$G$66,ROWS(Compose_0pct!$G$15:$G$66)),INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$A$15:$A$66,MATCH(F20,Compose_0pct!$G$15:$G$66,1))+(F20-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F20,Compose_0pct!$G$15:$G$66,1)))/(INDEX(Compose_0pct!$G$15:$G$66,MATCH(F20,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F20,Compose_0pct!$G$15:$G$66,1)))*(INDEX(Compose_0pct!$A$15:$A$66,MATCH(F20,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(F20,Compose_0pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D21" s="17">
-        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$J$13:$J$64,1),IF(C21&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$J$13:$J$64,ROWS(Compose_0pct!$J$13:$J$64)),INDEX(Compose_0pct!$J$13:$J$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1))+(C21-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$J$13:$J$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$J$13:$J$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$J$15:$J$66,1),IF(C21&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$J$15:$J$66,ROWS(Compose_0pct!$J$15:$J$66)),INDEX(Compose_0pct!$J$15:$J$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1))+(C21-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$J$15:$J$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$J$15:$J$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E21" s="16">
@@ -2381,11 +2381,11 @@
         <v/>
       </c>
       <c r="G21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$H$13:$H$64,1),IF(C21&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$H$13:$H$64,ROWS(Compose_0pct!$H$13:$H$64)),INDEX(Compose_0pct!$H$13:$H$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1))+(C21-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$H$13:$H$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$H$13:$H$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$H$15:$H$66,1),IF(C21&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$H$15:$H$66,ROWS(Compose_0pct!$H$15:$H$66)),INDEX(Compose_0pct!$H$15:$H$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1))+(C21-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$H$15:$H$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$H$15:$H$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$I$13:$I$64,1),IF(C21&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$I$13:$I$64,ROWS(Compose_0pct!$I$13:$I$64)),INDEX(Compose_0pct!$I$13:$I$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1))+(C21-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$I$13:$I$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$I$13:$I$64,MATCH(C21,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$I$15:$I$66,1),IF(C21&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$I$15:$I$66,ROWS(Compose_0pct!$I$15:$I$66)),INDEX(Compose_0pct!$I$15:$I$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1))+(C21-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$I$15:$I$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$I$15:$I$66,MATCH(C21,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I21" s="21">
@@ -2403,11 +2403,11 @@
         <v/>
       </c>
       <c r="C22" s="17">
-        <f>IF(F21&lt;=INDEX(Compose_0pct!$G$13:$G$64,1),INDEX(Compose_0pct!$A$13:$A$64,1),IF(F21&gt;=INDEX(Compose_0pct!$G$13:$G$64,ROWS(Compose_0pct!$G$13:$G$64)),INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$A$13:$A$64,MATCH(F21,Compose_0pct!$G$13:$G$64,1))+(F21-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F21,Compose_0pct!$G$13:$G$64,1)))/(INDEX(Compose_0pct!$G$13:$G$64,MATCH(F21,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F21,Compose_0pct!$G$13:$G$64,1)))*(INDEX(Compose_0pct!$A$13:$A$64,MATCH(F21,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(F21,Compose_0pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F21&lt;=INDEX(Compose_0pct!$G$15:$G$66,1),INDEX(Compose_0pct!$A$15:$A$66,1),IF(F21&gt;=INDEX(Compose_0pct!$G$15:$G$66,ROWS(Compose_0pct!$G$15:$G$66)),INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$A$15:$A$66,MATCH(F21,Compose_0pct!$G$15:$G$66,1))+(F21-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F21,Compose_0pct!$G$15:$G$66,1)))/(INDEX(Compose_0pct!$G$15:$G$66,MATCH(F21,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F21,Compose_0pct!$G$15:$G$66,1)))*(INDEX(Compose_0pct!$A$15:$A$66,MATCH(F21,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(F21,Compose_0pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D22" s="17">
-        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$J$13:$J$64,1),IF(C22&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$J$13:$J$64,ROWS(Compose_0pct!$J$13:$J$64)),INDEX(Compose_0pct!$J$13:$J$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1))+(C22-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$J$13:$J$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$J$13:$J$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$J$15:$J$66,1),IF(C22&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$J$15:$J$66,ROWS(Compose_0pct!$J$15:$J$66)),INDEX(Compose_0pct!$J$15:$J$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1))+(C22-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$J$15:$J$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$J$15:$J$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E22" s="16">
@@ -2419,11 +2419,11 @@
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$H$13:$H$64,1),IF(C22&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$H$13:$H$64,ROWS(Compose_0pct!$H$13:$H$64)),INDEX(Compose_0pct!$H$13:$H$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1))+(C22-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$H$13:$H$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$H$13:$H$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$H$15:$H$66,1),IF(C22&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$H$15:$H$66,ROWS(Compose_0pct!$H$15:$H$66)),INDEX(Compose_0pct!$H$15:$H$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1))+(C22-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$H$15:$H$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$H$15:$H$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$I$13:$I$64,1),IF(C22&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$I$13:$I$64,ROWS(Compose_0pct!$I$13:$I$64)),INDEX(Compose_0pct!$I$13:$I$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1))+(C22-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$I$13:$I$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$I$13:$I$64,MATCH(C22,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$I$15:$I$66,1),IF(C22&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$I$15:$I$66,ROWS(Compose_0pct!$I$15:$I$66)),INDEX(Compose_0pct!$I$15:$I$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1))+(C22-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$I$15:$I$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$I$15:$I$66,MATCH(C22,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I22" s="21">
@@ -2441,11 +2441,11 @@
         <v/>
       </c>
       <c r="C23" s="17">
-        <f>IF(F22&lt;=INDEX(Compose_0pct!$G$13:$G$64,1),INDEX(Compose_0pct!$A$13:$A$64,1),IF(F22&gt;=INDEX(Compose_0pct!$G$13:$G$64,ROWS(Compose_0pct!$G$13:$G$64)),INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$A$13:$A$64,MATCH(F22,Compose_0pct!$G$13:$G$64,1))+(F22-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F22,Compose_0pct!$G$13:$G$64,1)))/(INDEX(Compose_0pct!$G$13:$G$64,MATCH(F22,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F22,Compose_0pct!$G$13:$G$64,1)))*(INDEX(Compose_0pct!$A$13:$A$64,MATCH(F22,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(F22,Compose_0pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F22&lt;=INDEX(Compose_0pct!$G$15:$G$66,1),INDEX(Compose_0pct!$A$15:$A$66,1),IF(F22&gt;=INDEX(Compose_0pct!$G$15:$G$66,ROWS(Compose_0pct!$G$15:$G$66)),INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$A$15:$A$66,MATCH(F22,Compose_0pct!$G$15:$G$66,1))+(F22-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F22,Compose_0pct!$G$15:$G$66,1)))/(INDEX(Compose_0pct!$G$15:$G$66,MATCH(F22,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F22,Compose_0pct!$G$15:$G$66,1)))*(INDEX(Compose_0pct!$A$15:$A$66,MATCH(F22,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(F22,Compose_0pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D23" s="17">
-        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$J$13:$J$64,1),IF(C23&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$J$13:$J$64,ROWS(Compose_0pct!$J$13:$J$64)),INDEX(Compose_0pct!$J$13:$J$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1))+(C23-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$J$13:$J$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$J$13:$J$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$J$15:$J$66,1),IF(C23&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$J$15:$J$66,ROWS(Compose_0pct!$J$15:$J$66)),INDEX(Compose_0pct!$J$15:$J$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1))+(C23-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$J$15:$J$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$J$15:$J$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E23" s="16">
@@ -2457,11 +2457,11 @@
         <v/>
       </c>
       <c r="G23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$H$13:$H$64,1),IF(C23&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$H$13:$H$64,ROWS(Compose_0pct!$H$13:$H$64)),INDEX(Compose_0pct!$H$13:$H$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1))+(C23-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$H$13:$H$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$H$13:$H$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$H$15:$H$66,1),IF(C23&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$H$15:$H$66,ROWS(Compose_0pct!$H$15:$H$66)),INDEX(Compose_0pct!$H$15:$H$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1))+(C23-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$H$15:$H$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$H$15:$H$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$I$13:$I$64,1),IF(C23&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$I$13:$I$64,ROWS(Compose_0pct!$I$13:$I$64)),INDEX(Compose_0pct!$I$13:$I$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1))+(C23-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$I$13:$I$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$I$13:$I$64,MATCH(C23,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$I$15:$I$66,1),IF(C23&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$I$15:$I$66,ROWS(Compose_0pct!$I$15:$I$66)),INDEX(Compose_0pct!$I$15:$I$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1))+(C23-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$I$15:$I$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$I$15:$I$66,MATCH(C23,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I23" s="21">
@@ -2479,11 +2479,11 @@
         <v/>
       </c>
       <c r="C24" s="17">
-        <f>IF(F23&lt;=INDEX(Compose_0pct!$G$13:$G$64,1),INDEX(Compose_0pct!$A$13:$A$64,1),IF(F23&gt;=INDEX(Compose_0pct!$G$13:$G$64,ROWS(Compose_0pct!$G$13:$G$64)),INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$A$13:$A$64,MATCH(F23,Compose_0pct!$G$13:$G$64,1))+(F23-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F23,Compose_0pct!$G$13:$G$64,1)))/(INDEX(Compose_0pct!$G$13:$G$64,MATCH(F23,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F23,Compose_0pct!$G$13:$G$64,1)))*(INDEX(Compose_0pct!$A$13:$A$64,MATCH(F23,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(F23,Compose_0pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F23&lt;=INDEX(Compose_0pct!$G$15:$G$66,1),INDEX(Compose_0pct!$A$15:$A$66,1),IF(F23&gt;=INDEX(Compose_0pct!$G$15:$G$66,ROWS(Compose_0pct!$G$15:$G$66)),INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$A$15:$A$66,MATCH(F23,Compose_0pct!$G$15:$G$66,1))+(F23-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F23,Compose_0pct!$G$15:$G$66,1)))/(INDEX(Compose_0pct!$G$15:$G$66,MATCH(F23,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F23,Compose_0pct!$G$15:$G$66,1)))*(INDEX(Compose_0pct!$A$15:$A$66,MATCH(F23,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(F23,Compose_0pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D24" s="17">
-        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$J$13:$J$64,1),IF(C24&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$J$13:$J$64,ROWS(Compose_0pct!$J$13:$J$64)),INDEX(Compose_0pct!$J$13:$J$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1))+(C24-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$J$13:$J$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$J$13:$J$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$J$15:$J$66,1),IF(C24&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$J$15:$J$66,ROWS(Compose_0pct!$J$15:$J$66)),INDEX(Compose_0pct!$J$15:$J$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1))+(C24-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$J$15:$J$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$J$15:$J$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E24" s="16">
@@ -2495,11 +2495,11 @@
         <v/>
       </c>
       <c r="G24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$H$13:$H$64,1),IF(C24&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$H$13:$H$64,ROWS(Compose_0pct!$H$13:$H$64)),INDEX(Compose_0pct!$H$13:$H$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1))+(C24-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$H$13:$H$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$H$13:$H$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$H$15:$H$66,1),IF(C24&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$H$15:$H$66,ROWS(Compose_0pct!$H$15:$H$66)),INDEX(Compose_0pct!$H$15:$H$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1))+(C24-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$H$15:$H$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$H$15:$H$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$I$13:$I$64,1),IF(C24&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$I$13:$I$64,ROWS(Compose_0pct!$I$13:$I$64)),INDEX(Compose_0pct!$I$13:$I$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1))+(C24-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$I$13:$I$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$I$13:$I$64,MATCH(C24,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$I$15:$I$66,1),IF(C24&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$I$15:$I$66,ROWS(Compose_0pct!$I$15:$I$66)),INDEX(Compose_0pct!$I$15:$I$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1))+(C24-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$I$15:$I$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$I$15:$I$66,MATCH(C24,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I24" s="21">
@@ -2517,11 +2517,11 @@
         <v/>
       </c>
       <c r="C25" s="17">
-        <f>IF(F24&lt;=INDEX(Compose_0pct!$G$13:$G$64,1),INDEX(Compose_0pct!$A$13:$A$64,1),IF(F24&gt;=INDEX(Compose_0pct!$G$13:$G$64,ROWS(Compose_0pct!$G$13:$G$64)),INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$A$13:$A$64,MATCH(F24,Compose_0pct!$G$13:$G$64,1))+(F24-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F24,Compose_0pct!$G$13:$G$64,1)))/(INDEX(Compose_0pct!$G$13:$G$64,MATCH(F24,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F24,Compose_0pct!$G$13:$G$64,1)))*(INDEX(Compose_0pct!$A$13:$A$64,MATCH(F24,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(F24,Compose_0pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F24&lt;=INDEX(Compose_0pct!$G$15:$G$66,1),INDEX(Compose_0pct!$A$15:$A$66,1),IF(F24&gt;=INDEX(Compose_0pct!$G$15:$G$66,ROWS(Compose_0pct!$G$15:$G$66)),INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$A$15:$A$66,MATCH(F24,Compose_0pct!$G$15:$G$66,1))+(F24-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F24,Compose_0pct!$G$15:$G$66,1)))/(INDEX(Compose_0pct!$G$15:$G$66,MATCH(F24,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F24,Compose_0pct!$G$15:$G$66,1)))*(INDEX(Compose_0pct!$A$15:$A$66,MATCH(F24,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(F24,Compose_0pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D25" s="17">
-        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$J$13:$J$64,1),IF(C25&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$J$13:$J$64,ROWS(Compose_0pct!$J$13:$J$64)),INDEX(Compose_0pct!$J$13:$J$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1))+(C25-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$J$13:$J$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$J$13:$J$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$J$15:$J$66,1),IF(C25&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$J$15:$J$66,ROWS(Compose_0pct!$J$15:$J$66)),INDEX(Compose_0pct!$J$15:$J$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1))+(C25-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$J$15:$J$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$J$15:$J$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E25" s="16">
@@ -2533,11 +2533,11 @@
         <v/>
       </c>
       <c r="G25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$H$13:$H$64,1),IF(C25&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$H$13:$H$64,ROWS(Compose_0pct!$H$13:$H$64)),INDEX(Compose_0pct!$H$13:$H$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1))+(C25-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$H$13:$H$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$H$13:$H$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$H$15:$H$66,1),IF(C25&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$H$15:$H$66,ROWS(Compose_0pct!$H$15:$H$66)),INDEX(Compose_0pct!$H$15:$H$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1))+(C25-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$H$15:$H$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$H$15:$H$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$I$13:$I$64,1),IF(C25&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$I$13:$I$64,ROWS(Compose_0pct!$I$13:$I$64)),INDEX(Compose_0pct!$I$13:$I$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1))+(C25-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$I$13:$I$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$I$13:$I$64,MATCH(C25,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$I$15:$I$66,1),IF(C25&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$I$15:$I$66,ROWS(Compose_0pct!$I$15:$I$66)),INDEX(Compose_0pct!$I$15:$I$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1))+(C25-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$I$15:$I$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$I$15:$I$66,MATCH(C25,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I25" s="21">
@@ -2555,11 +2555,11 @@
         <v/>
       </c>
       <c r="C26" s="17">
-        <f>IF(F25&lt;=INDEX(Compose_0pct!$G$13:$G$64,1),INDEX(Compose_0pct!$A$13:$A$64,1),IF(F25&gt;=INDEX(Compose_0pct!$G$13:$G$64,ROWS(Compose_0pct!$G$13:$G$64)),INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$A$13:$A$64,MATCH(F25,Compose_0pct!$G$13:$G$64,1))+(F25-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F25,Compose_0pct!$G$13:$G$64,1)))/(INDEX(Compose_0pct!$G$13:$G$64,MATCH(F25,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F25,Compose_0pct!$G$13:$G$64,1)))*(INDEX(Compose_0pct!$A$13:$A$64,MATCH(F25,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(F25,Compose_0pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F25&lt;=INDEX(Compose_0pct!$G$15:$G$66,1),INDEX(Compose_0pct!$A$15:$A$66,1),IF(F25&gt;=INDEX(Compose_0pct!$G$15:$G$66,ROWS(Compose_0pct!$G$15:$G$66)),INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$A$15:$A$66,MATCH(F25,Compose_0pct!$G$15:$G$66,1))+(F25-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F25,Compose_0pct!$G$15:$G$66,1)))/(INDEX(Compose_0pct!$G$15:$G$66,MATCH(F25,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F25,Compose_0pct!$G$15:$G$66,1)))*(INDEX(Compose_0pct!$A$15:$A$66,MATCH(F25,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(F25,Compose_0pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D26" s="17">
-        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$J$13:$J$64,1),IF(C26&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$J$13:$J$64,ROWS(Compose_0pct!$J$13:$J$64)),INDEX(Compose_0pct!$J$13:$J$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1))+(C26-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$J$13:$J$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$J$13:$J$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$J$15:$J$66,1),IF(C26&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$J$15:$J$66,ROWS(Compose_0pct!$J$15:$J$66)),INDEX(Compose_0pct!$J$15:$J$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1))+(C26-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$J$15:$J$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$J$15:$J$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E26" s="16">
@@ -2571,11 +2571,11 @@
         <v/>
       </c>
       <c r="G26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$H$13:$H$64,1),IF(C26&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$H$13:$H$64,ROWS(Compose_0pct!$H$13:$H$64)),INDEX(Compose_0pct!$H$13:$H$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1))+(C26-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$H$13:$H$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$H$13:$H$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$H$15:$H$66,1),IF(C26&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$H$15:$H$66,ROWS(Compose_0pct!$H$15:$H$66)),INDEX(Compose_0pct!$H$15:$H$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1))+(C26-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$H$15:$H$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$H$15:$H$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$I$13:$I$64,1),IF(C26&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$I$13:$I$64,ROWS(Compose_0pct!$I$13:$I$64)),INDEX(Compose_0pct!$I$13:$I$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1))+(C26-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$I$13:$I$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$I$13:$I$64,MATCH(C26,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$I$15:$I$66,1),IF(C26&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$I$15:$I$66,ROWS(Compose_0pct!$I$15:$I$66)),INDEX(Compose_0pct!$I$15:$I$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1))+(C26-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$I$15:$I$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$I$15:$I$66,MATCH(C26,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I26" s="21">
@@ -2593,11 +2593,11 @@
         <v/>
       </c>
       <c r="C27" s="17">
-        <f>IF(F26&lt;=INDEX(Compose_0pct!$G$13:$G$64,1),INDEX(Compose_0pct!$A$13:$A$64,1),IF(F26&gt;=INDEX(Compose_0pct!$G$13:$G$64,ROWS(Compose_0pct!$G$13:$G$64)),INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$A$13:$A$64,MATCH(F26,Compose_0pct!$G$13:$G$64,1))+(F26-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F26,Compose_0pct!$G$13:$G$64,1)))/(INDEX(Compose_0pct!$G$13:$G$64,MATCH(F26,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$G$13:$G$64,MATCH(F26,Compose_0pct!$G$13:$G$64,1)))*(INDEX(Compose_0pct!$A$13:$A$64,MATCH(F26,Compose_0pct!$G$13:$G$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(F26,Compose_0pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F26&lt;=INDEX(Compose_0pct!$G$15:$G$66,1),INDEX(Compose_0pct!$A$15:$A$66,1),IF(F26&gt;=INDEX(Compose_0pct!$G$15:$G$66,ROWS(Compose_0pct!$G$15:$G$66)),INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$A$15:$A$66,MATCH(F26,Compose_0pct!$G$15:$G$66,1))+(F26-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F26,Compose_0pct!$G$15:$G$66,1)))/(INDEX(Compose_0pct!$G$15:$G$66,MATCH(F26,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$G$15:$G$66,MATCH(F26,Compose_0pct!$G$15:$G$66,1)))*(INDEX(Compose_0pct!$A$15:$A$66,MATCH(F26,Compose_0pct!$G$15:$G$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(F26,Compose_0pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D27" s="17">
-        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$J$13:$J$64,1),IF(C27&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$J$13:$J$64,ROWS(Compose_0pct!$J$13:$J$64)),INDEX(Compose_0pct!$J$13:$J$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1))+(C27-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$J$13:$J$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$J$13:$J$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$J$15:$J$66,1),IF(C27&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$J$15:$J$66,ROWS(Compose_0pct!$J$15:$J$66)),INDEX(Compose_0pct!$J$15:$J$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1))+(C27-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$J$15:$J$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$J$15:$J$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E27" s="16">
@@ -2609,11 +2609,11 @@
         <v/>
       </c>
       <c r="G27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$H$13:$H$64,1),IF(C27&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$H$13:$H$64,ROWS(Compose_0pct!$H$13:$H$64)),INDEX(Compose_0pct!$H$13:$H$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1))+(C27-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$H$13:$H$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$H$13:$H$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$H$15:$H$66,1),IF(C27&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$H$15:$H$66,ROWS(Compose_0pct!$H$15:$H$66)),INDEX(Compose_0pct!$H$15:$H$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1))+(C27-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$H$15:$H$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$H$15:$H$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_0pct!$A$13:$A$64,1),INDEX(Compose_0pct!$I$13:$I$64,1),IF(C27&gt;=INDEX(Compose_0pct!$A$13:$A$64,ROWS(Compose_0pct!$A$13:$A$64)),INDEX(Compose_0pct!$I$13:$I$64,ROWS(Compose_0pct!$I$13:$I$64)),INDEX(Compose_0pct!$I$13:$I$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1))+(C27-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1)))/(INDEX(Compose_0pct!$A$13:$A$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$A$13:$A$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1)))*(INDEX(Compose_0pct!$I$13:$I$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1)+1)-INDEX(Compose_0pct!$I$13:$I$64,MATCH(C27,Compose_0pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_0pct!$A$15:$A$66,1),INDEX(Compose_0pct!$I$15:$I$66,1),IF(C27&gt;=INDEX(Compose_0pct!$A$15:$A$66,ROWS(Compose_0pct!$A$15:$A$66)),INDEX(Compose_0pct!$I$15:$I$66,ROWS(Compose_0pct!$I$15:$I$66)),INDEX(Compose_0pct!$I$15:$I$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1))+(C27-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1)))/(INDEX(Compose_0pct!$A$15:$A$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$A$15:$A$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1)))*(INDEX(Compose_0pct!$I$15:$I$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1)+1)-INDEX(Compose_0pct!$I$15:$I$66,MATCH(C27,Compose_0pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I27" s="21">
@@ -2636,7 +2636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2649,7 +2649,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colonnes = formules Excel. Crest / facteur pipe en jaune.</t>
+          <t>Colonnes = formules Excel. Crest / facteur pipe / plafond Q en jaune.</t>
         </is>
       </c>
     </row>
@@ -2742,134 +2742,72 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q_cap (m3/s)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>WSE</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>HW</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>y_ov</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>A_ditch</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>V_ditch</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>V_pond</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>V_total</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Q_1200</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>Q_overflow</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>Qout</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="B13" s="19">
-        <f>A13-$B$10</f>
-        <v/>
-      </c>
-      <c r="C13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="16">
-        <f>IF(A13&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A13&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1))+(A13-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G13" s="14">
-        <f>F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
-        <f>($B$11)*(IF(B13&lt;=0,0,IF(B13&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))+(B13-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="8">
-        <f>H13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="n">
-        <v>34.98</v>
-      </c>
-      <c r="B14" s="19">
-        <f>A14-$B$10</f>
-        <v/>
-      </c>
-      <c r="C14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="16">
-        <f>IF(A14&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A14&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1))+(A14-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G14" s="14">
-        <f>F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
-        <f>($B$11)*(IF(B14&lt;=0,0,IF(B14&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))+(B14-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="8">
-        <f>H14</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="n">
-        <v>35.08</v>
+        <v>34.88</v>
       </c>
       <c r="B15" s="19">
         <f>A15-$B$10</f>
@@ -2893,7 +2831,7 @@
         <v/>
       </c>
       <c r="H15" s="17">
-        <f>($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I15" s="17" t="n">
@@ -2906,7 +2844,7 @@
     </row>
     <row r="16">
       <c r="A16" s="19" t="n">
-        <v>35.18</v>
+        <v>34.98</v>
       </c>
       <c r="B16" s="19">
         <f>A16-$B$10</f>
@@ -2930,7 +2868,7 @@
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I16" s="17" t="n">
@@ -2943,7 +2881,7 @@
     </row>
     <row r="17">
       <c r="A17" s="19" t="n">
-        <v>35.28</v>
+        <v>35.08</v>
       </c>
       <c r="B17" s="19">
         <f>A17-$B$10</f>
@@ -2967,7 +2905,7 @@
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I17" s="17" t="n">
@@ -2980,7 +2918,7 @@
     </row>
     <row r="18">
       <c r="A18" s="19" t="n">
-        <v>35.38</v>
+        <v>35.18</v>
       </c>
       <c r="B18" s="19">
         <f>A18-$B$10</f>
@@ -3004,7 +2942,7 @@
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I18" s="17" t="n">
@@ -3017,7 +2955,7 @@
     </row>
     <row r="19">
       <c r="A19" s="19" t="n">
-        <v>35.48</v>
+        <v>35.28</v>
       </c>
       <c r="B19" s="19">
         <f>A19-$B$10</f>
@@ -3041,7 +2979,7 @@
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I19" s="17" t="n">
@@ -3054,7 +2992,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="n">
-        <v>35.58</v>
+        <v>35.38</v>
       </c>
       <c r="B20" s="19">
         <f>A20-$B$10</f>
@@ -3078,7 +3016,7 @@
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I20" s="17" t="n">
@@ -3091,7 +3029,7 @@
     </row>
     <row r="21">
       <c r="A21" s="19" t="n">
-        <v>35.68</v>
+        <v>35.48</v>
       </c>
       <c r="B21" s="19">
         <f>A21-$B$10</f>
@@ -3115,7 +3053,7 @@
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I21" s="17" t="n">
@@ -3128,7 +3066,7 @@
     </row>
     <row r="22">
       <c r="A22" s="19" t="n">
-        <v>35.78</v>
+        <v>35.58</v>
       </c>
       <c r="B22" s="19">
         <f>A22-$B$10</f>
@@ -3152,7 +3090,7 @@
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I22" s="17" t="n">
@@ -3165,7 +3103,7 @@
     </row>
     <row r="23">
       <c r="A23" s="19" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="B23" s="19">
         <f>A23-$B$10</f>
@@ -3189,7 +3127,7 @@
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I23" s="17" t="n">
@@ -3202,7 +3140,7 @@
     </row>
     <row r="24">
       <c r="A24" s="19" t="n">
-        <v>35.98</v>
+        <v>35.78</v>
       </c>
       <c r="B24" s="19">
         <f>A24-$B$10</f>
@@ -3226,7 +3164,7 @@
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I24" s="17" t="n">
@@ -3239,7 +3177,7 @@
     </row>
     <row r="25">
       <c r="A25" s="19" t="n">
-        <v>36.08</v>
+        <v>35.88</v>
       </c>
       <c r="B25" s="19">
         <f>A25-$B$10</f>
@@ -3263,7 +3201,7 @@
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I25" s="17" t="n">
@@ -3276,7 +3214,7 @@
     </row>
     <row r="26">
       <c r="A26" s="19" t="n">
-        <v>36.18</v>
+        <v>35.98</v>
       </c>
       <c r="B26" s="19">
         <f>A26-$B$10</f>
@@ -3300,7 +3238,7 @@
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I26" s="17" t="n">
@@ -3313,7 +3251,7 @@
     </row>
     <row r="27">
       <c r="A27" s="19" t="n">
-        <v>36.28</v>
+        <v>36.08</v>
       </c>
       <c r="B27" s="19">
         <f>A27-$B$10</f>
@@ -3337,7 +3275,7 @@
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I27" s="17" t="n">
@@ -3350,7 +3288,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="n">
-        <v>36.38</v>
+        <v>36.18</v>
       </c>
       <c r="B28" s="19">
         <f>A28-$B$10</f>
@@ -3374,7 +3312,7 @@
         <v/>
       </c>
       <c r="H28" s="17">
-        <f>($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I28" s="17" t="n">
@@ -3387,7 +3325,7 @@
     </row>
     <row r="29">
       <c r="A29" s="19" t="n">
-        <v>36.48</v>
+        <v>36.28</v>
       </c>
       <c r="B29" s="19">
         <f>A29-$B$10</f>
@@ -3411,7 +3349,7 @@
         <v/>
       </c>
       <c r="H29" s="17">
-        <f>($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I29" s="17" t="n">
@@ -3424,7 +3362,7 @@
     </row>
     <row r="30">
       <c r="A30" s="19" t="n">
-        <v>36.58</v>
+        <v>36.38</v>
       </c>
       <c r="B30" s="19">
         <f>A30-$B$10</f>
@@ -3448,7 +3386,7 @@
         <v/>
       </c>
       <c r="H30" s="17">
-        <f>($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I30" s="17" t="n">
@@ -3461,7 +3399,7 @@
     </row>
     <row r="31">
       <c r="A31" s="19" t="n">
-        <v>36.68</v>
+        <v>36.48</v>
       </c>
       <c r="B31" s="19">
         <f>A31-$B$10</f>
@@ -3485,7 +3423,7 @@
         <v/>
       </c>
       <c r="H31" s="17">
-        <f>($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I31" s="17" t="n">
@@ -3498,7 +3436,7 @@
     </row>
     <row r="32">
       <c r="A32" s="19" t="n">
-        <v>36.78</v>
+        <v>36.58</v>
       </c>
       <c r="B32" s="19">
         <f>A32-$B$10</f>
@@ -3522,7 +3460,7 @@
         <v/>
       </c>
       <c r="H32" s="17">
-        <f>($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I32" s="17" t="n">
@@ -3535,7 +3473,7 @@
     </row>
     <row r="33">
       <c r="A33" s="19" t="n">
-        <v>36.88</v>
+        <v>36.68</v>
       </c>
       <c r="B33" s="19">
         <f>A33-$B$10</f>
@@ -3559,7 +3497,7 @@
         <v/>
       </c>
       <c r="H33" s="17">
-        <f>($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I33" s="17" t="n">
@@ -3572,7 +3510,7 @@
     </row>
     <row r="34">
       <c r="A34" s="19" t="n">
-        <v>36.98</v>
+        <v>36.78</v>
       </c>
       <c r="B34" s="19">
         <f>A34-$B$10</f>
@@ -3596,7 +3534,7 @@
         <v/>
       </c>
       <c r="H34" s="17">
-        <f>($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I34" s="17" t="n">
@@ -3609,7 +3547,7 @@
     </row>
     <row r="35">
       <c r="A35" s="19" t="n">
-        <v>37.08</v>
+        <v>36.88</v>
       </c>
       <c r="B35" s="19">
         <f>A35-$B$10</f>
@@ -3633,7 +3571,7 @@
         <v/>
       </c>
       <c r="H35" s="17">
-        <f>($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I35" s="17" t="n">
@@ -3646,7 +3584,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="n">
-        <v>37.18</v>
+        <v>36.98</v>
       </c>
       <c r="B36" s="19">
         <f>A36-$B$10</f>
@@ -3670,7 +3608,7 @@
         <v/>
       </c>
       <c r="H36" s="17">
-        <f>($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I36" s="17" t="n">
@@ -3683,7 +3621,7 @@
     </row>
     <row r="37">
       <c r="A37" s="19" t="n">
-        <v>37.28</v>
+        <v>37.08</v>
       </c>
       <c r="B37" s="19">
         <f>A37-$B$10</f>
@@ -3707,7 +3645,7 @@
         <v/>
       </c>
       <c r="H37" s="17">
-        <f>($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I37" s="17" t="n">
@@ -3720,7 +3658,7 @@
     </row>
     <row r="38">
       <c r="A38" s="19" t="n">
-        <v>37.38</v>
+        <v>37.18</v>
       </c>
       <c r="B38" s="19">
         <f>A38-$B$10</f>
@@ -3744,7 +3682,7 @@
         <v/>
       </c>
       <c r="H38" s="17">
-        <f>($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I38" s="17" t="n">
@@ -3757,7 +3695,7 @@
     </row>
     <row r="39">
       <c r="A39" s="19" t="n">
-        <v>37.48</v>
+        <v>37.28</v>
       </c>
       <c r="B39" s="19">
         <f>A39-$B$10</f>
@@ -3781,7 +3719,7 @@
         <v/>
       </c>
       <c r="H39" s="17">
-        <f>($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I39" s="17" t="n">
@@ -3794,7 +3732,7 @@
     </row>
     <row r="40">
       <c r="A40" s="19" t="n">
-        <v>37.58</v>
+        <v>37.38</v>
       </c>
       <c r="B40" s="19">
         <f>A40-$B$10</f>
@@ -3818,7 +3756,7 @@
         <v/>
       </c>
       <c r="H40" s="17">
-        <f>($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I40" s="17" t="n">
@@ -3831,7 +3769,7 @@
     </row>
     <row r="41">
       <c r="A41" s="19" t="n">
-        <v>37.68</v>
+        <v>37.48</v>
       </c>
       <c r="B41" s="19">
         <f>A41-$B$10</f>
@@ -3855,7 +3793,7 @@
         <v/>
       </c>
       <c r="H41" s="17">
-        <f>($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I41" s="17" t="n">
@@ -3868,7 +3806,7 @@
     </row>
     <row r="42">
       <c r="A42" s="19" t="n">
-        <v>37.78</v>
+        <v>37.58</v>
       </c>
       <c r="B42" s="19">
         <f>A42-$B$10</f>
@@ -3892,7 +3830,7 @@
         <v/>
       </c>
       <c r="H42" s="17">
-        <f>($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I42" s="17" t="n">
@@ -3905,7 +3843,7 @@
     </row>
     <row r="43">
       <c r="A43" s="19" t="n">
-        <v>37.88</v>
+        <v>37.68</v>
       </c>
       <c r="B43" s="19">
         <f>A43-$B$10</f>
@@ -3929,7 +3867,7 @@
         <v/>
       </c>
       <c r="H43" s="17">
-        <f>($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I43" s="17" t="n">
@@ -3942,7 +3880,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="n">
-        <v>37.98</v>
+        <v>37.78</v>
       </c>
       <c r="B44" s="19">
         <f>A44-$B$10</f>
@@ -3966,7 +3904,7 @@
         <v/>
       </c>
       <c r="H44" s="17">
-        <f>($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I44" s="17" t="n">
@@ -3979,7 +3917,7 @@
     </row>
     <row r="45">
       <c r="A45" s="19" t="n">
-        <v>38.08</v>
+        <v>37.88</v>
       </c>
       <c r="B45" s="19">
         <f>A45-$B$10</f>
@@ -4003,7 +3941,7 @@
         <v/>
       </c>
       <c r="H45" s="17">
-        <f>($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I45" s="17" t="n">
@@ -4016,7 +3954,7 @@
     </row>
     <row r="46">
       <c r="A46" s="19" t="n">
-        <v>38.18</v>
+        <v>37.98</v>
       </c>
       <c r="B46" s="19">
         <f>A46-$B$10</f>
@@ -4040,7 +3978,7 @@
         <v/>
       </c>
       <c r="H46" s="17">
-        <f>($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I46" s="17" t="n">
@@ -4053,7 +3991,7 @@
     </row>
     <row r="47">
       <c r="A47" s="19" t="n">
-        <v>38.28</v>
+        <v>38.08</v>
       </c>
       <c r="B47" s="19">
         <f>A47-$B$10</f>
@@ -4077,7 +4015,7 @@
         <v/>
       </c>
       <c r="H47" s="17">
-        <f>($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I47" s="17" t="n">
@@ -4090,7 +4028,7 @@
     </row>
     <row r="48">
       <c r="A48" s="19" t="n">
-        <v>38.38</v>
+        <v>38.18</v>
       </c>
       <c r="B48" s="19">
         <f>A48-$B$10</f>
@@ -4114,7 +4052,7 @@
         <v/>
       </c>
       <c r="H48" s="17">
-        <f>($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I48" s="17" t="n">
@@ -4127,7 +4065,7 @@
     </row>
     <row r="49">
       <c r="A49" s="19" t="n">
-        <v>38.48</v>
+        <v>38.28</v>
       </c>
       <c r="B49" s="19">
         <f>A49-$B$10</f>
@@ -4151,7 +4089,7 @@
         <v/>
       </c>
       <c r="H49" s="17">
-        <f>($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I49" s="17" t="n">
@@ -4164,7 +4102,7 @@
     </row>
     <row r="50">
       <c r="A50" s="19" t="n">
-        <v>38.58</v>
+        <v>38.38</v>
       </c>
       <c r="B50" s="19">
         <f>A50-$B$10</f>
@@ -4188,7 +4126,7 @@
         <v/>
       </c>
       <c r="H50" s="17">
-        <f>($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I50" s="17" t="n">
@@ -4201,7 +4139,7 @@
     </row>
     <row r="51">
       <c r="A51" s="19" t="n">
-        <v>38.68</v>
+        <v>38.48</v>
       </c>
       <c r="B51" s="19">
         <f>A51-$B$10</f>
@@ -4225,7 +4163,7 @@
         <v/>
       </c>
       <c r="H51" s="17">
-        <f>($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I51" s="17" t="n">
@@ -4238,7 +4176,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="n">
-        <v>38.78</v>
+        <v>38.58</v>
       </c>
       <c r="B52" s="19">
         <f>A52-$B$10</f>
@@ -4262,7 +4200,7 @@
         <v/>
       </c>
       <c r="H52" s="17">
-        <f>($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I52" s="17" t="n">
@@ -4275,7 +4213,7 @@
     </row>
     <row r="53">
       <c r="A53" s="19" t="n">
-        <v>38.88</v>
+        <v>38.68</v>
       </c>
       <c r="B53" s="19">
         <f>A53-$B$10</f>
@@ -4299,7 +4237,7 @@
         <v/>
       </c>
       <c r="H53" s="17">
-        <f>($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I53" s="17" t="n">
@@ -4312,7 +4250,7 @@
     </row>
     <row r="54">
       <c r="A54" s="19" t="n">
-        <v>38.98</v>
+        <v>38.78</v>
       </c>
       <c r="B54" s="19">
         <f>A54-$B$10</f>
@@ -4336,7 +4274,7 @@
         <v/>
       </c>
       <c r="H54" s="17">
-        <f>($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I54" s="17" t="n">
@@ -4349,7 +4287,7 @@
     </row>
     <row r="55">
       <c r="A55" s="19" t="n">
-        <v>39.08</v>
+        <v>38.88</v>
       </c>
       <c r="B55" s="19">
         <f>A55-$B$10</f>
@@ -4373,7 +4311,7 @@
         <v/>
       </c>
       <c r="H55" s="17">
-        <f>($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I55" s="17" t="n">
@@ -4386,7 +4324,7 @@
     </row>
     <row r="56">
       <c r="A56" s="19" t="n">
-        <v>39.18</v>
+        <v>38.98</v>
       </c>
       <c r="B56" s="19">
         <f>A56-$B$10</f>
@@ -4410,7 +4348,7 @@
         <v/>
       </c>
       <c r="H56" s="17">
-        <f>($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I56" s="17" t="n">
@@ -4423,7 +4361,7 @@
     </row>
     <row r="57">
       <c r="A57" s="19" t="n">
-        <v>39.28</v>
+        <v>39.08</v>
       </c>
       <c r="B57" s="19">
         <f>A57-$B$10</f>
@@ -4447,7 +4385,7 @@
         <v/>
       </c>
       <c r="H57" s="17">
-        <f>($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I57" s="17" t="n">
@@ -4460,7 +4398,7 @@
     </row>
     <row r="58">
       <c r="A58" s="19" t="n">
-        <v>39.38</v>
+        <v>39.18</v>
       </c>
       <c r="B58" s="19">
         <f>A58-$B$10</f>
@@ -4484,7 +4422,7 @@
         <v/>
       </c>
       <c r="H58" s="17">
-        <f>($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I58" s="17" t="n">
@@ -4497,7 +4435,7 @@
     </row>
     <row r="59">
       <c r="A59" s="19" t="n">
-        <v>39.48</v>
+        <v>39.28</v>
       </c>
       <c r="B59" s="19">
         <f>A59-$B$10</f>
@@ -4521,7 +4459,7 @@
         <v/>
       </c>
       <c r="H59" s="17">
-        <f>($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I59" s="17" t="n">
@@ -4534,7 +4472,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="n">
-        <v>39.58</v>
+        <v>39.38</v>
       </c>
       <c r="B60" s="19">
         <f>A60-$B$10</f>
@@ -4558,7 +4496,7 @@
         <v/>
       </c>
       <c r="H60" s="17">
-        <f>($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I60" s="17" t="n">
@@ -4571,7 +4509,7 @@
     </row>
     <row r="61">
       <c r="A61" s="19" t="n">
-        <v>39.68</v>
+        <v>39.48</v>
       </c>
       <c r="B61" s="19">
         <f>A61-$B$10</f>
@@ -4595,7 +4533,7 @@
         <v/>
       </c>
       <c r="H61" s="17">
-        <f>($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I61" s="17" t="n">
@@ -4608,7 +4546,7 @@
     </row>
     <row r="62">
       <c r="A62" s="19" t="n">
-        <v>39.78</v>
+        <v>39.58</v>
       </c>
       <c r="B62" s="19">
         <f>A62-$B$10</f>
@@ -4632,7 +4570,7 @@
         <v/>
       </c>
       <c r="H62" s="17">
-        <f>($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I62" s="17" t="n">
@@ -4645,7 +4583,7 @@
     </row>
     <row r="63">
       <c r="A63" s="19" t="n">
-        <v>39.88</v>
+        <v>39.68</v>
       </c>
       <c r="B63" s="19">
         <f>A63-$B$10</f>
@@ -4669,7 +4607,7 @@
         <v/>
       </c>
       <c r="H63" s="17">
-        <f>($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I63" s="17" t="n">
@@ -4682,7 +4620,7 @@
     </row>
     <row r="64">
       <c r="A64" s="19" t="n">
-        <v>39.98</v>
+        <v>39.78</v>
       </c>
       <c r="B64" s="19">
         <f>A64-$B$10</f>
@@ -4706,7 +4644,7 @@
         <v/>
       </c>
       <c r="H64" s="17">
-        <f>($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I64" s="17" t="n">
@@ -4714,6 +4652,80 @@
       </c>
       <c r="J64" s="8">
         <f>H64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="B65" s="19">
+        <f>A65-$B$10</f>
+        <v/>
+      </c>
+      <c r="C65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="16">
+        <f>IF(A65&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A65&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1))+(A65-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G65" s="14">
+        <f>F65</f>
+        <v/>
+      </c>
+      <c r="H65" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B65&lt;=0,0,IF(B65&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1))+(B65-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I65" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="8">
+        <f>H65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="B66" s="19">
+        <f>A66-$B$10</f>
+        <v/>
+      </c>
+      <c r="C66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="16">
+        <f>IF(A66&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A66&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1))+(A66-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G66" s="14">
+        <f>F66</f>
+        <v/>
+      </c>
+      <c r="H66" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B66&lt;=0,0,IF(B66&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1))+(B66-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I66" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="8">
+        <f>H66</f>
         <v/>
       </c>
     </row>
@@ -4950,11 +4962,11 @@
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>IF(F15&lt;=INDEX(Compose_100_NoOv!$G$13:$G$64,1),INDEX(Compose_100_NoOv!$A$13:$A$64,1),IF(F15&gt;=INDEX(Compose_100_NoOv!$G$13:$G$64,ROWS(Compose_100_NoOv!$G$13:$G$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F15,Compose_100_NoOv!$G$13:$G$64,1))+(F15-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F15,Compose_100_NoOv!$G$13:$G$64,1)))/(INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F15,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F15,Compose_100_NoOv!$G$13:$G$64,1)))*(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F15,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F15,Compose_100_NoOv!$G$13:$G$64,1)))))</f>
+        <f>IF(F15&lt;=INDEX(Compose_100_NoOv!$G$15:$G$66,1),INDEX(Compose_100_NoOv!$A$15:$A$66,1),IF(F15&gt;=INDEX(Compose_100_NoOv!$G$15:$G$66,ROWS(Compose_100_NoOv!$G$15:$G$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F15,Compose_100_NoOv!$G$15:$G$66,1))+(F15-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F15,Compose_100_NoOv!$G$15:$G$66,1)))/(INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F15,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F15,Compose_100_NoOv!$G$15:$G$66,1)))*(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F15,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F15,Compose_100_NoOv!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$J$13:$J$64,1),IF(C16&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,ROWS(Compose_100_NoOv!$J$13:$J$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1))+(C16-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1))))))</f>
+        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$J$15:$J$66,1),IF(C16&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,ROWS(Compose_100_NoOv!$J$15:$J$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1))+(C16-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E16" s="16">
@@ -4966,11 +4978,11 @@
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$H$13:$H$64,1),IF(C16&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,ROWS(Compose_100_NoOv!$H$13:$H$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1))+(C16-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$H$15:$H$66,1),IF(C16&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,ROWS(Compose_100_NoOv!$H$15:$H$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1))+(C16-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$I$13:$I$64,1),IF(C16&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,ROWS(Compose_100_NoOv!$I$13:$I$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1))+(C16-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C16,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$I$15:$I$66,1),IF(C16&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,ROWS(Compose_100_NoOv!$I$15:$I$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1))+(C16-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C16,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I16" s="21">
@@ -4988,11 +5000,11 @@
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>IF(F16&lt;=INDEX(Compose_100_NoOv!$G$13:$G$64,1),INDEX(Compose_100_NoOv!$A$13:$A$64,1),IF(F16&gt;=INDEX(Compose_100_NoOv!$G$13:$G$64,ROWS(Compose_100_NoOv!$G$13:$G$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F16,Compose_100_NoOv!$G$13:$G$64,1))+(F16-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F16,Compose_100_NoOv!$G$13:$G$64,1)))/(INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F16,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F16,Compose_100_NoOv!$G$13:$G$64,1)))*(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F16,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F16,Compose_100_NoOv!$G$13:$G$64,1)))))</f>
+        <f>IF(F16&lt;=INDEX(Compose_100_NoOv!$G$15:$G$66,1),INDEX(Compose_100_NoOv!$A$15:$A$66,1),IF(F16&gt;=INDEX(Compose_100_NoOv!$G$15:$G$66,ROWS(Compose_100_NoOv!$G$15:$G$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F16,Compose_100_NoOv!$G$15:$G$66,1))+(F16-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F16,Compose_100_NoOv!$G$15:$G$66,1)))/(INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F16,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F16,Compose_100_NoOv!$G$15:$G$66,1)))*(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F16,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F16,Compose_100_NoOv!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$J$13:$J$64,1),IF(C17&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,ROWS(Compose_100_NoOv!$J$13:$J$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1))+(C17-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1))))))</f>
+        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$J$15:$J$66,1),IF(C17&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,ROWS(Compose_100_NoOv!$J$15:$J$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1))+(C17-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E17" s="16">
@@ -5004,11 +5016,11 @@
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$H$13:$H$64,1),IF(C17&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,ROWS(Compose_100_NoOv!$H$13:$H$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1))+(C17-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$H$15:$H$66,1),IF(C17&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,ROWS(Compose_100_NoOv!$H$15:$H$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1))+(C17-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$I$13:$I$64,1),IF(C17&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,ROWS(Compose_100_NoOv!$I$13:$I$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1))+(C17-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C17,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$I$15:$I$66,1),IF(C17&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,ROWS(Compose_100_NoOv!$I$15:$I$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1))+(C17-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C17,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I17" s="21">
@@ -5026,11 +5038,11 @@
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>IF(F17&lt;=INDEX(Compose_100_NoOv!$G$13:$G$64,1),INDEX(Compose_100_NoOv!$A$13:$A$64,1),IF(F17&gt;=INDEX(Compose_100_NoOv!$G$13:$G$64,ROWS(Compose_100_NoOv!$G$13:$G$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F17,Compose_100_NoOv!$G$13:$G$64,1))+(F17-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F17,Compose_100_NoOv!$G$13:$G$64,1)))/(INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F17,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F17,Compose_100_NoOv!$G$13:$G$64,1)))*(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F17,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F17,Compose_100_NoOv!$G$13:$G$64,1)))))</f>
+        <f>IF(F17&lt;=INDEX(Compose_100_NoOv!$G$15:$G$66,1),INDEX(Compose_100_NoOv!$A$15:$A$66,1),IF(F17&gt;=INDEX(Compose_100_NoOv!$G$15:$G$66,ROWS(Compose_100_NoOv!$G$15:$G$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F17,Compose_100_NoOv!$G$15:$G$66,1))+(F17-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F17,Compose_100_NoOv!$G$15:$G$66,1)))/(INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F17,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F17,Compose_100_NoOv!$G$15:$G$66,1)))*(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F17,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F17,Compose_100_NoOv!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$J$13:$J$64,1),IF(C18&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,ROWS(Compose_100_NoOv!$J$13:$J$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1))+(C18-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1))))))</f>
+        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$J$15:$J$66,1),IF(C18&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,ROWS(Compose_100_NoOv!$J$15:$J$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1))+(C18-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E18" s="16">
@@ -5042,11 +5054,11 @@
         <v/>
       </c>
       <c r="G18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$H$13:$H$64,1),IF(C18&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,ROWS(Compose_100_NoOv!$H$13:$H$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1))+(C18-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$H$15:$H$66,1),IF(C18&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,ROWS(Compose_100_NoOv!$H$15:$H$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1))+(C18-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$I$13:$I$64,1),IF(C18&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,ROWS(Compose_100_NoOv!$I$13:$I$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1))+(C18-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C18,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$I$15:$I$66,1),IF(C18&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,ROWS(Compose_100_NoOv!$I$15:$I$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1))+(C18-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C18,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I18" s="21">
@@ -5064,11 +5076,11 @@
         <v/>
       </c>
       <c r="C19" s="17">
-        <f>IF(F18&lt;=INDEX(Compose_100_NoOv!$G$13:$G$64,1),INDEX(Compose_100_NoOv!$A$13:$A$64,1),IF(F18&gt;=INDEX(Compose_100_NoOv!$G$13:$G$64,ROWS(Compose_100_NoOv!$G$13:$G$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F18,Compose_100_NoOv!$G$13:$G$64,1))+(F18-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F18,Compose_100_NoOv!$G$13:$G$64,1)))/(INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F18,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F18,Compose_100_NoOv!$G$13:$G$64,1)))*(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F18,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F18,Compose_100_NoOv!$G$13:$G$64,1)))))</f>
+        <f>IF(F18&lt;=INDEX(Compose_100_NoOv!$G$15:$G$66,1),INDEX(Compose_100_NoOv!$A$15:$A$66,1),IF(F18&gt;=INDEX(Compose_100_NoOv!$G$15:$G$66,ROWS(Compose_100_NoOv!$G$15:$G$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F18,Compose_100_NoOv!$G$15:$G$66,1))+(F18-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F18,Compose_100_NoOv!$G$15:$G$66,1)))/(INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F18,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F18,Compose_100_NoOv!$G$15:$G$66,1)))*(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F18,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F18,Compose_100_NoOv!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$J$13:$J$64,1),IF(C19&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,ROWS(Compose_100_NoOv!$J$13:$J$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1))+(C19-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1))))))</f>
+        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$J$15:$J$66,1),IF(C19&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,ROWS(Compose_100_NoOv!$J$15:$J$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1))+(C19-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E19" s="16">
@@ -5080,11 +5092,11 @@
         <v/>
       </c>
       <c r="G19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$H$13:$H$64,1),IF(C19&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,ROWS(Compose_100_NoOv!$H$13:$H$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1))+(C19-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$H$15:$H$66,1),IF(C19&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,ROWS(Compose_100_NoOv!$H$15:$H$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1))+(C19-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$I$13:$I$64,1),IF(C19&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,ROWS(Compose_100_NoOv!$I$13:$I$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1))+(C19-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C19,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$I$15:$I$66,1),IF(C19&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,ROWS(Compose_100_NoOv!$I$15:$I$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1))+(C19-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C19,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I19" s="21">
@@ -5102,11 +5114,11 @@
         <v/>
       </c>
       <c r="C20" s="17">
-        <f>IF(F19&lt;=INDEX(Compose_100_NoOv!$G$13:$G$64,1),INDEX(Compose_100_NoOv!$A$13:$A$64,1),IF(F19&gt;=INDEX(Compose_100_NoOv!$G$13:$G$64,ROWS(Compose_100_NoOv!$G$13:$G$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F19,Compose_100_NoOv!$G$13:$G$64,1))+(F19-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F19,Compose_100_NoOv!$G$13:$G$64,1)))/(INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F19,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F19,Compose_100_NoOv!$G$13:$G$64,1)))*(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F19,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F19,Compose_100_NoOv!$G$13:$G$64,1)))))</f>
+        <f>IF(F19&lt;=INDEX(Compose_100_NoOv!$G$15:$G$66,1),INDEX(Compose_100_NoOv!$A$15:$A$66,1),IF(F19&gt;=INDEX(Compose_100_NoOv!$G$15:$G$66,ROWS(Compose_100_NoOv!$G$15:$G$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F19,Compose_100_NoOv!$G$15:$G$66,1))+(F19-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F19,Compose_100_NoOv!$G$15:$G$66,1)))/(INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F19,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F19,Compose_100_NoOv!$G$15:$G$66,1)))*(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F19,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F19,Compose_100_NoOv!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D20" s="17">
-        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$J$13:$J$64,1),IF(C20&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,ROWS(Compose_100_NoOv!$J$13:$J$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1))+(C20-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1))))))</f>
+        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$J$15:$J$66,1),IF(C20&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,ROWS(Compose_100_NoOv!$J$15:$J$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1))+(C20-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E20" s="16">
@@ -5118,11 +5130,11 @@
         <v/>
       </c>
       <c r="G20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$H$13:$H$64,1),IF(C20&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,ROWS(Compose_100_NoOv!$H$13:$H$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1))+(C20-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$H$15:$H$66,1),IF(C20&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,ROWS(Compose_100_NoOv!$H$15:$H$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1))+(C20-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$I$13:$I$64,1),IF(C20&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,ROWS(Compose_100_NoOv!$I$13:$I$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1))+(C20-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C20,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$I$15:$I$66,1),IF(C20&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,ROWS(Compose_100_NoOv!$I$15:$I$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1))+(C20-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C20,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I20" s="21">
@@ -5140,11 +5152,11 @@
         <v/>
       </c>
       <c r="C21" s="17">
-        <f>IF(F20&lt;=INDEX(Compose_100_NoOv!$G$13:$G$64,1),INDEX(Compose_100_NoOv!$A$13:$A$64,1),IF(F20&gt;=INDEX(Compose_100_NoOv!$G$13:$G$64,ROWS(Compose_100_NoOv!$G$13:$G$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F20,Compose_100_NoOv!$G$13:$G$64,1))+(F20-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F20,Compose_100_NoOv!$G$13:$G$64,1)))/(INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F20,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F20,Compose_100_NoOv!$G$13:$G$64,1)))*(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F20,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F20,Compose_100_NoOv!$G$13:$G$64,1)))))</f>
+        <f>IF(F20&lt;=INDEX(Compose_100_NoOv!$G$15:$G$66,1),INDEX(Compose_100_NoOv!$A$15:$A$66,1),IF(F20&gt;=INDEX(Compose_100_NoOv!$G$15:$G$66,ROWS(Compose_100_NoOv!$G$15:$G$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F20,Compose_100_NoOv!$G$15:$G$66,1))+(F20-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F20,Compose_100_NoOv!$G$15:$G$66,1)))/(INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F20,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F20,Compose_100_NoOv!$G$15:$G$66,1)))*(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F20,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F20,Compose_100_NoOv!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D21" s="17">
-        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$J$13:$J$64,1),IF(C21&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,ROWS(Compose_100_NoOv!$J$13:$J$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1))+(C21-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1))))))</f>
+        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$J$15:$J$66,1),IF(C21&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,ROWS(Compose_100_NoOv!$J$15:$J$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1))+(C21-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E21" s="16">
@@ -5156,11 +5168,11 @@
         <v/>
       </c>
       <c r="G21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$H$13:$H$64,1),IF(C21&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,ROWS(Compose_100_NoOv!$H$13:$H$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1))+(C21-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$H$15:$H$66,1),IF(C21&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,ROWS(Compose_100_NoOv!$H$15:$H$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1))+(C21-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$I$13:$I$64,1),IF(C21&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,ROWS(Compose_100_NoOv!$I$13:$I$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1))+(C21-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C21,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$I$15:$I$66,1),IF(C21&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,ROWS(Compose_100_NoOv!$I$15:$I$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1))+(C21-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C21,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I21" s="21">
@@ -5178,11 +5190,11 @@
         <v/>
       </c>
       <c r="C22" s="17">
-        <f>IF(F21&lt;=INDEX(Compose_100_NoOv!$G$13:$G$64,1),INDEX(Compose_100_NoOv!$A$13:$A$64,1),IF(F21&gt;=INDEX(Compose_100_NoOv!$G$13:$G$64,ROWS(Compose_100_NoOv!$G$13:$G$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F21,Compose_100_NoOv!$G$13:$G$64,1))+(F21-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F21,Compose_100_NoOv!$G$13:$G$64,1)))/(INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F21,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F21,Compose_100_NoOv!$G$13:$G$64,1)))*(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F21,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F21,Compose_100_NoOv!$G$13:$G$64,1)))))</f>
+        <f>IF(F21&lt;=INDEX(Compose_100_NoOv!$G$15:$G$66,1),INDEX(Compose_100_NoOv!$A$15:$A$66,1),IF(F21&gt;=INDEX(Compose_100_NoOv!$G$15:$G$66,ROWS(Compose_100_NoOv!$G$15:$G$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F21,Compose_100_NoOv!$G$15:$G$66,1))+(F21-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F21,Compose_100_NoOv!$G$15:$G$66,1)))/(INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F21,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F21,Compose_100_NoOv!$G$15:$G$66,1)))*(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F21,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F21,Compose_100_NoOv!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D22" s="17">
-        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$J$13:$J$64,1),IF(C22&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,ROWS(Compose_100_NoOv!$J$13:$J$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1))+(C22-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1))))))</f>
+        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$J$15:$J$66,1),IF(C22&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,ROWS(Compose_100_NoOv!$J$15:$J$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1))+(C22-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E22" s="16">
@@ -5194,11 +5206,11 @@
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$H$13:$H$64,1),IF(C22&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,ROWS(Compose_100_NoOv!$H$13:$H$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1))+(C22-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$H$15:$H$66,1),IF(C22&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,ROWS(Compose_100_NoOv!$H$15:$H$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1))+(C22-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$I$13:$I$64,1),IF(C22&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,ROWS(Compose_100_NoOv!$I$13:$I$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1))+(C22-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C22,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$I$15:$I$66,1),IF(C22&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,ROWS(Compose_100_NoOv!$I$15:$I$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1))+(C22-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C22,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I22" s="21">
@@ -5216,11 +5228,11 @@
         <v/>
       </c>
       <c r="C23" s="17">
-        <f>IF(F22&lt;=INDEX(Compose_100_NoOv!$G$13:$G$64,1),INDEX(Compose_100_NoOv!$A$13:$A$64,1),IF(F22&gt;=INDEX(Compose_100_NoOv!$G$13:$G$64,ROWS(Compose_100_NoOv!$G$13:$G$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F22,Compose_100_NoOv!$G$13:$G$64,1))+(F22-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F22,Compose_100_NoOv!$G$13:$G$64,1)))/(INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F22,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F22,Compose_100_NoOv!$G$13:$G$64,1)))*(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F22,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F22,Compose_100_NoOv!$G$13:$G$64,1)))))</f>
+        <f>IF(F22&lt;=INDEX(Compose_100_NoOv!$G$15:$G$66,1),INDEX(Compose_100_NoOv!$A$15:$A$66,1),IF(F22&gt;=INDEX(Compose_100_NoOv!$G$15:$G$66,ROWS(Compose_100_NoOv!$G$15:$G$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F22,Compose_100_NoOv!$G$15:$G$66,1))+(F22-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F22,Compose_100_NoOv!$G$15:$G$66,1)))/(INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F22,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F22,Compose_100_NoOv!$G$15:$G$66,1)))*(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F22,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F22,Compose_100_NoOv!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D23" s="17">
-        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$J$13:$J$64,1),IF(C23&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,ROWS(Compose_100_NoOv!$J$13:$J$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1))+(C23-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1))))))</f>
+        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$J$15:$J$66,1),IF(C23&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,ROWS(Compose_100_NoOv!$J$15:$J$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1))+(C23-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E23" s="16">
@@ -5232,11 +5244,11 @@
         <v/>
       </c>
       <c r="G23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$H$13:$H$64,1),IF(C23&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,ROWS(Compose_100_NoOv!$H$13:$H$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1))+(C23-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$H$15:$H$66,1),IF(C23&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,ROWS(Compose_100_NoOv!$H$15:$H$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1))+(C23-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$I$13:$I$64,1),IF(C23&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,ROWS(Compose_100_NoOv!$I$13:$I$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1))+(C23-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C23,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$I$15:$I$66,1),IF(C23&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,ROWS(Compose_100_NoOv!$I$15:$I$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1))+(C23-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C23,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I23" s="21">
@@ -5254,11 +5266,11 @@
         <v/>
       </c>
       <c r="C24" s="17">
-        <f>IF(F23&lt;=INDEX(Compose_100_NoOv!$G$13:$G$64,1),INDEX(Compose_100_NoOv!$A$13:$A$64,1),IF(F23&gt;=INDEX(Compose_100_NoOv!$G$13:$G$64,ROWS(Compose_100_NoOv!$G$13:$G$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F23,Compose_100_NoOv!$G$13:$G$64,1))+(F23-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F23,Compose_100_NoOv!$G$13:$G$64,1)))/(INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F23,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F23,Compose_100_NoOv!$G$13:$G$64,1)))*(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F23,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F23,Compose_100_NoOv!$G$13:$G$64,1)))))</f>
+        <f>IF(F23&lt;=INDEX(Compose_100_NoOv!$G$15:$G$66,1),INDEX(Compose_100_NoOv!$A$15:$A$66,1),IF(F23&gt;=INDEX(Compose_100_NoOv!$G$15:$G$66,ROWS(Compose_100_NoOv!$G$15:$G$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F23,Compose_100_NoOv!$G$15:$G$66,1))+(F23-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F23,Compose_100_NoOv!$G$15:$G$66,1)))/(INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F23,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F23,Compose_100_NoOv!$G$15:$G$66,1)))*(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F23,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F23,Compose_100_NoOv!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D24" s="17">
-        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$J$13:$J$64,1),IF(C24&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,ROWS(Compose_100_NoOv!$J$13:$J$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1))+(C24-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1))))))</f>
+        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$J$15:$J$66,1),IF(C24&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,ROWS(Compose_100_NoOv!$J$15:$J$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1))+(C24-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E24" s="16">
@@ -5270,11 +5282,11 @@
         <v/>
       </c>
       <c r="G24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$H$13:$H$64,1),IF(C24&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,ROWS(Compose_100_NoOv!$H$13:$H$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1))+(C24-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$H$15:$H$66,1),IF(C24&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,ROWS(Compose_100_NoOv!$H$15:$H$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1))+(C24-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$I$13:$I$64,1),IF(C24&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,ROWS(Compose_100_NoOv!$I$13:$I$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1))+(C24-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C24,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$I$15:$I$66,1),IF(C24&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,ROWS(Compose_100_NoOv!$I$15:$I$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1))+(C24-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C24,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I24" s="21">
@@ -5292,11 +5304,11 @@
         <v/>
       </c>
       <c r="C25" s="17">
-        <f>IF(F24&lt;=INDEX(Compose_100_NoOv!$G$13:$G$64,1),INDEX(Compose_100_NoOv!$A$13:$A$64,1),IF(F24&gt;=INDEX(Compose_100_NoOv!$G$13:$G$64,ROWS(Compose_100_NoOv!$G$13:$G$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F24,Compose_100_NoOv!$G$13:$G$64,1))+(F24-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F24,Compose_100_NoOv!$G$13:$G$64,1)))/(INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F24,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F24,Compose_100_NoOv!$G$13:$G$64,1)))*(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F24,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F24,Compose_100_NoOv!$G$13:$G$64,1)))))</f>
+        <f>IF(F24&lt;=INDEX(Compose_100_NoOv!$G$15:$G$66,1),INDEX(Compose_100_NoOv!$A$15:$A$66,1),IF(F24&gt;=INDEX(Compose_100_NoOv!$G$15:$G$66,ROWS(Compose_100_NoOv!$G$15:$G$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F24,Compose_100_NoOv!$G$15:$G$66,1))+(F24-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F24,Compose_100_NoOv!$G$15:$G$66,1)))/(INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F24,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F24,Compose_100_NoOv!$G$15:$G$66,1)))*(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F24,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F24,Compose_100_NoOv!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D25" s="17">
-        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$J$13:$J$64,1),IF(C25&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,ROWS(Compose_100_NoOv!$J$13:$J$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1))+(C25-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1))))))</f>
+        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$J$15:$J$66,1),IF(C25&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,ROWS(Compose_100_NoOv!$J$15:$J$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1))+(C25-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E25" s="16">
@@ -5308,11 +5320,11 @@
         <v/>
       </c>
       <c r="G25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$H$13:$H$64,1),IF(C25&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,ROWS(Compose_100_NoOv!$H$13:$H$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1))+(C25-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$H$15:$H$66,1),IF(C25&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,ROWS(Compose_100_NoOv!$H$15:$H$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1))+(C25-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$I$13:$I$64,1),IF(C25&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,ROWS(Compose_100_NoOv!$I$13:$I$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1))+(C25-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C25,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$I$15:$I$66,1),IF(C25&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,ROWS(Compose_100_NoOv!$I$15:$I$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1))+(C25-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C25,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I25" s="21">
@@ -5330,11 +5342,11 @@
         <v/>
       </c>
       <c r="C26" s="17">
-        <f>IF(F25&lt;=INDEX(Compose_100_NoOv!$G$13:$G$64,1),INDEX(Compose_100_NoOv!$A$13:$A$64,1),IF(F25&gt;=INDEX(Compose_100_NoOv!$G$13:$G$64,ROWS(Compose_100_NoOv!$G$13:$G$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F25,Compose_100_NoOv!$G$13:$G$64,1))+(F25-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F25,Compose_100_NoOv!$G$13:$G$64,1)))/(INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F25,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F25,Compose_100_NoOv!$G$13:$G$64,1)))*(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F25,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F25,Compose_100_NoOv!$G$13:$G$64,1)))))</f>
+        <f>IF(F25&lt;=INDEX(Compose_100_NoOv!$G$15:$G$66,1),INDEX(Compose_100_NoOv!$A$15:$A$66,1),IF(F25&gt;=INDEX(Compose_100_NoOv!$G$15:$G$66,ROWS(Compose_100_NoOv!$G$15:$G$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F25,Compose_100_NoOv!$G$15:$G$66,1))+(F25-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F25,Compose_100_NoOv!$G$15:$G$66,1)))/(INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F25,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F25,Compose_100_NoOv!$G$15:$G$66,1)))*(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F25,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F25,Compose_100_NoOv!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D26" s="17">
-        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$J$13:$J$64,1),IF(C26&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,ROWS(Compose_100_NoOv!$J$13:$J$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1))+(C26-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1))))))</f>
+        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$J$15:$J$66,1),IF(C26&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,ROWS(Compose_100_NoOv!$J$15:$J$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1))+(C26-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E26" s="16">
@@ -5346,11 +5358,11 @@
         <v/>
       </c>
       <c r="G26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$H$13:$H$64,1),IF(C26&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,ROWS(Compose_100_NoOv!$H$13:$H$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1))+(C26-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$H$15:$H$66,1),IF(C26&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,ROWS(Compose_100_NoOv!$H$15:$H$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1))+(C26-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$I$13:$I$64,1),IF(C26&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,ROWS(Compose_100_NoOv!$I$13:$I$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1))+(C26-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C26,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$I$15:$I$66,1),IF(C26&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,ROWS(Compose_100_NoOv!$I$15:$I$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1))+(C26-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C26,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I26" s="21">
@@ -5368,11 +5380,11 @@
         <v/>
       </c>
       <c r="C27" s="17">
-        <f>IF(F26&lt;=INDEX(Compose_100_NoOv!$G$13:$G$64,1),INDEX(Compose_100_NoOv!$A$13:$A$64,1),IF(F26&gt;=INDEX(Compose_100_NoOv!$G$13:$G$64,ROWS(Compose_100_NoOv!$G$13:$G$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F26,Compose_100_NoOv!$G$13:$G$64,1))+(F26-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F26,Compose_100_NoOv!$G$13:$G$64,1)))/(INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F26,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$G$13:$G$64,MATCH(F26,Compose_100_NoOv!$G$13:$G$64,1)))*(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F26,Compose_100_NoOv!$G$13:$G$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(F26,Compose_100_NoOv!$G$13:$G$64,1)))))</f>
+        <f>IF(F26&lt;=INDEX(Compose_100_NoOv!$G$15:$G$66,1),INDEX(Compose_100_NoOv!$A$15:$A$66,1),IF(F26&gt;=INDEX(Compose_100_NoOv!$G$15:$G$66,ROWS(Compose_100_NoOv!$G$15:$G$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F26,Compose_100_NoOv!$G$15:$G$66,1))+(F26-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F26,Compose_100_NoOv!$G$15:$G$66,1)))/(INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F26,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$G$15:$G$66,MATCH(F26,Compose_100_NoOv!$G$15:$G$66,1)))*(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F26,Compose_100_NoOv!$G$15:$G$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(F26,Compose_100_NoOv!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D27" s="17">
-        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$J$13:$J$64,1),IF(C27&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,ROWS(Compose_100_NoOv!$J$13:$J$64)),INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1))+(C27-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$J$13:$J$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1))))))</f>
+        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$J$15:$J$66,1),IF(C27&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,ROWS(Compose_100_NoOv!$J$15:$J$66)),INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1))+(C27-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$J$15:$J$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E27" s="16">
@@ -5384,11 +5396,11 @@
         <v/>
       </c>
       <c r="G27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$H$13:$H$64,1),IF(C27&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,ROWS(Compose_100_NoOv!$H$13:$H$64)),INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1))+(C27-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$H$13:$H$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$H$15:$H$66,1),IF(C27&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,ROWS(Compose_100_NoOv!$H$15:$H$66)),INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1))+(C27-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$H$15:$H$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_100_NoOv!$A$13:$A$64,1),INDEX(Compose_100_NoOv!$I$13:$I$64,1),IF(C27&gt;=INDEX(Compose_100_NoOv!$A$13:$A$64,ROWS(Compose_100_NoOv!$A$13:$A$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,ROWS(Compose_100_NoOv!$I$13:$I$64)),INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1))+(C27-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1)))/(INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$A$13:$A$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1)))*(INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1)+1)-INDEX(Compose_100_NoOv!$I$13:$I$64,MATCH(C27,Compose_100_NoOv!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_100_NoOv!$A$15:$A$66,1),INDEX(Compose_100_NoOv!$I$15:$I$66,1),IF(C27&gt;=INDEX(Compose_100_NoOv!$A$15:$A$66,ROWS(Compose_100_NoOv!$A$15:$A$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,ROWS(Compose_100_NoOv!$I$15:$I$66)),INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1))+(C27-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1)))/(INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$A$15:$A$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1)))*(INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1)+1)-INDEX(Compose_100_NoOv!$I$15:$I$66,MATCH(C27,Compose_100_NoOv!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I27" s="21">
@@ -7513,7 +7525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7526,7 +7538,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colonnes = formules Excel. Crest / facteur pipe en jaune.</t>
+          <t>Colonnes = formules Excel. Crest / facteur pipe / plafond Q en jaune.</t>
         </is>
       </c>
     </row>
@@ -7619,142 +7631,72 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q_cap (m3/s)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>WSE</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>HW</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>y_ov</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>A_ditch</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>V_ditch</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>V_pond</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>V_total</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Q_1200</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>Q_overflow</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>Qout</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="B13" s="19">
-        <f>A13-$B$10</f>
-        <v/>
-      </c>
-      <c r="C13" s="19">
-        <f>MAX(0,A13-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D13" s="17">
-        <f>IF(C13&lt;=0,0,($B$5+$B$7*C13)*C13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>D13*$B$9</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>IF(A13&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A13&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1))+(A13-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G13" s="14">
-        <f>E13+F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
-        <f>($B$11)*(IF(B13&lt;=0,0,IF(B13&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))+(B13-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I13" s="17">
-        <f>IF(C13&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D13*IF(($B$5+2*C13*SQRT(1+$B$7^2))&lt;=0,0,((D13/($B$5+2*C13*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J13" s="8">
-        <f>H13+I13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="n">
-        <v>34.98</v>
-      </c>
-      <c r="B14" s="19">
-        <f>A14-$B$10</f>
-        <v/>
-      </c>
-      <c r="C14" s="19">
-        <f>MAX(0,A14-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D14" s="17">
-        <f>IF(C14&lt;=0,0,($B$5+$B$7*C14)*C14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>D14*$B$9</f>
-        <v/>
-      </c>
-      <c r="F14" s="16">
-        <f>IF(A14&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A14&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1))+(A14-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G14" s="14">
-        <f>E14+F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
-        <f>($B$11)*(IF(B14&lt;=0,0,IF(B14&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))+(B14-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
-        <f>IF(C14&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D14*IF(($B$5+2*C14*SQRT(1+$B$7^2))&lt;=0,0,((D14/($B$5+2*C14*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J14" s="8">
-        <f>H14+I14</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="n">
-        <v>35.08</v>
+        <v>34.88</v>
       </c>
       <c r="B15" s="19">
         <f>A15-$B$10</f>
@@ -7781,7 +7723,7 @@
         <v/>
       </c>
       <c r="H15" s="17">
-        <f>($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I15" s="17">
@@ -7795,7 +7737,7 @@
     </row>
     <row r="16">
       <c r="A16" s="19" t="n">
-        <v>35.18</v>
+        <v>34.98</v>
       </c>
       <c r="B16" s="19">
         <f>A16-$B$10</f>
@@ -7822,7 +7764,7 @@
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I16" s="17">
@@ -7836,7 +7778,7 @@
     </row>
     <row r="17">
       <c r="A17" s="19" t="n">
-        <v>35.28</v>
+        <v>35.08</v>
       </c>
       <c r="B17" s="19">
         <f>A17-$B$10</f>
@@ -7863,7 +7805,7 @@
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I17" s="17">
@@ -7877,7 +7819,7 @@
     </row>
     <row r="18">
       <c r="A18" s="19" t="n">
-        <v>35.38</v>
+        <v>35.18</v>
       </c>
       <c r="B18" s="19">
         <f>A18-$B$10</f>
@@ -7904,7 +7846,7 @@
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I18" s="17">
@@ -7918,7 +7860,7 @@
     </row>
     <row r="19">
       <c r="A19" s="19" t="n">
-        <v>35.48</v>
+        <v>35.28</v>
       </c>
       <c r="B19" s="19">
         <f>A19-$B$10</f>
@@ -7945,7 +7887,7 @@
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I19" s="17">
@@ -7959,7 +7901,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="n">
-        <v>35.58</v>
+        <v>35.38</v>
       </c>
       <c r="B20" s="19">
         <f>A20-$B$10</f>
@@ -7986,7 +7928,7 @@
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I20" s="17">
@@ -8000,7 +7942,7 @@
     </row>
     <row r="21">
       <c r="A21" s="19" t="n">
-        <v>35.68</v>
+        <v>35.48</v>
       </c>
       <c r="B21" s="19">
         <f>A21-$B$10</f>
@@ -8027,7 +7969,7 @@
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I21" s="17">
@@ -8041,7 +7983,7 @@
     </row>
     <row r="22">
       <c r="A22" s="19" t="n">
-        <v>35.78</v>
+        <v>35.58</v>
       </c>
       <c r="B22" s="19">
         <f>A22-$B$10</f>
@@ -8068,7 +8010,7 @@
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I22" s="17">
@@ -8082,7 +8024,7 @@
     </row>
     <row r="23">
       <c r="A23" s="19" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="B23" s="19">
         <f>A23-$B$10</f>
@@ -8109,7 +8051,7 @@
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I23" s="17">
@@ -8123,7 +8065,7 @@
     </row>
     <row r="24">
       <c r="A24" s="19" t="n">
-        <v>35.98</v>
+        <v>35.78</v>
       </c>
       <c r="B24" s="19">
         <f>A24-$B$10</f>
@@ -8150,7 +8092,7 @@
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I24" s="17">
@@ -8164,7 +8106,7 @@
     </row>
     <row r="25">
       <c r="A25" s="19" t="n">
-        <v>36.08</v>
+        <v>35.88</v>
       </c>
       <c r="B25" s="19">
         <f>A25-$B$10</f>
@@ -8191,7 +8133,7 @@
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I25" s="17">
@@ -8205,7 +8147,7 @@
     </row>
     <row r="26">
       <c r="A26" s="19" t="n">
-        <v>36.18</v>
+        <v>35.98</v>
       </c>
       <c r="B26" s="19">
         <f>A26-$B$10</f>
@@ -8232,7 +8174,7 @@
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I26" s="17">
@@ -8246,7 +8188,7 @@
     </row>
     <row r="27">
       <c r="A27" s="19" t="n">
-        <v>36.28</v>
+        <v>36.08</v>
       </c>
       <c r="B27" s="19">
         <f>A27-$B$10</f>
@@ -8273,7 +8215,7 @@
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I27" s="17">
@@ -8287,7 +8229,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="n">
-        <v>36.38</v>
+        <v>36.18</v>
       </c>
       <c r="B28" s="19">
         <f>A28-$B$10</f>
@@ -8314,7 +8256,7 @@
         <v/>
       </c>
       <c r="H28" s="17">
-        <f>($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I28" s="17">
@@ -8328,7 +8270,7 @@
     </row>
     <row r="29">
       <c r="A29" s="19" t="n">
-        <v>36.48</v>
+        <v>36.28</v>
       </c>
       <c r="B29" s="19">
         <f>A29-$B$10</f>
@@ -8355,7 +8297,7 @@
         <v/>
       </c>
       <c r="H29" s="17">
-        <f>($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I29" s="17">
@@ -8369,7 +8311,7 @@
     </row>
     <row r="30">
       <c r="A30" s="19" t="n">
-        <v>36.58</v>
+        <v>36.38</v>
       </c>
       <c r="B30" s="19">
         <f>A30-$B$10</f>
@@ -8396,7 +8338,7 @@
         <v/>
       </c>
       <c r="H30" s="17">
-        <f>($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I30" s="17">
@@ -8410,7 +8352,7 @@
     </row>
     <row r="31">
       <c r="A31" s="19" t="n">
-        <v>36.68</v>
+        <v>36.48</v>
       </c>
       <c r="B31" s="19">
         <f>A31-$B$10</f>
@@ -8437,7 +8379,7 @@
         <v/>
       </c>
       <c r="H31" s="17">
-        <f>($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I31" s="17">
@@ -8451,7 +8393,7 @@
     </row>
     <row r="32">
       <c r="A32" s="19" t="n">
-        <v>36.78</v>
+        <v>36.58</v>
       </c>
       <c r="B32" s="19">
         <f>A32-$B$10</f>
@@ -8478,7 +8420,7 @@
         <v/>
       </c>
       <c r="H32" s="17">
-        <f>($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I32" s="17">
@@ -8492,7 +8434,7 @@
     </row>
     <row r="33">
       <c r="A33" s="19" t="n">
-        <v>36.88</v>
+        <v>36.68</v>
       </c>
       <c r="B33" s="19">
         <f>A33-$B$10</f>
@@ -8519,7 +8461,7 @@
         <v/>
       </c>
       <c r="H33" s="17">
-        <f>($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I33" s="17">
@@ -8533,7 +8475,7 @@
     </row>
     <row r="34">
       <c r="A34" s="19" t="n">
-        <v>36.98</v>
+        <v>36.78</v>
       </c>
       <c r="B34" s="19">
         <f>A34-$B$10</f>
@@ -8560,7 +8502,7 @@
         <v/>
       </c>
       <c r="H34" s="17">
-        <f>($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I34" s="17">
@@ -8574,7 +8516,7 @@
     </row>
     <row r="35">
       <c r="A35" s="19" t="n">
-        <v>37.08</v>
+        <v>36.88</v>
       </c>
       <c r="B35" s="19">
         <f>A35-$B$10</f>
@@ -8601,7 +8543,7 @@
         <v/>
       </c>
       <c r="H35" s="17">
-        <f>($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I35" s="17">
@@ -8615,7 +8557,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="n">
-        <v>37.18</v>
+        <v>36.98</v>
       </c>
       <c r="B36" s="19">
         <f>A36-$B$10</f>
@@ -8642,7 +8584,7 @@
         <v/>
       </c>
       <c r="H36" s="17">
-        <f>($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I36" s="17">
@@ -8656,7 +8598,7 @@
     </row>
     <row r="37">
       <c r="A37" s="19" t="n">
-        <v>37.28</v>
+        <v>37.08</v>
       </c>
       <c r="B37" s="19">
         <f>A37-$B$10</f>
@@ -8683,7 +8625,7 @@
         <v/>
       </c>
       <c r="H37" s="17">
-        <f>($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I37" s="17">
@@ -8697,7 +8639,7 @@
     </row>
     <row r="38">
       <c r="A38" s="19" t="n">
-        <v>37.38</v>
+        <v>37.18</v>
       </c>
       <c r="B38" s="19">
         <f>A38-$B$10</f>
@@ -8724,7 +8666,7 @@
         <v/>
       </c>
       <c r="H38" s="17">
-        <f>($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I38" s="17">
@@ -8738,7 +8680,7 @@
     </row>
     <row r="39">
       <c r="A39" s="19" t="n">
-        <v>37.48</v>
+        <v>37.28</v>
       </c>
       <c r="B39" s="19">
         <f>A39-$B$10</f>
@@ -8765,7 +8707,7 @@
         <v/>
       </c>
       <c r="H39" s="17">
-        <f>($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I39" s="17">
@@ -8779,7 +8721,7 @@
     </row>
     <row r="40">
       <c r="A40" s="19" t="n">
-        <v>37.58</v>
+        <v>37.38</v>
       </c>
       <c r="B40" s="19">
         <f>A40-$B$10</f>
@@ -8806,7 +8748,7 @@
         <v/>
       </c>
       <c r="H40" s="17">
-        <f>($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I40" s="17">
@@ -8820,7 +8762,7 @@
     </row>
     <row r="41">
       <c r="A41" s="19" t="n">
-        <v>37.68</v>
+        <v>37.48</v>
       </c>
       <c r="B41" s="19">
         <f>A41-$B$10</f>
@@ -8847,7 +8789,7 @@
         <v/>
       </c>
       <c r="H41" s="17">
-        <f>($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I41" s="17">
@@ -8861,7 +8803,7 @@
     </row>
     <row r="42">
       <c r="A42" s="19" t="n">
-        <v>37.78</v>
+        <v>37.58</v>
       </c>
       <c r="B42" s="19">
         <f>A42-$B$10</f>
@@ -8888,7 +8830,7 @@
         <v/>
       </c>
       <c r="H42" s="17">
-        <f>($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I42" s="17">
@@ -8902,7 +8844,7 @@
     </row>
     <row r="43">
       <c r="A43" s="19" t="n">
-        <v>37.88</v>
+        <v>37.68</v>
       </c>
       <c r="B43" s="19">
         <f>A43-$B$10</f>
@@ -8929,7 +8871,7 @@
         <v/>
       </c>
       <c r="H43" s="17">
-        <f>($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I43" s="17">
@@ -8943,7 +8885,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="n">
-        <v>37.98</v>
+        <v>37.78</v>
       </c>
       <c r="B44" s="19">
         <f>A44-$B$10</f>
@@ -8970,7 +8912,7 @@
         <v/>
       </c>
       <c r="H44" s="17">
-        <f>($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I44" s="17">
@@ -8984,7 +8926,7 @@
     </row>
     <row r="45">
       <c r="A45" s="19" t="n">
-        <v>38.08</v>
+        <v>37.88</v>
       </c>
       <c r="B45" s="19">
         <f>A45-$B$10</f>
@@ -9011,7 +8953,7 @@
         <v/>
       </c>
       <c r="H45" s="17">
-        <f>($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I45" s="17">
@@ -9025,7 +8967,7 @@
     </row>
     <row r="46">
       <c r="A46" s="19" t="n">
-        <v>38.18</v>
+        <v>37.98</v>
       </c>
       <c r="B46" s="19">
         <f>A46-$B$10</f>
@@ -9052,7 +8994,7 @@
         <v/>
       </c>
       <c r="H46" s="17">
-        <f>($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I46" s="17">
@@ -9066,7 +9008,7 @@
     </row>
     <row r="47">
       <c r="A47" s="19" t="n">
-        <v>38.28</v>
+        <v>38.08</v>
       </c>
       <c r="B47" s="19">
         <f>A47-$B$10</f>
@@ -9093,7 +9035,7 @@
         <v/>
       </c>
       <c r="H47" s="17">
-        <f>($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I47" s="17">
@@ -9107,7 +9049,7 @@
     </row>
     <row r="48">
       <c r="A48" s="19" t="n">
-        <v>38.38</v>
+        <v>38.18</v>
       </c>
       <c r="B48" s="19">
         <f>A48-$B$10</f>
@@ -9134,7 +9076,7 @@
         <v/>
       </c>
       <c r="H48" s="17">
-        <f>($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I48" s="17">
@@ -9148,7 +9090,7 @@
     </row>
     <row r="49">
       <c r="A49" s="19" t="n">
-        <v>38.48</v>
+        <v>38.28</v>
       </c>
       <c r="B49" s="19">
         <f>A49-$B$10</f>
@@ -9175,7 +9117,7 @@
         <v/>
       </c>
       <c r="H49" s="17">
-        <f>($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I49" s="17">
@@ -9189,7 +9131,7 @@
     </row>
     <row r="50">
       <c r="A50" s="19" t="n">
-        <v>38.58</v>
+        <v>38.38</v>
       </c>
       <c r="B50" s="19">
         <f>A50-$B$10</f>
@@ -9216,7 +9158,7 @@
         <v/>
       </c>
       <c r="H50" s="17">
-        <f>($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I50" s="17">
@@ -9230,7 +9172,7 @@
     </row>
     <row r="51">
       <c r="A51" s="19" t="n">
-        <v>38.68</v>
+        <v>38.48</v>
       </c>
       <c r="B51" s="19">
         <f>A51-$B$10</f>
@@ -9257,7 +9199,7 @@
         <v/>
       </c>
       <c r="H51" s="17">
-        <f>($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I51" s="17">
@@ -9271,7 +9213,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="n">
-        <v>38.78</v>
+        <v>38.58</v>
       </c>
       <c r="B52" s="19">
         <f>A52-$B$10</f>
@@ -9298,7 +9240,7 @@
         <v/>
       </c>
       <c r="H52" s="17">
-        <f>($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I52" s="17">
@@ -9312,7 +9254,7 @@
     </row>
     <row r="53">
       <c r="A53" s="19" t="n">
-        <v>38.88</v>
+        <v>38.68</v>
       </c>
       <c r="B53" s="19">
         <f>A53-$B$10</f>
@@ -9339,7 +9281,7 @@
         <v/>
       </c>
       <c r="H53" s="17">
-        <f>($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I53" s="17">
@@ -9353,7 +9295,7 @@
     </row>
     <row r="54">
       <c r="A54" s="19" t="n">
-        <v>38.98</v>
+        <v>38.78</v>
       </c>
       <c r="B54" s="19">
         <f>A54-$B$10</f>
@@ -9380,7 +9322,7 @@
         <v/>
       </c>
       <c r="H54" s="17">
-        <f>($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I54" s="17">
@@ -9394,7 +9336,7 @@
     </row>
     <row r="55">
       <c r="A55" s="19" t="n">
-        <v>39.08</v>
+        <v>38.88</v>
       </c>
       <c r="B55" s="19">
         <f>A55-$B$10</f>
@@ -9421,7 +9363,7 @@
         <v/>
       </c>
       <c r="H55" s="17">
-        <f>($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I55" s="17">
@@ -9435,7 +9377,7 @@
     </row>
     <row r="56">
       <c r="A56" s="19" t="n">
-        <v>39.18</v>
+        <v>38.98</v>
       </c>
       <c r="B56" s="19">
         <f>A56-$B$10</f>
@@ -9462,7 +9404,7 @@
         <v/>
       </c>
       <c r="H56" s="17">
-        <f>($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I56" s="17">
@@ -9476,7 +9418,7 @@
     </row>
     <row r="57">
       <c r="A57" s="19" t="n">
-        <v>39.28</v>
+        <v>39.08</v>
       </c>
       <c r="B57" s="19">
         <f>A57-$B$10</f>
@@ -9503,7 +9445,7 @@
         <v/>
       </c>
       <c r="H57" s="17">
-        <f>($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I57" s="17">
@@ -9517,7 +9459,7 @@
     </row>
     <row r="58">
       <c r="A58" s="19" t="n">
-        <v>39.38</v>
+        <v>39.18</v>
       </c>
       <c r="B58" s="19">
         <f>A58-$B$10</f>
@@ -9544,7 +9486,7 @@
         <v/>
       </c>
       <c r="H58" s="17">
-        <f>($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I58" s="17">
@@ -9558,7 +9500,7 @@
     </row>
     <row r="59">
       <c r="A59" s="19" t="n">
-        <v>39.48</v>
+        <v>39.28</v>
       </c>
       <c r="B59" s="19">
         <f>A59-$B$10</f>
@@ -9585,7 +9527,7 @@
         <v/>
       </c>
       <c r="H59" s="17">
-        <f>($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I59" s="17">
@@ -9599,7 +9541,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="n">
-        <v>39.58</v>
+        <v>39.38</v>
       </c>
       <c r="B60" s="19">
         <f>A60-$B$10</f>
@@ -9626,7 +9568,7 @@
         <v/>
       </c>
       <c r="H60" s="17">
-        <f>($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I60" s="17">
@@ -9640,7 +9582,7 @@
     </row>
     <row r="61">
       <c r="A61" s="19" t="n">
-        <v>39.68</v>
+        <v>39.48</v>
       </c>
       <c r="B61" s="19">
         <f>A61-$B$10</f>
@@ -9667,7 +9609,7 @@
         <v/>
       </c>
       <c r="H61" s="17">
-        <f>($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I61" s="17">
@@ -9681,7 +9623,7 @@
     </row>
     <row r="62">
       <c r="A62" s="19" t="n">
-        <v>39.78</v>
+        <v>39.58</v>
       </c>
       <c r="B62" s="19">
         <f>A62-$B$10</f>
@@ -9708,7 +9650,7 @@
         <v/>
       </c>
       <c r="H62" s="17">
-        <f>($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I62" s="17">
@@ -9722,7 +9664,7 @@
     </row>
     <row r="63">
       <c r="A63" s="19" t="n">
-        <v>39.88</v>
+        <v>39.68</v>
       </c>
       <c r="B63" s="19">
         <f>A63-$B$10</f>
@@ -9749,7 +9691,7 @@
         <v/>
       </c>
       <c r="H63" s="17">
-        <f>($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I63" s="17">
@@ -9763,7 +9705,7 @@
     </row>
     <row r="64">
       <c r="A64" s="19" t="n">
-        <v>39.98</v>
+        <v>39.78</v>
       </c>
       <c r="B64" s="19">
         <f>A64-$B$10</f>
@@ -9790,7 +9732,7 @@
         <v/>
       </c>
       <c r="H64" s="17">
-        <f>($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I64" s="17">
@@ -9799,6 +9741,88 @@
       </c>
       <c r="J64" s="8">
         <f>H64+I64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="B65" s="19">
+        <f>A65-$B$10</f>
+        <v/>
+      </c>
+      <c r="C65" s="19">
+        <f>MAX(0,A65-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D65" s="17">
+        <f>IF(C65&lt;=0,0,($B$5+$B$7*C65)*C65)</f>
+        <v/>
+      </c>
+      <c r="E65" s="16">
+        <f>D65*$B$9</f>
+        <v/>
+      </c>
+      <c r="F65" s="16">
+        <f>IF(A65&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A65&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1))+(A65-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G65" s="14">
+        <f>E65+F65</f>
+        <v/>
+      </c>
+      <c r="H65" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B65&lt;=0,0,IF(B65&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1))+(B65-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I65" s="17">
+        <f>IF(C65&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D65*IF(($B$5+2*C65*SQRT(1+$B$7^2))&lt;=0,0,((D65/($B$5+2*C65*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J65" s="8">
+        <f>H65+I65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="B66" s="19">
+        <f>A66-$B$10</f>
+        <v/>
+      </c>
+      <c r="C66" s="19">
+        <f>MAX(0,A66-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D66" s="17">
+        <f>IF(C66&lt;=0,0,($B$5+$B$7*C66)*C66)</f>
+        <v/>
+      </c>
+      <c r="E66" s="16">
+        <f>D66*$B$9</f>
+        <v/>
+      </c>
+      <c r="F66" s="16">
+        <f>IF(A66&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A66&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1))+(A66-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G66" s="14">
+        <f>E66+F66</f>
+        <v/>
+      </c>
+      <c r="H66" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B66&lt;=0,0,IF(B66&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1))+(B66-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I66" s="17">
+        <f>IF(C66&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D66*IF(($B$5+2*C66*SQRT(1+$B$7^2))&lt;=0,0,((D66/($B$5+2*C66*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J66" s="8">
+        <f>H66+I66</f>
         <v/>
       </c>
     </row>
@@ -10035,11 +10059,11 @@
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>IF(F15&lt;=INDEX(Compose_100pct!$G$13:$G$64,1),INDEX(Compose_100pct!$A$13:$A$64,1),IF(F15&gt;=INDEX(Compose_100pct!$G$13:$G$64,ROWS(Compose_100pct!$G$13:$G$64)),INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$A$13:$A$64,MATCH(F15,Compose_100pct!$G$13:$G$64,1))+(F15-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F15,Compose_100pct!$G$13:$G$64,1)))/(INDEX(Compose_100pct!$G$13:$G$64,MATCH(F15,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F15,Compose_100pct!$G$13:$G$64,1)))*(INDEX(Compose_100pct!$A$13:$A$64,MATCH(F15,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(F15,Compose_100pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F15&lt;=INDEX(Compose_100pct!$G$15:$G$66,1),INDEX(Compose_100pct!$A$15:$A$66,1),IF(F15&gt;=INDEX(Compose_100pct!$G$15:$G$66,ROWS(Compose_100pct!$G$15:$G$66)),INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$A$15:$A$66,MATCH(F15,Compose_100pct!$G$15:$G$66,1))+(F15-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F15,Compose_100pct!$G$15:$G$66,1)))/(INDEX(Compose_100pct!$G$15:$G$66,MATCH(F15,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F15,Compose_100pct!$G$15:$G$66,1)))*(INDEX(Compose_100pct!$A$15:$A$66,MATCH(F15,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(F15,Compose_100pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$J$13:$J$64,1),IF(C16&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$J$13:$J$64,ROWS(Compose_100pct!$J$13:$J$64)),INDEX(Compose_100pct!$J$13:$J$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1))+(C16-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$J$13:$J$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$J$13:$J$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$J$15:$J$66,1),IF(C16&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$J$15:$J$66,ROWS(Compose_100pct!$J$15:$J$66)),INDEX(Compose_100pct!$J$15:$J$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1))+(C16-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$J$15:$J$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$J$15:$J$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E16" s="16">
@@ -10051,11 +10075,11 @@
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$H$13:$H$64,1),IF(C16&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$H$13:$H$64,ROWS(Compose_100pct!$H$13:$H$64)),INDEX(Compose_100pct!$H$13:$H$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1))+(C16-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$H$13:$H$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$H$13:$H$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$H$15:$H$66,1),IF(C16&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$H$15:$H$66,ROWS(Compose_100pct!$H$15:$H$66)),INDEX(Compose_100pct!$H$15:$H$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1))+(C16-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$H$15:$H$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$H$15:$H$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$I$13:$I$64,1),IF(C16&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$I$13:$I$64,ROWS(Compose_100pct!$I$13:$I$64)),INDEX(Compose_100pct!$I$13:$I$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1))+(C16-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$I$13:$I$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$I$13:$I$64,MATCH(C16,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$I$15:$I$66,1),IF(C16&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$I$15:$I$66,ROWS(Compose_100pct!$I$15:$I$66)),INDEX(Compose_100pct!$I$15:$I$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1))+(C16-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$I$15:$I$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$I$15:$I$66,MATCH(C16,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I16" s="21">
@@ -10073,11 +10097,11 @@
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>IF(F16&lt;=INDEX(Compose_100pct!$G$13:$G$64,1),INDEX(Compose_100pct!$A$13:$A$64,1),IF(F16&gt;=INDEX(Compose_100pct!$G$13:$G$64,ROWS(Compose_100pct!$G$13:$G$64)),INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$A$13:$A$64,MATCH(F16,Compose_100pct!$G$13:$G$64,1))+(F16-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F16,Compose_100pct!$G$13:$G$64,1)))/(INDEX(Compose_100pct!$G$13:$G$64,MATCH(F16,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F16,Compose_100pct!$G$13:$G$64,1)))*(INDEX(Compose_100pct!$A$13:$A$64,MATCH(F16,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(F16,Compose_100pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F16&lt;=INDEX(Compose_100pct!$G$15:$G$66,1),INDEX(Compose_100pct!$A$15:$A$66,1),IF(F16&gt;=INDEX(Compose_100pct!$G$15:$G$66,ROWS(Compose_100pct!$G$15:$G$66)),INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$A$15:$A$66,MATCH(F16,Compose_100pct!$G$15:$G$66,1))+(F16-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F16,Compose_100pct!$G$15:$G$66,1)))/(INDEX(Compose_100pct!$G$15:$G$66,MATCH(F16,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F16,Compose_100pct!$G$15:$G$66,1)))*(INDEX(Compose_100pct!$A$15:$A$66,MATCH(F16,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(F16,Compose_100pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$J$13:$J$64,1),IF(C17&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$J$13:$J$64,ROWS(Compose_100pct!$J$13:$J$64)),INDEX(Compose_100pct!$J$13:$J$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1))+(C17-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$J$13:$J$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$J$13:$J$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$J$15:$J$66,1),IF(C17&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$J$15:$J$66,ROWS(Compose_100pct!$J$15:$J$66)),INDEX(Compose_100pct!$J$15:$J$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1))+(C17-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$J$15:$J$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$J$15:$J$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E17" s="16">
@@ -10089,11 +10113,11 @@
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$H$13:$H$64,1),IF(C17&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$H$13:$H$64,ROWS(Compose_100pct!$H$13:$H$64)),INDEX(Compose_100pct!$H$13:$H$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1))+(C17-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$H$13:$H$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$H$13:$H$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$H$15:$H$66,1),IF(C17&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$H$15:$H$66,ROWS(Compose_100pct!$H$15:$H$66)),INDEX(Compose_100pct!$H$15:$H$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1))+(C17-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$H$15:$H$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$H$15:$H$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$I$13:$I$64,1),IF(C17&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$I$13:$I$64,ROWS(Compose_100pct!$I$13:$I$64)),INDEX(Compose_100pct!$I$13:$I$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1))+(C17-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$I$13:$I$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$I$13:$I$64,MATCH(C17,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$I$15:$I$66,1),IF(C17&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$I$15:$I$66,ROWS(Compose_100pct!$I$15:$I$66)),INDEX(Compose_100pct!$I$15:$I$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1))+(C17-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$I$15:$I$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$I$15:$I$66,MATCH(C17,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I17" s="21">
@@ -10111,11 +10135,11 @@
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>IF(F17&lt;=INDEX(Compose_100pct!$G$13:$G$64,1),INDEX(Compose_100pct!$A$13:$A$64,1),IF(F17&gt;=INDEX(Compose_100pct!$G$13:$G$64,ROWS(Compose_100pct!$G$13:$G$64)),INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$A$13:$A$64,MATCH(F17,Compose_100pct!$G$13:$G$64,1))+(F17-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F17,Compose_100pct!$G$13:$G$64,1)))/(INDEX(Compose_100pct!$G$13:$G$64,MATCH(F17,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F17,Compose_100pct!$G$13:$G$64,1)))*(INDEX(Compose_100pct!$A$13:$A$64,MATCH(F17,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(F17,Compose_100pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F17&lt;=INDEX(Compose_100pct!$G$15:$G$66,1),INDEX(Compose_100pct!$A$15:$A$66,1),IF(F17&gt;=INDEX(Compose_100pct!$G$15:$G$66,ROWS(Compose_100pct!$G$15:$G$66)),INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$A$15:$A$66,MATCH(F17,Compose_100pct!$G$15:$G$66,1))+(F17-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F17,Compose_100pct!$G$15:$G$66,1)))/(INDEX(Compose_100pct!$G$15:$G$66,MATCH(F17,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F17,Compose_100pct!$G$15:$G$66,1)))*(INDEX(Compose_100pct!$A$15:$A$66,MATCH(F17,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(F17,Compose_100pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$J$13:$J$64,1),IF(C18&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$J$13:$J$64,ROWS(Compose_100pct!$J$13:$J$64)),INDEX(Compose_100pct!$J$13:$J$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1))+(C18-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$J$13:$J$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$J$13:$J$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$J$15:$J$66,1),IF(C18&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$J$15:$J$66,ROWS(Compose_100pct!$J$15:$J$66)),INDEX(Compose_100pct!$J$15:$J$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1))+(C18-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$J$15:$J$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$J$15:$J$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E18" s="16">
@@ -10127,11 +10151,11 @@
         <v/>
       </c>
       <c r="G18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$H$13:$H$64,1),IF(C18&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$H$13:$H$64,ROWS(Compose_100pct!$H$13:$H$64)),INDEX(Compose_100pct!$H$13:$H$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1))+(C18-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$H$13:$H$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$H$13:$H$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$H$15:$H$66,1),IF(C18&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$H$15:$H$66,ROWS(Compose_100pct!$H$15:$H$66)),INDEX(Compose_100pct!$H$15:$H$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1))+(C18-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$H$15:$H$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$H$15:$H$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$I$13:$I$64,1),IF(C18&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$I$13:$I$64,ROWS(Compose_100pct!$I$13:$I$64)),INDEX(Compose_100pct!$I$13:$I$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1))+(C18-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$I$13:$I$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$I$13:$I$64,MATCH(C18,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$I$15:$I$66,1),IF(C18&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$I$15:$I$66,ROWS(Compose_100pct!$I$15:$I$66)),INDEX(Compose_100pct!$I$15:$I$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1))+(C18-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$I$15:$I$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$I$15:$I$66,MATCH(C18,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I18" s="21">
@@ -10149,11 +10173,11 @@
         <v/>
       </c>
       <c r="C19" s="17">
-        <f>IF(F18&lt;=INDEX(Compose_100pct!$G$13:$G$64,1),INDEX(Compose_100pct!$A$13:$A$64,1),IF(F18&gt;=INDEX(Compose_100pct!$G$13:$G$64,ROWS(Compose_100pct!$G$13:$G$64)),INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$A$13:$A$64,MATCH(F18,Compose_100pct!$G$13:$G$64,1))+(F18-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F18,Compose_100pct!$G$13:$G$64,1)))/(INDEX(Compose_100pct!$G$13:$G$64,MATCH(F18,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F18,Compose_100pct!$G$13:$G$64,1)))*(INDEX(Compose_100pct!$A$13:$A$64,MATCH(F18,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(F18,Compose_100pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F18&lt;=INDEX(Compose_100pct!$G$15:$G$66,1),INDEX(Compose_100pct!$A$15:$A$66,1),IF(F18&gt;=INDEX(Compose_100pct!$G$15:$G$66,ROWS(Compose_100pct!$G$15:$G$66)),INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$A$15:$A$66,MATCH(F18,Compose_100pct!$G$15:$G$66,1))+(F18-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F18,Compose_100pct!$G$15:$G$66,1)))/(INDEX(Compose_100pct!$G$15:$G$66,MATCH(F18,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F18,Compose_100pct!$G$15:$G$66,1)))*(INDEX(Compose_100pct!$A$15:$A$66,MATCH(F18,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(F18,Compose_100pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$J$13:$J$64,1),IF(C19&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$J$13:$J$64,ROWS(Compose_100pct!$J$13:$J$64)),INDEX(Compose_100pct!$J$13:$J$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1))+(C19-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$J$13:$J$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$J$13:$J$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$J$15:$J$66,1),IF(C19&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$J$15:$J$66,ROWS(Compose_100pct!$J$15:$J$66)),INDEX(Compose_100pct!$J$15:$J$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1))+(C19-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$J$15:$J$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$J$15:$J$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E19" s="16">
@@ -10165,11 +10189,11 @@
         <v/>
       </c>
       <c r="G19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$H$13:$H$64,1),IF(C19&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$H$13:$H$64,ROWS(Compose_100pct!$H$13:$H$64)),INDEX(Compose_100pct!$H$13:$H$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1))+(C19-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$H$13:$H$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$H$13:$H$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$H$15:$H$66,1),IF(C19&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$H$15:$H$66,ROWS(Compose_100pct!$H$15:$H$66)),INDEX(Compose_100pct!$H$15:$H$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1))+(C19-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$H$15:$H$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$H$15:$H$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$I$13:$I$64,1),IF(C19&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$I$13:$I$64,ROWS(Compose_100pct!$I$13:$I$64)),INDEX(Compose_100pct!$I$13:$I$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1))+(C19-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$I$13:$I$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$I$13:$I$64,MATCH(C19,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$I$15:$I$66,1),IF(C19&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$I$15:$I$66,ROWS(Compose_100pct!$I$15:$I$66)),INDEX(Compose_100pct!$I$15:$I$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1))+(C19-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$I$15:$I$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$I$15:$I$66,MATCH(C19,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I19" s="21">
@@ -10187,11 +10211,11 @@
         <v/>
       </c>
       <c r="C20" s="17">
-        <f>IF(F19&lt;=INDEX(Compose_100pct!$G$13:$G$64,1),INDEX(Compose_100pct!$A$13:$A$64,1),IF(F19&gt;=INDEX(Compose_100pct!$G$13:$G$64,ROWS(Compose_100pct!$G$13:$G$64)),INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$A$13:$A$64,MATCH(F19,Compose_100pct!$G$13:$G$64,1))+(F19-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F19,Compose_100pct!$G$13:$G$64,1)))/(INDEX(Compose_100pct!$G$13:$G$64,MATCH(F19,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F19,Compose_100pct!$G$13:$G$64,1)))*(INDEX(Compose_100pct!$A$13:$A$64,MATCH(F19,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(F19,Compose_100pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F19&lt;=INDEX(Compose_100pct!$G$15:$G$66,1),INDEX(Compose_100pct!$A$15:$A$66,1),IF(F19&gt;=INDEX(Compose_100pct!$G$15:$G$66,ROWS(Compose_100pct!$G$15:$G$66)),INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$A$15:$A$66,MATCH(F19,Compose_100pct!$G$15:$G$66,1))+(F19-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F19,Compose_100pct!$G$15:$G$66,1)))/(INDEX(Compose_100pct!$G$15:$G$66,MATCH(F19,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F19,Compose_100pct!$G$15:$G$66,1)))*(INDEX(Compose_100pct!$A$15:$A$66,MATCH(F19,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(F19,Compose_100pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D20" s="17">
-        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$J$13:$J$64,1),IF(C20&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$J$13:$J$64,ROWS(Compose_100pct!$J$13:$J$64)),INDEX(Compose_100pct!$J$13:$J$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1))+(C20-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$J$13:$J$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$J$13:$J$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$J$15:$J$66,1),IF(C20&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$J$15:$J$66,ROWS(Compose_100pct!$J$15:$J$66)),INDEX(Compose_100pct!$J$15:$J$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1))+(C20-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$J$15:$J$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$J$15:$J$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E20" s="16">
@@ -10203,11 +10227,11 @@
         <v/>
       </c>
       <c r="G20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$H$13:$H$64,1),IF(C20&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$H$13:$H$64,ROWS(Compose_100pct!$H$13:$H$64)),INDEX(Compose_100pct!$H$13:$H$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1))+(C20-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$H$13:$H$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$H$13:$H$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$H$15:$H$66,1),IF(C20&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$H$15:$H$66,ROWS(Compose_100pct!$H$15:$H$66)),INDEX(Compose_100pct!$H$15:$H$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1))+(C20-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$H$15:$H$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$H$15:$H$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$I$13:$I$64,1),IF(C20&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$I$13:$I$64,ROWS(Compose_100pct!$I$13:$I$64)),INDEX(Compose_100pct!$I$13:$I$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1))+(C20-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$I$13:$I$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$I$13:$I$64,MATCH(C20,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$I$15:$I$66,1),IF(C20&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$I$15:$I$66,ROWS(Compose_100pct!$I$15:$I$66)),INDEX(Compose_100pct!$I$15:$I$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1))+(C20-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$I$15:$I$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$I$15:$I$66,MATCH(C20,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I20" s="21">
@@ -10225,11 +10249,11 @@
         <v/>
       </c>
       <c r="C21" s="17">
-        <f>IF(F20&lt;=INDEX(Compose_100pct!$G$13:$G$64,1),INDEX(Compose_100pct!$A$13:$A$64,1),IF(F20&gt;=INDEX(Compose_100pct!$G$13:$G$64,ROWS(Compose_100pct!$G$13:$G$64)),INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$A$13:$A$64,MATCH(F20,Compose_100pct!$G$13:$G$64,1))+(F20-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F20,Compose_100pct!$G$13:$G$64,1)))/(INDEX(Compose_100pct!$G$13:$G$64,MATCH(F20,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F20,Compose_100pct!$G$13:$G$64,1)))*(INDEX(Compose_100pct!$A$13:$A$64,MATCH(F20,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(F20,Compose_100pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F20&lt;=INDEX(Compose_100pct!$G$15:$G$66,1),INDEX(Compose_100pct!$A$15:$A$66,1),IF(F20&gt;=INDEX(Compose_100pct!$G$15:$G$66,ROWS(Compose_100pct!$G$15:$G$66)),INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$A$15:$A$66,MATCH(F20,Compose_100pct!$G$15:$G$66,1))+(F20-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F20,Compose_100pct!$G$15:$G$66,1)))/(INDEX(Compose_100pct!$G$15:$G$66,MATCH(F20,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F20,Compose_100pct!$G$15:$G$66,1)))*(INDEX(Compose_100pct!$A$15:$A$66,MATCH(F20,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(F20,Compose_100pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D21" s="17">
-        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$J$13:$J$64,1),IF(C21&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$J$13:$J$64,ROWS(Compose_100pct!$J$13:$J$64)),INDEX(Compose_100pct!$J$13:$J$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1))+(C21-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$J$13:$J$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$J$13:$J$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$J$15:$J$66,1),IF(C21&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$J$15:$J$66,ROWS(Compose_100pct!$J$15:$J$66)),INDEX(Compose_100pct!$J$15:$J$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1))+(C21-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$J$15:$J$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$J$15:$J$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E21" s="16">
@@ -10241,11 +10265,11 @@
         <v/>
       </c>
       <c r="G21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$H$13:$H$64,1),IF(C21&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$H$13:$H$64,ROWS(Compose_100pct!$H$13:$H$64)),INDEX(Compose_100pct!$H$13:$H$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1))+(C21-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$H$13:$H$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$H$13:$H$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$H$15:$H$66,1),IF(C21&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$H$15:$H$66,ROWS(Compose_100pct!$H$15:$H$66)),INDEX(Compose_100pct!$H$15:$H$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1))+(C21-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$H$15:$H$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$H$15:$H$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$I$13:$I$64,1),IF(C21&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$I$13:$I$64,ROWS(Compose_100pct!$I$13:$I$64)),INDEX(Compose_100pct!$I$13:$I$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1))+(C21-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$I$13:$I$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$I$13:$I$64,MATCH(C21,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$I$15:$I$66,1),IF(C21&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$I$15:$I$66,ROWS(Compose_100pct!$I$15:$I$66)),INDEX(Compose_100pct!$I$15:$I$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1))+(C21-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$I$15:$I$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$I$15:$I$66,MATCH(C21,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I21" s="21">
@@ -10263,11 +10287,11 @@
         <v/>
       </c>
       <c r="C22" s="17">
-        <f>IF(F21&lt;=INDEX(Compose_100pct!$G$13:$G$64,1),INDEX(Compose_100pct!$A$13:$A$64,1),IF(F21&gt;=INDEX(Compose_100pct!$G$13:$G$64,ROWS(Compose_100pct!$G$13:$G$64)),INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$A$13:$A$64,MATCH(F21,Compose_100pct!$G$13:$G$64,1))+(F21-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F21,Compose_100pct!$G$13:$G$64,1)))/(INDEX(Compose_100pct!$G$13:$G$64,MATCH(F21,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F21,Compose_100pct!$G$13:$G$64,1)))*(INDEX(Compose_100pct!$A$13:$A$64,MATCH(F21,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(F21,Compose_100pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F21&lt;=INDEX(Compose_100pct!$G$15:$G$66,1),INDEX(Compose_100pct!$A$15:$A$66,1),IF(F21&gt;=INDEX(Compose_100pct!$G$15:$G$66,ROWS(Compose_100pct!$G$15:$G$66)),INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$A$15:$A$66,MATCH(F21,Compose_100pct!$G$15:$G$66,1))+(F21-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F21,Compose_100pct!$G$15:$G$66,1)))/(INDEX(Compose_100pct!$G$15:$G$66,MATCH(F21,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F21,Compose_100pct!$G$15:$G$66,1)))*(INDEX(Compose_100pct!$A$15:$A$66,MATCH(F21,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(F21,Compose_100pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D22" s="17">
-        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$J$13:$J$64,1),IF(C22&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$J$13:$J$64,ROWS(Compose_100pct!$J$13:$J$64)),INDEX(Compose_100pct!$J$13:$J$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1))+(C22-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$J$13:$J$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$J$13:$J$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$J$15:$J$66,1),IF(C22&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$J$15:$J$66,ROWS(Compose_100pct!$J$15:$J$66)),INDEX(Compose_100pct!$J$15:$J$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1))+(C22-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$J$15:$J$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$J$15:$J$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E22" s="16">
@@ -10279,11 +10303,11 @@
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$H$13:$H$64,1),IF(C22&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$H$13:$H$64,ROWS(Compose_100pct!$H$13:$H$64)),INDEX(Compose_100pct!$H$13:$H$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1))+(C22-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$H$13:$H$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$H$13:$H$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$H$15:$H$66,1),IF(C22&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$H$15:$H$66,ROWS(Compose_100pct!$H$15:$H$66)),INDEX(Compose_100pct!$H$15:$H$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1))+(C22-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$H$15:$H$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$H$15:$H$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$I$13:$I$64,1),IF(C22&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$I$13:$I$64,ROWS(Compose_100pct!$I$13:$I$64)),INDEX(Compose_100pct!$I$13:$I$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1))+(C22-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$I$13:$I$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$I$13:$I$64,MATCH(C22,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$I$15:$I$66,1),IF(C22&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$I$15:$I$66,ROWS(Compose_100pct!$I$15:$I$66)),INDEX(Compose_100pct!$I$15:$I$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1))+(C22-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$I$15:$I$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$I$15:$I$66,MATCH(C22,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I22" s="21">
@@ -10301,11 +10325,11 @@
         <v/>
       </c>
       <c r="C23" s="17">
-        <f>IF(F22&lt;=INDEX(Compose_100pct!$G$13:$G$64,1),INDEX(Compose_100pct!$A$13:$A$64,1),IF(F22&gt;=INDEX(Compose_100pct!$G$13:$G$64,ROWS(Compose_100pct!$G$13:$G$64)),INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$A$13:$A$64,MATCH(F22,Compose_100pct!$G$13:$G$64,1))+(F22-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F22,Compose_100pct!$G$13:$G$64,1)))/(INDEX(Compose_100pct!$G$13:$G$64,MATCH(F22,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F22,Compose_100pct!$G$13:$G$64,1)))*(INDEX(Compose_100pct!$A$13:$A$64,MATCH(F22,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(F22,Compose_100pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F22&lt;=INDEX(Compose_100pct!$G$15:$G$66,1),INDEX(Compose_100pct!$A$15:$A$66,1),IF(F22&gt;=INDEX(Compose_100pct!$G$15:$G$66,ROWS(Compose_100pct!$G$15:$G$66)),INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$A$15:$A$66,MATCH(F22,Compose_100pct!$G$15:$G$66,1))+(F22-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F22,Compose_100pct!$G$15:$G$66,1)))/(INDEX(Compose_100pct!$G$15:$G$66,MATCH(F22,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F22,Compose_100pct!$G$15:$G$66,1)))*(INDEX(Compose_100pct!$A$15:$A$66,MATCH(F22,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(F22,Compose_100pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D23" s="17">
-        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$J$13:$J$64,1),IF(C23&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$J$13:$J$64,ROWS(Compose_100pct!$J$13:$J$64)),INDEX(Compose_100pct!$J$13:$J$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1))+(C23-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$J$13:$J$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$J$13:$J$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$J$15:$J$66,1),IF(C23&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$J$15:$J$66,ROWS(Compose_100pct!$J$15:$J$66)),INDEX(Compose_100pct!$J$15:$J$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1))+(C23-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$J$15:$J$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$J$15:$J$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E23" s="16">
@@ -10317,11 +10341,11 @@
         <v/>
       </c>
       <c r="G23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$H$13:$H$64,1),IF(C23&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$H$13:$H$64,ROWS(Compose_100pct!$H$13:$H$64)),INDEX(Compose_100pct!$H$13:$H$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1))+(C23-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$H$13:$H$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$H$13:$H$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$H$15:$H$66,1),IF(C23&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$H$15:$H$66,ROWS(Compose_100pct!$H$15:$H$66)),INDEX(Compose_100pct!$H$15:$H$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1))+(C23-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$H$15:$H$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$H$15:$H$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$I$13:$I$64,1),IF(C23&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$I$13:$I$64,ROWS(Compose_100pct!$I$13:$I$64)),INDEX(Compose_100pct!$I$13:$I$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1))+(C23-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$I$13:$I$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$I$13:$I$64,MATCH(C23,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$I$15:$I$66,1),IF(C23&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$I$15:$I$66,ROWS(Compose_100pct!$I$15:$I$66)),INDEX(Compose_100pct!$I$15:$I$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1))+(C23-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$I$15:$I$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$I$15:$I$66,MATCH(C23,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I23" s="21">
@@ -10339,11 +10363,11 @@
         <v/>
       </c>
       <c r="C24" s="17">
-        <f>IF(F23&lt;=INDEX(Compose_100pct!$G$13:$G$64,1),INDEX(Compose_100pct!$A$13:$A$64,1),IF(F23&gt;=INDEX(Compose_100pct!$G$13:$G$64,ROWS(Compose_100pct!$G$13:$G$64)),INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$A$13:$A$64,MATCH(F23,Compose_100pct!$G$13:$G$64,1))+(F23-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F23,Compose_100pct!$G$13:$G$64,1)))/(INDEX(Compose_100pct!$G$13:$G$64,MATCH(F23,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F23,Compose_100pct!$G$13:$G$64,1)))*(INDEX(Compose_100pct!$A$13:$A$64,MATCH(F23,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(F23,Compose_100pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F23&lt;=INDEX(Compose_100pct!$G$15:$G$66,1),INDEX(Compose_100pct!$A$15:$A$66,1),IF(F23&gt;=INDEX(Compose_100pct!$G$15:$G$66,ROWS(Compose_100pct!$G$15:$G$66)),INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$A$15:$A$66,MATCH(F23,Compose_100pct!$G$15:$G$66,1))+(F23-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F23,Compose_100pct!$G$15:$G$66,1)))/(INDEX(Compose_100pct!$G$15:$G$66,MATCH(F23,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F23,Compose_100pct!$G$15:$G$66,1)))*(INDEX(Compose_100pct!$A$15:$A$66,MATCH(F23,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(F23,Compose_100pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D24" s="17">
-        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$J$13:$J$64,1),IF(C24&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$J$13:$J$64,ROWS(Compose_100pct!$J$13:$J$64)),INDEX(Compose_100pct!$J$13:$J$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1))+(C24-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$J$13:$J$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$J$13:$J$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$J$15:$J$66,1),IF(C24&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$J$15:$J$66,ROWS(Compose_100pct!$J$15:$J$66)),INDEX(Compose_100pct!$J$15:$J$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1))+(C24-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$J$15:$J$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$J$15:$J$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E24" s="16">
@@ -10355,11 +10379,11 @@
         <v/>
       </c>
       <c r="G24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$H$13:$H$64,1),IF(C24&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$H$13:$H$64,ROWS(Compose_100pct!$H$13:$H$64)),INDEX(Compose_100pct!$H$13:$H$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1))+(C24-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$H$13:$H$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$H$13:$H$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$H$15:$H$66,1),IF(C24&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$H$15:$H$66,ROWS(Compose_100pct!$H$15:$H$66)),INDEX(Compose_100pct!$H$15:$H$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1))+(C24-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$H$15:$H$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$H$15:$H$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$I$13:$I$64,1),IF(C24&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$I$13:$I$64,ROWS(Compose_100pct!$I$13:$I$64)),INDEX(Compose_100pct!$I$13:$I$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1))+(C24-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$I$13:$I$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$I$13:$I$64,MATCH(C24,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$I$15:$I$66,1),IF(C24&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$I$15:$I$66,ROWS(Compose_100pct!$I$15:$I$66)),INDEX(Compose_100pct!$I$15:$I$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1))+(C24-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$I$15:$I$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$I$15:$I$66,MATCH(C24,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I24" s="21">
@@ -10377,11 +10401,11 @@
         <v/>
       </c>
       <c r="C25" s="17">
-        <f>IF(F24&lt;=INDEX(Compose_100pct!$G$13:$G$64,1),INDEX(Compose_100pct!$A$13:$A$64,1),IF(F24&gt;=INDEX(Compose_100pct!$G$13:$G$64,ROWS(Compose_100pct!$G$13:$G$64)),INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$A$13:$A$64,MATCH(F24,Compose_100pct!$G$13:$G$64,1))+(F24-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F24,Compose_100pct!$G$13:$G$64,1)))/(INDEX(Compose_100pct!$G$13:$G$64,MATCH(F24,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F24,Compose_100pct!$G$13:$G$64,1)))*(INDEX(Compose_100pct!$A$13:$A$64,MATCH(F24,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(F24,Compose_100pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F24&lt;=INDEX(Compose_100pct!$G$15:$G$66,1),INDEX(Compose_100pct!$A$15:$A$66,1),IF(F24&gt;=INDEX(Compose_100pct!$G$15:$G$66,ROWS(Compose_100pct!$G$15:$G$66)),INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$A$15:$A$66,MATCH(F24,Compose_100pct!$G$15:$G$66,1))+(F24-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F24,Compose_100pct!$G$15:$G$66,1)))/(INDEX(Compose_100pct!$G$15:$G$66,MATCH(F24,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F24,Compose_100pct!$G$15:$G$66,1)))*(INDEX(Compose_100pct!$A$15:$A$66,MATCH(F24,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(F24,Compose_100pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D25" s="17">
-        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$J$13:$J$64,1),IF(C25&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$J$13:$J$64,ROWS(Compose_100pct!$J$13:$J$64)),INDEX(Compose_100pct!$J$13:$J$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1))+(C25-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$J$13:$J$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$J$13:$J$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$J$15:$J$66,1),IF(C25&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$J$15:$J$66,ROWS(Compose_100pct!$J$15:$J$66)),INDEX(Compose_100pct!$J$15:$J$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1))+(C25-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$J$15:$J$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$J$15:$J$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E25" s="16">
@@ -10393,11 +10417,11 @@
         <v/>
       </c>
       <c r="G25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$H$13:$H$64,1),IF(C25&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$H$13:$H$64,ROWS(Compose_100pct!$H$13:$H$64)),INDEX(Compose_100pct!$H$13:$H$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1))+(C25-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$H$13:$H$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$H$13:$H$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$H$15:$H$66,1),IF(C25&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$H$15:$H$66,ROWS(Compose_100pct!$H$15:$H$66)),INDEX(Compose_100pct!$H$15:$H$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1))+(C25-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$H$15:$H$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$H$15:$H$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$I$13:$I$64,1),IF(C25&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$I$13:$I$64,ROWS(Compose_100pct!$I$13:$I$64)),INDEX(Compose_100pct!$I$13:$I$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1))+(C25-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$I$13:$I$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$I$13:$I$64,MATCH(C25,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$I$15:$I$66,1),IF(C25&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$I$15:$I$66,ROWS(Compose_100pct!$I$15:$I$66)),INDEX(Compose_100pct!$I$15:$I$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1))+(C25-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$I$15:$I$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$I$15:$I$66,MATCH(C25,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I25" s="21">
@@ -10415,11 +10439,11 @@
         <v/>
       </c>
       <c r="C26" s="17">
-        <f>IF(F25&lt;=INDEX(Compose_100pct!$G$13:$G$64,1),INDEX(Compose_100pct!$A$13:$A$64,1),IF(F25&gt;=INDEX(Compose_100pct!$G$13:$G$64,ROWS(Compose_100pct!$G$13:$G$64)),INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$A$13:$A$64,MATCH(F25,Compose_100pct!$G$13:$G$64,1))+(F25-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F25,Compose_100pct!$G$13:$G$64,1)))/(INDEX(Compose_100pct!$G$13:$G$64,MATCH(F25,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F25,Compose_100pct!$G$13:$G$64,1)))*(INDEX(Compose_100pct!$A$13:$A$64,MATCH(F25,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(F25,Compose_100pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F25&lt;=INDEX(Compose_100pct!$G$15:$G$66,1),INDEX(Compose_100pct!$A$15:$A$66,1),IF(F25&gt;=INDEX(Compose_100pct!$G$15:$G$66,ROWS(Compose_100pct!$G$15:$G$66)),INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$A$15:$A$66,MATCH(F25,Compose_100pct!$G$15:$G$66,1))+(F25-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F25,Compose_100pct!$G$15:$G$66,1)))/(INDEX(Compose_100pct!$G$15:$G$66,MATCH(F25,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F25,Compose_100pct!$G$15:$G$66,1)))*(INDEX(Compose_100pct!$A$15:$A$66,MATCH(F25,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(F25,Compose_100pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D26" s="17">
-        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$J$13:$J$64,1),IF(C26&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$J$13:$J$64,ROWS(Compose_100pct!$J$13:$J$64)),INDEX(Compose_100pct!$J$13:$J$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1))+(C26-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$J$13:$J$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$J$13:$J$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$J$15:$J$66,1),IF(C26&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$J$15:$J$66,ROWS(Compose_100pct!$J$15:$J$66)),INDEX(Compose_100pct!$J$15:$J$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1))+(C26-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$J$15:$J$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$J$15:$J$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E26" s="16">
@@ -10431,11 +10455,11 @@
         <v/>
       </c>
       <c r="G26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$H$13:$H$64,1),IF(C26&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$H$13:$H$64,ROWS(Compose_100pct!$H$13:$H$64)),INDEX(Compose_100pct!$H$13:$H$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1))+(C26-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$H$13:$H$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$H$13:$H$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$H$15:$H$66,1),IF(C26&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$H$15:$H$66,ROWS(Compose_100pct!$H$15:$H$66)),INDEX(Compose_100pct!$H$15:$H$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1))+(C26-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$H$15:$H$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$H$15:$H$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$I$13:$I$64,1),IF(C26&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$I$13:$I$64,ROWS(Compose_100pct!$I$13:$I$64)),INDEX(Compose_100pct!$I$13:$I$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1))+(C26-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$I$13:$I$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$I$13:$I$64,MATCH(C26,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$I$15:$I$66,1),IF(C26&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$I$15:$I$66,ROWS(Compose_100pct!$I$15:$I$66)),INDEX(Compose_100pct!$I$15:$I$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1))+(C26-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$I$15:$I$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$I$15:$I$66,MATCH(C26,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I26" s="21">
@@ -10453,11 +10477,11 @@
         <v/>
       </c>
       <c r="C27" s="17">
-        <f>IF(F26&lt;=INDEX(Compose_100pct!$G$13:$G$64,1),INDEX(Compose_100pct!$A$13:$A$64,1),IF(F26&gt;=INDEX(Compose_100pct!$G$13:$G$64,ROWS(Compose_100pct!$G$13:$G$64)),INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$A$13:$A$64,MATCH(F26,Compose_100pct!$G$13:$G$64,1))+(F26-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F26,Compose_100pct!$G$13:$G$64,1)))/(INDEX(Compose_100pct!$G$13:$G$64,MATCH(F26,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$G$13:$G$64,MATCH(F26,Compose_100pct!$G$13:$G$64,1)))*(INDEX(Compose_100pct!$A$13:$A$64,MATCH(F26,Compose_100pct!$G$13:$G$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(F26,Compose_100pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F26&lt;=INDEX(Compose_100pct!$G$15:$G$66,1),INDEX(Compose_100pct!$A$15:$A$66,1),IF(F26&gt;=INDEX(Compose_100pct!$G$15:$G$66,ROWS(Compose_100pct!$G$15:$G$66)),INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$A$15:$A$66,MATCH(F26,Compose_100pct!$G$15:$G$66,1))+(F26-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F26,Compose_100pct!$G$15:$G$66,1)))/(INDEX(Compose_100pct!$G$15:$G$66,MATCH(F26,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$G$15:$G$66,MATCH(F26,Compose_100pct!$G$15:$G$66,1)))*(INDEX(Compose_100pct!$A$15:$A$66,MATCH(F26,Compose_100pct!$G$15:$G$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(F26,Compose_100pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D27" s="17">
-        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$J$13:$J$64,1),IF(C27&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$J$13:$J$64,ROWS(Compose_100pct!$J$13:$J$64)),INDEX(Compose_100pct!$J$13:$J$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1))+(C27-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$J$13:$J$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$J$13:$J$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$J$15:$J$66,1),IF(C27&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$J$15:$J$66,ROWS(Compose_100pct!$J$15:$J$66)),INDEX(Compose_100pct!$J$15:$J$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1))+(C27-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$J$15:$J$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$J$15:$J$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E27" s="16">
@@ -10469,11 +10493,11 @@
         <v/>
       </c>
       <c r="G27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$H$13:$H$64,1),IF(C27&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$H$13:$H$64,ROWS(Compose_100pct!$H$13:$H$64)),INDEX(Compose_100pct!$H$13:$H$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1))+(C27-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$H$13:$H$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$H$13:$H$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$H$15:$H$66,1),IF(C27&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$H$15:$H$66,ROWS(Compose_100pct!$H$15:$H$66)),INDEX(Compose_100pct!$H$15:$H$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1))+(C27-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$H$15:$H$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$H$15:$H$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_100pct!$A$13:$A$64,1),INDEX(Compose_100pct!$I$13:$I$64,1),IF(C27&gt;=INDEX(Compose_100pct!$A$13:$A$64,ROWS(Compose_100pct!$A$13:$A$64)),INDEX(Compose_100pct!$I$13:$I$64,ROWS(Compose_100pct!$I$13:$I$64)),INDEX(Compose_100pct!$I$13:$I$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1))+(C27-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1)))/(INDEX(Compose_100pct!$A$13:$A$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$A$13:$A$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1)))*(INDEX(Compose_100pct!$I$13:$I$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1)+1)-INDEX(Compose_100pct!$I$13:$I$64,MATCH(C27,Compose_100pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_100pct!$A$15:$A$66,1),INDEX(Compose_100pct!$I$15:$I$66,1),IF(C27&gt;=INDEX(Compose_100pct!$A$15:$A$66,ROWS(Compose_100pct!$A$15:$A$66)),INDEX(Compose_100pct!$I$15:$I$66,ROWS(Compose_100pct!$I$15:$I$66)),INDEX(Compose_100pct!$I$15:$I$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1))+(C27-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1)))/(INDEX(Compose_100pct!$A$15:$A$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$A$15:$A$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1)))*(INDEX(Compose_100pct!$I$15:$I$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1)+1)-INDEX(Compose_100pct!$I$15:$I$66,MATCH(C27,Compose_100pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I27" s="21">
@@ -10496,7 +10520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10509,7 +10533,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colonnes = formules Excel. Crest / facteur pipe en jaune.</t>
+          <t>Colonnes = formules Excel. Crest / facteur pipe / plafond Q en jaune.</t>
         </is>
       </c>
     </row>
@@ -10602,142 +10626,72 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q_cap (m3/s)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>WSE</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>HW</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>y_ov</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>A_ditch</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>V_ditch</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>V_pond</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>V_total</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Q_1200</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>Q_overflow</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>Qout</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="B13" s="19">
-        <f>A13-$B$10</f>
-        <v/>
-      </c>
-      <c r="C13" s="19">
-        <f>MAX(0,A13-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D13" s="17">
-        <f>IF(C13&lt;=0,0,($B$5+$B$7*C13)*C13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>D13*$B$9</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>IF(A13&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A13&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1))+(A13-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G13" s="14">
-        <f>E13+F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
-        <f>($B$11)*(IF(B13&lt;=0,0,IF(B13&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))+(B13-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I13" s="17">
-        <f>IF(C13&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D13*IF(($B$5+2*C13*SQRT(1+$B$7^2))&lt;=0,0,((D13/($B$5+2*C13*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J13" s="8">
-        <f>H13+I13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="n">
-        <v>34.98</v>
-      </c>
-      <c r="B14" s="19">
-        <f>A14-$B$10</f>
-        <v/>
-      </c>
-      <c r="C14" s="19">
-        <f>MAX(0,A14-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D14" s="17">
-        <f>IF(C14&lt;=0,0,($B$5+$B$7*C14)*C14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>D14*$B$9</f>
-        <v/>
-      </c>
-      <c r="F14" s="16">
-        <f>IF(A14&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A14&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1))+(A14-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G14" s="14">
-        <f>E14+F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
-        <f>($B$11)*(IF(B14&lt;=0,0,IF(B14&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))+(B14-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
-        <f>IF(C14&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D14*IF(($B$5+2*C14*SQRT(1+$B$7^2))&lt;=0,0,((D14/($B$5+2*C14*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J14" s="8">
-        <f>H14+I14</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="n">
-        <v>35.08</v>
+        <v>34.88</v>
       </c>
       <c r="B15" s="19">
         <f>A15-$B$10</f>
@@ -10764,7 +10718,7 @@
         <v/>
       </c>
       <c r="H15" s="17">
-        <f>($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I15" s="17">
@@ -10778,7 +10732,7 @@
     </row>
     <row r="16">
       <c r="A16" s="19" t="n">
-        <v>35.18</v>
+        <v>34.98</v>
       </c>
       <c r="B16" s="19">
         <f>A16-$B$10</f>
@@ -10805,7 +10759,7 @@
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I16" s="17">
@@ -10819,7 +10773,7 @@
     </row>
     <row r="17">
       <c r="A17" s="19" t="n">
-        <v>35.28</v>
+        <v>35.08</v>
       </c>
       <c r="B17" s="19">
         <f>A17-$B$10</f>
@@ -10846,7 +10800,7 @@
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I17" s="17">
@@ -10860,7 +10814,7 @@
     </row>
     <row r="18">
       <c r="A18" s="19" t="n">
-        <v>35.38</v>
+        <v>35.18</v>
       </c>
       <c r="B18" s="19">
         <f>A18-$B$10</f>
@@ -10887,7 +10841,7 @@
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I18" s="17">
@@ -10901,7 +10855,7 @@
     </row>
     <row r="19">
       <c r="A19" s="19" t="n">
-        <v>35.48</v>
+        <v>35.28</v>
       </c>
       <c r="B19" s="19">
         <f>A19-$B$10</f>
@@ -10928,7 +10882,7 @@
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I19" s="17">
@@ -10942,7 +10896,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="n">
-        <v>35.58</v>
+        <v>35.38</v>
       </c>
       <c r="B20" s="19">
         <f>A20-$B$10</f>
@@ -10969,7 +10923,7 @@
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I20" s="17">
@@ -10983,7 +10937,7 @@
     </row>
     <row r="21">
       <c r="A21" s="19" t="n">
-        <v>35.68</v>
+        <v>35.48</v>
       </c>
       <c r="B21" s="19">
         <f>A21-$B$10</f>
@@ -11010,7 +10964,7 @@
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I21" s="17">
@@ -11024,7 +10978,7 @@
     </row>
     <row r="22">
       <c r="A22" s="19" t="n">
-        <v>35.78</v>
+        <v>35.58</v>
       </c>
       <c r="B22" s="19">
         <f>A22-$B$10</f>
@@ -11051,7 +11005,7 @@
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I22" s="17">
@@ -11065,7 +11019,7 @@
     </row>
     <row r="23">
       <c r="A23" s="19" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="B23" s="19">
         <f>A23-$B$10</f>
@@ -11092,7 +11046,7 @@
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I23" s="17">
@@ -11106,7 +11060,7 @@
     </row>
     <row r="24">
       <c r="A24" s="19" t="n">
-        <v>35.98</v>
+        <v>35.78</v>
       </c>
       <c r="B24" s="19">
         <f>A24-$B$10</f>
@@ -11133,7 +11087,7 @@
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I24" s="17">
@@ -11147,7 +11101,7 @@
     </row>
     <row r="25">
       <c r="A25" s="19" t="n">
-        <v>36.08</v>
+        <v>35.88</v>
       </c>
       <c r="B25" s="19">
         <f>A25-$B$10</f>
@@ -11174,7 +11128,7 @@
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I25" s="17">
@@ -11188,7 +11142,7 @@
     </row>
     <row r="26">
       <c r="A26" s="19" t="n">
-        <v>36.18</v>
+        <v>35.98</v>
       </c>
       <c r="B26" s="19">
         <f>A26-$B$10</f>
@@ -11215,7 +11169,7 @@
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I26" s="17">
@@ -11229,7 +11183,7 @@
     </row>
     <row r="27">
       <c r="A27" s="19" t="n">
-        <v>36.28</v>
+        <v>36.08</v>
       </c>
       <c r="B27" s="19">
         <f>A27-$B$10</f>
@@ -11256,7 +11210,7 @@
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I27" s="17">
@@ -11270,7 +11224,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="n">
-        <v>36.38</v>
+        <v>36.18</v>
       </c>
       <c r="B28" s="19">
         <f>A28-$B$10</f>
@@ -11297,7 +11251,7 @@
         <v/>
       </c>
       <c r="H28" s="17">
-        <f>($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I28" s="17">
@@ -11311,7 +11265,7 @@
     </row>
     <row r="29">
       <c r="A29" s="19" t="n">
-        <v>36.48</v>
+        <v>36.28</v>
       </c>
       <c r="B29" s="19">
         <f>A29-$B$10</f>
@@ -11338,7 +11292,7 @@
         <v/>
       </c>
       <c r="H29" s="17">
-        <f>($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I29" s="17">
@@ -11352,7 +11306,7 @@
     </row>
     <row r="30">
       <c r="A30" s="19" t="n">
-        <v>36.58</v>
+        <v>36.38</v>
       </c>
       <c r="B30" s="19">
         <f>A30-$B$10</f>
@@ -11379,7 +11333,7 @@
         <v/>
       </c>
       <c r="H30" s="17">
-        <f>($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I30" s="17">
@@ -11393,7 +11347,7 @@
     </row>
     <row r="31">
       <c r="A31" s="19" t="n">
-        <v>36.68</v>
+        <v>36.48</v>
       </c>
       <c r="B31" s="19">
         <f>A31-$B$10</f>
@@ -11420,7 +11374,7 @@
         <v/>
       </c>
       <c r="H31" s="17">
-        <f>($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I31" s="17">
@@ -11434,7 +11388,7 @@
     </row>
     <row r="32">
       <c r="A32" s="19" t="n">
-        <v>36.78</v>
+        <v>36.58</v>
       </c>
       <c r="B32" s="19">
         <f>A32-$B$10</f>
@@ -11461,7 +11415,7 @@
         <v/>
       </c>
       <c r="H32" s="17">
-        <f>($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I32" s="17">
@@ -11475,7 +11429,7 @@
     </row>
     <row r="33">
       <c r="A33" s="19" t="n">
-        <v>36.88</v>
+        <v>36.68</v>
       </c>
       <c r="B33" s="19">
         <f>A33-$B$10</f>
@@ -11502,7 +11456,7 @@
         <v/>
       </c>
       <c r="H33" s="17">
-        <f>($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I33" s="17">
@@ -11516,7 +11470,7 @@
     </row>
     <row r="34">
       <c r="A34" s="19" t="n">
-        <v>36.98</v>
+        <v>36.78</v>
       </c>
       <c r="B34" s="19">
         <f>A34-$B$10</f>
@@ -11543,7 +11497,7 @@
         <v/>
       </c>
       <c r="H34" s="17">
-        <f>($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I34" s="17">
@@ -11557,7 +11511,7 @@
     </row>
     <row r="35">
       <c r="A35" s="19" t="n">
-        <v>37.08</v>
+        <v>36.88</v>
       </c>
       <c r="B35" s="19">
         <f>A35-$B$10</f>
@@ -11584,7 +11538,7 @@
         <v/>
       </c>
       <c r="H35" s="17">
-        <f>($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I35" s="17">
@@ -11598,7 +11552,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="n">
-        <v>37.18</v>
+        <v>36.98</v>
       </c>
       <c r="B36" s="19">
         <f>A36-$B$10</f>
@@ -11625,7 +11579,7 @@
         <v/>
       </c>
       <c r="H36" s="17">
-        <f>($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I36" s="17">
@@ -11639,7 +11593,7 @@
     </row>
     <row r="37">
       <c r="A37" s="19" t="n">
-        <v>37.28</v>
+        <v>37.08</v>
       </c>
       <c r="B37" s="19">
         <f>A37-$B$10</f>
@@ -11666,7 +11620,7 @@
         <v/>
       </c>
       <c r="H37" s="17">
-        <f>($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I37" s="17">
@@ -11680,7 +11634,7 @@
     </row>
     <row r="38">
       <c r="A38" s="19" t="n">
-        <v>37.38</v>
+        <v>37.18</v>
       </c>
       <c r="B38" s="19">
         <f>A38-$B$10</f>
@@ -11707,7 +11661,7 @@
         <v/>
       </c>
       <c r="H38" s="17">
-        <f>($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I38" s="17">
@@ -11721,7 +11675,7 @@
     </row>
     <row r="39">
       <c r="A39" s="19" t="n">
-        <v>37.48</v>
+        <v>37.28</v>
       </c>
       <c r="B39" s="19">
         <f>A39-$B$10</f>
@@ -11748,7 +11702,7 @@
         <v/>
       </c>
       <c r="H39" s="17">
-        <f>($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I39" s="17">
@@ -11762,7 +11716,7 @@
     </row>
     <row r="40">
       <c r="A40" s="19" t="n">
-        <v>37.58</v>
+        <v>37.38</v>
       </c>
       <c r="B40" s="19">
         <f>A40-$B$10</f>
@@ -11789,7 +11743,7 @@
         <v/>
       </c>
       <c r="H40" s="17">
-        <f>($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I40" s="17">
@@ -11803,7 +11757,7 @@
     </row>
     <row r="41">
       <c r="A41" s="19" t="n">
-        <v>37.68</v>
+        <v>37.48</v>
       </c>
       <c r="B41" s="19">
         <f>A41-$B$10</f>
@@ -11830,7 +11784,7 @@
         <v/>
       </c>
       <c r="H41" s="17">
-        <f>($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I41" s="17">
@@ -11844,7 +11798,7 @@
     </row>
     <row r="42">
       <c r="A42" s="19" t="n">
-        <v>37.78</v>
+        <v>37.58</v>
       </c>
       <c r="B42" s="19">
         <f>A42-$B$10</f>
@@ -11871,7 +11825,7 @@
         <v/>
       </c>
       <c r="H42" s="17">
-        <f>($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I42" s="17">
@@ -11885,7 +11839,7 @@
     </row>
     <row r="43">
       <c r="A43" s="19" t="n">
-        <v>37.88</v>
+        <v>37.68</v>
       </c>
       <c r="B43" s="19">
         <f>A43-$B$10</f>
@@ -11912,7 +11866,7 @@
         <v/>
       </c>
       <c r="H43" s="17">
-        <f>($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I43" s="17">
@@ -11926,7 +11880,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="n">
-        <v>37.98</v>
+        <v>37.78</v>
       </c>
       <c r="B44" s="19">
         <f>A44-$B$10</f>
@@ -11953,7 +11907,7 @@
         <v/>
       </c>
       <c r="H44" s="17">
-        <f>($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I44" s="17">
@@ -11967,7 +11921,7 @@
     </row>
     <row r="45">
       <c r="A45" s="19" t="n">
-        <v>38.08</v>
+        <v>37.88</v>
       </c>
       <c r="B45" s="19">
         <f>A45-$B$10</f>
@@ -11994,7 +11948,7 @@
         <v/>
       </c>
       <c r="H45" s="17">
-        <f>($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I45" s="17">
@@ -12008,7 +11962,7 @@
     </row>
     <row r="46">
       <c r="A46" s="19" t="n">
-        <v>38.18</v>
+        <v>37.98</v>
       </c>
       <c r="B46" s="19">
         <f>A46-$B$10</f>
@@ -12035,7 +11989,7 @@
         <v/>
       </c>
       <c r="H46" s="17">
-        <f>($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I46" s="17">
@@ -12049,7 +12003,7 @@
     </row>
     <row r="47">
       <c r="A47" s="19" t="n">
-        <v>38.28</v>
+        <v>38.08</v>
       </c>
       <c r="B47" s="19">
         <f>A47-$B$10</f>
@@ -12076,7 +12030,7 @@
         <v/>
       </c>
       <c r="H47" s="17">
-        <f>($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I47" s="17">
@@ -12090,7 +12044,7 @@
     </row>
     <row r="48">
       <c r="A48" s="19" t="n">
-        <v>38.38</v>
+        <v>38.18</v>
       </c>
       <c r="B48" s="19">
         <f>A48-$B$10</f>
@@ -12117,7 +12071,7 @@
         <v/>
       </c>
       <c r="H48" s="17">
-        <f>($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I48" s="17">
@@ -12131,7 +12085,7 @@
     </row>
     <row r="49">
       <c r="A49" s="19" t="n">
-        <v>38.48</v>
+        <v>38.28</v>
       </c>
       <c r="B49" s="19">
         <f>A49-$B$10</f>
@@ -12158,7 +12112,7 @@
         <v/>
       </c>
       <c r="H49" s="17">
-        <f>($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I49" s="17">
@@ -12172,7 +12126,7 @@
     </row>
     <row r="50">
       <c r="A50" s="19" t="n">
-        <v>38.58</v>
+        <v>38.38</v>
       </c>
       <c r="B50" s="19">
         <f>A50-$B$10</f>
@@ -12199,7 +12153,7 @@
         <v/>
       </c>
       <c r="H50" s="17">
-        <f>($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I50" s="17">
@@ -12213,7 +12167,7 @@
     </row>
     <row r="51">
       <c r="A51" s="19" t="n">
-        <v>38.68</v>
+        <v>38.48</v>
       </c>
       <c r="B51" s="19">
         <f>A51-$B$10</f>
@@ -12240,7 +12194,7 @@
         <v/>
       </c>
       <c r="H51" s="17">
-        <f>($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I51" s="17">
@@ -12254,7 +12208,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="n">
-        <v>38.78</v>
+        <v>38.58</v>
       </c>
       <c r="B52" s="19">
         <f>A52-$B$10</f>
@@ -12281,7 +12235,7 @@
         <v/>
       </c>
       <c r="H52" s="17">
-        <f>($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I52" s="17">
@@ -12295,7 +12249,7 @@
     </row>
     <row r="53">
       <c r="A53" s="19" t="n">
-        <v>38.88</v>
+        <v>38.68</v>
       </c>
       <c r="B53" s="19">
         <f>A53-$B$10</f>
@@ -12322,7 +12276,7 @@
         <v/>
       </c>
       <c r="H53" s="17">
-        <f>($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I53" s="17">
@@ -12336,7 +12290,7 @@
     </row>
     <row r="54">
       <c r="A54" s="19" t="n">
-        <v>38.98</v>
+        <v>38.78</v>
       </c>
       <c r="B54" s="19">
         <f>A54-$B$10</f>
@@ -12363,7 +12317,7 @@
         <v/>
       </c>
       <c r="H54" s="17">
-        <f>($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I54" s="17">
@@ -12377,7 +12331,7 @@
     </row>
     <row r="55">
       <c r="A55" s="19" t="n">
-        <v>39.08</v>
+        <v>38.88</v>
       </c>
       <c r="B55" s="19">
         <f>A55-$B$10</f>
@@ -12404,7 +12358,7 @@
         <v/>
       </c>
       <c r="H55" s="17">
-        <f>($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I55" s="17">
@@ -12418,7 +12372,7 @@
     </row>
     <row r="56">
       <c r="A56" s="19" t="n">
-        <v>39.18</v>
+        <v>38.98</v>
       </c>
       <c r="B56" s="19">
         <f>A56-$B$10</f>
@@ -12445,7 +12399,7 @@
         <v/>
       </c>
       <c r="H56" s="17">
-        <f>($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I56" s="17">
@@ -12459,7 +12413,7 @@
     </row>
     <row r="57">
       <c r="A57" s="19" t="n">
-        <v>39.28</v>
+        <v>39.08</v>
       </c>
       <c r="B57" s="19">
         <f>A57-$B$10</f>
@@ -12486,7 +12440,7 @@
         <v/>
       </c>
       <c r="H57" s="17">
-        <f>($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I57" s="17">
@@ -12500,7 +12454,7 @@
     </row>
     <row r="58">
       <c r="A58" s="19" t="n">
-        <v>39.38</v>
+        <v>39.18</v>
       </c>
       <c r="B58" s="19">
         <f>A58-$B$10</f>
@@ -12527,7 +12481,7 @@
         <v/>
       </c>
       <c r="H58" s="17">
-        <f>($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I58" s="17">
@@ -12541,7 +12495,7 @@
     </row>
     <row r="59">
       <c r="A59" s="19" t="n">
-        <v>39.48</v>
+        <v>39.28</v>
       </c>
       <c r="B59" s="19">
         <f>A59-$B$10</f>
@@ -12568,7 +12522,7 @@
         <v/>
       </c>
       <c r="H59" s="17">
-        <f>($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I59" s="17">
@@ -12582,7 +12536,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="n">
-        <v>39.58</v>
+        <v>39.38</v>
       </c>
       <c r="B60" s="19">
         <f>A60-$B$10</f>
@@ -12609,7 +12563,7 @@
         <v/>
       </c>
       <c r="H60" s="17">
-        <f>($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I60" s="17">
@@ -12623,7 +12577,7 @@
     </row>
     <row r="61">
       <c r="A61" s="19" t="n">
-        <v>39.68</v>
+        <v>39.48</v>
       </c>
       <c r="B61" s="19">
         <f>A61-$B$10</f>
@@ -12650,7 +12604,7 @@
         <v/>
       </c>
       <c r="H61" s="17">
-        <f>($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I61" s="17">
@@ -12664,7 +12618,7 @@
     </row>
     <row r="62">
       <c r="A62" s="19" t="n">
-        <v>39.78</v>
+        <v>39.58</v>
       </c>
       <c r="B62" s="19">
         <f>A62-$B$10</f>
@@ -12691,7 +12645,7 @@
         <v/>
       </c>
       <c r="H62" s="17">
-        <f>($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I62" s="17">
@@ -12705,7 +12659,7 @@
     </row>
     <row r="63">
       <c r="A63" s="19" t="n">
-        <v>39.88</v>
+        <v>39.68</v>
       </c>
       <c r="B63" s="19">
         <f>A63-$B$10</f>
@@ -12732,7 +12686,7 @@
         <v/>
       </c>
       <c r="H63" s="17">
-        <f>($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I63" s="17">
@@ -12746,7 +12700,7 @@
     </row>
     <row r="64">
       <c r="A64" s="19" t="n">
-        <v>39.98</v>
+        <v>39.78</v>
       </c>
       <c r="B64" s="19">
         <f>A64-$B$10</f>
@@ -12773,7 +12727,7 @@
         <v/>
       </c>
       <c r="H64" s="17">
-        <f>($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I64" s="17">
@@ -12782,6 +12736,88 @@
       </c>
       <c r="J64" s="8">
         <f>H64+I64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="B65" s="19">
+        <f>A65-$B$10</f>
+        <v/>
+      </c>
+      <c r="C65" s="19">
+        <f>MAX(0,A65-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D65" s="17">
+        <f>IF(C65&lt;=0,0,($B$5+$B$7*C65)*C65)</f>
+        <v/>
+      </c>
+      <c r="E65" s="16">
+        <f>D65*$B$9</f>
+        <v/>
+      </c>
+      <c r="F65" s="16">
+        <f>IF(A65&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A65&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1))+(A65-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G65" s="14">
+        <f>E65+F65</f>
+        <v/>
+      </c>
+      <c r="H65" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B65&lt;=0,0,IF(B65&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1))+(B65-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I65" s="17">
+        <f>IF(C65&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D65*IF(($B$5+2*C65*SQRT(1+$B$7^2))&lt;=0,0,((D65/($B$5+2*C65*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J65" s="8">
+        <f>H65+I65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="B66" s="19">
+        <f>A66-$B$10</f>
+        <v/>
+      </c>
+      <c r="C66" s="19">
+        <f>MAX(0,A66-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D66" s="17">
+        <f>IF(C66&lt;=0,0,($B$5+$B$7*C66)*C66)</f>
+        <v/>
+      </c>
+      <c r="E66" s="16">
+        <f>D66*$B$9</f>
+        <v/>
+      </c>
+      <c r="F66" s="16">
+        <f>IF(A66&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A66&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1))+(A66-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G66" s="14">
+        <f>E66+F66</f>
+        <v/>
+      </c>
+      <c r="H66" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B66&lt;=0,0,IF(B66&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1))+(B66-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I66" s="17">
+        <f>IF(C66&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D66*IF(($B$5+2*C66*SQRT(1+$B$7^2))&lt;=0,0,((D66/($B$5+2*C66*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J66" s="8">
+        <f>H66+I66</f>
         <v/>
       </c>
     </row>
@@ -13018,11 +13054,11 @@
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>IF(F15&lt;=INDEX(Compose_50pct!$G$13:$G$64,1),INDEX(Compose_50pct!$A$13:$A$64,1),IF(F15&gt;=INDEX(Compose_50pct!$G$13:$G$64,ROWS(Compose_50pct!$G$13:$G$64)),INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$A$13:$A$64,MATCH(F15,Compose_50pct!$G$13:$G$64,1))+(F15-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F15,Compose_50pct!$G$13:$G$64,1)))/(INDEX(Compose_50pct!$G$13:$G$64,MATCH(F15,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F15,Compose_50pct!$G$13:$G$64,1)))*(INDEX(Compose_50pct!$A$13:$A$64,MATCH(F15,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(F15,Compose_50pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F15&lt;=INDEX(Compose_50pct!$G$15:$G$66,1),INDEX(Compose_50pct!$A$15:$A$66,1),IF(F15&gt;=INDEX(Compose_50pct!$G$15:$G$66,ROWS(Compose_50pct!$G$15:$G$66)),INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$A$15:$A$66,MATCH(F15,Compose_50pct!$G$15:$G$66,1))+(F15-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F15,Compose_50pct!$G$15:$G$66,1)))/(INDEX(Compose_50pct!$G$15:$G$66,MATCH(F15,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F15,Compose_50pct!$G$15:$G$66,1)))*(INDEX(Compose_50pct!$A$15:$A$66,MATCH(F15,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(F15,Compose_50pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$J$13:$J$64,1),IF(C16&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$J$13:$J$64,ROWS(Compose_50pct!$J$13:$J$64)),INDEX(Compose_50pct!$J$13:$J$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1))+(C16-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$J$13:$J$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$J$13:$J$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$J$15:$J$66,1),IF(C16&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$J$15:$J$66,ROWS(Compose_50pct!$J$15:$J$66)),INDEX(Compose_50pct!$J$15:$J$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1))+(C16-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$J$15:$J$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$J$15:$J$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E16" s="16">
@@ -13034,11 +13070,11 @@
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$H$13:$H$64,1),IF(C16&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$H$13:$H$64,ROWS(Compose_50pct!$H$13:$H$64)),INDEX(Compose_50pct!$H$13:$H$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1))+(C16-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$H$13:$H$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$H$13:$H$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$H$15:$H$66,1),IF(C16&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$H$15:$H$66,ROWS(Compose_50pct!$H$15:$H$66)),INDEX(Compose_50pct!$H$15:$H$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1))+(C16-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$H$15:$H$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$H$15:$H$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$I$13:$I$64,1),IF(C16&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$I$13:$I$64,ROWS(Compose_50pct!$I$13:$I$64)),INDEX(Compose_50pct!$I$13:$I$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1))+(C16-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$I$13:$I$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$I$13:$I$64,MATCH(C16,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$I$15:$I$66,1),IF(C16&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$I$15:$I$66,ROWS(Compose_50pct!$I$15:$I$66)),INDEX(Compose_50pct!$I$15:$I$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1))+(C16-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$I$15:$I$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$I$15:$I$66,MATCH(C16,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I16" s="21">
@@ -13056,11 +13092,11 @@
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>IF(F16&lt;=INDEX(Compose_50pct!$G$13:$G$64,1),INDEX(Compose_50pct!$A$13:$A$64,1),IF(F16&gt;=INDEX(Compose_50pct!$G$13:$G$64,ROWS(Compose_50pct!$G$13:$G$64)),INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$A$13:$A$64,MATCH(F16,Compose_50pct!$G$13:$G$64,1))+(F16-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F16,Compose_50pct!$G$13:$G$64,1)))/(INDEX(Compose_50pct!$G$13:$G$64,MATCH(F16,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F16,Compose_50pct!$G$13:$G$64,1)))*(INDEX(Compose_50pct!$A$13:$A$64,MATCH(F16,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(F16,Compose_50pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F16&lt;=INDEX(Compose_50pct!$G$15:$G$66,1),INDEX(Compose_50pct!$A$15:$A$66,1),IF(F16&gt;=INDEX(Compose_50pct!$G$15:$G$66,ROWS(Compose_50pct!$G$15:$G$66)),INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$A$15:$A$66,MATCH(F16,Compose_50pct!$G$15:$G$66,1))+(F16-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F16,Compose_50pct!$G$15:$G$66,1)))/(INDEX(Compose_50pct!$G$15:$G$66,MATCH(F16,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F16,Compose_50pct!$G$15:$G$66,1)))*(INDEX(Compose_50pct!$A$15:$A$66,MATCH(F16,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(F16,Compose_50pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$J$13:$J$64,1),IF(C17&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$J$13:$J$64,ROWS(Compose_50pct!$J$13:$J$64)),INDEX(Compose_50pct!$J$13:$J$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1))+(C17-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$J$13:$J$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$J$13:$J$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$J$15:$J$66,1),IF(C17&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$J$15:$J$66,ROWS(Compose_50pct!$J$15:$J$66)),INDEX(Compose_50pct!$J$15:$J$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1))+(C17-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$J$15:$J$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$J$15:$J$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E17" s="16">
@@ -13072,11 +13108,11 @@
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$H$13:$H$64,1),IF(C17&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$H$13:$H$64,ROWS(Compose_50pct!$H$13:$H$64)),INDEX(Compose_50pct!$H$13:$H$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1))+(C17-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$H$13:$H$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$H$13:$H$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$H$15:$H$66,1),IF(C17&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$H$15:$H$66,ROWS(Compose_50pct!$H$15:$H$66)),INDEX(Compose_50pct!$H$15:$H$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1))+(C17-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$H$15:$H$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$H$15:$H$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$I$13:$I$64,1),IF(C17&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$I$13:$I$64,ROWS(Compose_50pct!$I$13:$I$64)),INDEX(Compose_50pct!$I$13:$I$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1))+(C17-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$I$13:$I$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$I$13:$I$64,MATCH(C17,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$I$15:$I$66,1),IF(C17&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$I$15:$I$66,ROWS(Compose_50pct!$I$15:$I$66)),INDEX(Compose_50pct!$I$15:$I$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1))+(C17-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$I$15:$I$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$I$15:$I$66,MATCH(C17,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I17" s="21">
@@ -13094,11 +13130,11 @@
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>IF(F17&lt;=INDEX(Compose_50pct!$G$13:$G$64,1),INDEX(Compose_50pct!$A$13:$A$64,1),IF(F17&gt;=INDEX(Compose_50pct!$G$13:$G$64,ROWS(Compose_50pct!$G$13:$G$64)),INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$A$13:$A$64,MATCH(F17,Compose_50pct!$G$13:$G$64,1))+(F17-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F17,Compose_50pct!$G$13:$G$64,1)))/(INDEX(Compose_50pct!$G$13:$G$64,MATCH(F17,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F17,Compose_50pct!$G$13:$G$64,1)))*(INDEX(Compose_50pct!$A$13:$A$64,MATCH(F17,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(F17,Compose_50pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F17&lt;=INDEX(Compose_50pct!$G$15:$G$66,1),INDEX(Compose_50pct!$A$15:$A$66,1),IF(F17&gt;=INDEX(Compose_50pct!$G$15:$G$66,ROWS(Compose_50pct!$G$15:$G$66)),INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$A$15:$A$66,MATCH(F17,Compose_50pct!$G$15:$G$66,1))+(F17-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F17,Compose_50pct!$G$15:$G$66,1)))/(INDEX(Compose_50pct!$G$15:$G$66,MATCH(F17,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F17,Compose_50pct!$G$15:$G$66,1)))*(INDEX(Compose_50pct!$A$15:$A$66,MATCH(F17,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(F17,Compose_50pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$J$13:$J$64,1),IF(C18&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$J$13:$J$64,ROWS(Compose_50pct!$J$13:$J$64)),INDEX(Compose_50pct!$J$13:$J$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1))+(C18-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$J$13:$J$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$J$13:$J$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$J$15:$J$66,1),IF(C18&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$J$15:$J$66,ROWS(Compose_50pct!$J$15:$J$66)),INDEX(Compose_50pct!$J$15:$J$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1))+(C18-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$J$15:$J$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$J$15:$J$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E18" s="16">
@@ -13110,11 +13146,11 @@
         <v/>
       </c>
       <c r="G18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$H$13:$H$64,1),IF(C18&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$H$13:$H$64,ROWS(Compose_50pct!$H$13:$H$64)),INDEX(Compose_50pct!$H$13:$H$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1))+(C18-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$H$13:$H$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$H$13:$H$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$H$15:$H$66,1),IF(C18&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$H$15:$H$66,ROWS(Compose_50pct!$H$15:$H$66)),INDEX(Compose_50pct!$H$15:$H$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1))+(C18-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$H$15:$H$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$H$15:$H$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$I$13:$I$64,1),IF(C18&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$I$13:$I$64,ROWS(Compose_50pct!$I$13:$I$64)),INDEX(Compose_50pct!$I$13:$I$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1))+(C18-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$I$13:$I$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$I$13:$I$64,MATCH(C18,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$I$15:$I$66,1),IF(C18&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$I$15:$I$66,ROWS(Compose_50pct!$I$15:$I$66)),INDEX(Compose_50pct!$I$15:$I$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1))+(C18-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$I$15:$I$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$I$15:$I$66,MATCH(C18,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I18" s="21">
@@ -13132,11 +13168,11 @@
         <v/>
       </c>
       <c r="C19" s="17">
-        <f>IF(F18&lt;=INDEX(Compose_50pct!$G$13:$G$64,1),INDEX(Compose_50pct!$A$13:$A$64,1),IF(F18&gt;=INDEX(Compose_50pct!$G$13:$G$64,ROWS(Compose_50pct!$G$13:$G$64)),INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$A$13:$A$64,MATCH(F18,Compose_50pct!$G$13:$G$64,1))+(F18-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F18,Compose_50pct!$G$13:$G$64,1)))/(INDEX(Compose_50pct!$G$13:$G$64,MATCH(F18,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F18,Compose_50pct!$G$13:$G$64,1)))*(INDEX(Compose_50pct!$A$13:$A$64,MATCH(F18,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(F18,Compose_50pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F18&lt;=INDEX(Compose_50pct!$G$15:$G$66,1),INDEX(Compose_50pct!$A$15:$A$66,1),IF(F18&gt;=INDEX(Compose_50pct!$G$15:$G$66,ROWS(Compose_50pct!$G$15:$G$66)),INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$A$15:$A$66,MATCH(F18,Compose_50pct!$G$15:$G$66,1))+(F18-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F18,Compose_50pct!$G$15:$G$66,1)))/(INDEX(Compose_50pct!$G$15:$G$66,MATCH(F18,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F18,Compose_50pct!$G$15:$G$66,1)))*(INDEX(Compose_50pct!$A$15:$A$66,MATCH(F18,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(F18,Compose_50pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$J$13:$J$64,1),IF(C19&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$J$13:$J$64,ROWS(Compose_50pct!$J$13:$J$64)),INDEX(Compose_50pct!$J$13:$J$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1))+(C19-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$J$13:$J$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$J$13:$J$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$J$15:$J$66,1),IF(C19&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$J$15:$J$66,ROWS(Compose_50pct!$J$15:$J$66)),INDEX(Compose_50pct!$J$15:$J$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1))+(C19-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$J$15:$J$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$J$15:$J$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E19" s="16">
@@ -13148,11 +13184,11 @@
         <v/>
       </c>
       <c r="G19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$H$13:$H$64,1),IF(C19&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$H$13:$H$64,ROWS(Compose_50pct!$H$13:$H$64)),INDEX(Compose_50pct!$H$13:$H$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1))+(C19-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$H$13:$H$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$H$13:$H$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$H$15:$H$66,1),IF(C19&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$H$15:$H$66,ROWS(Compose_50pct!$H$15:$H$66)),INDEX(Compose_50pct!$H$15:$H$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1))+(C19-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$H$15:$H$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$H$15:$H$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$I$13:$I$64,1),IF(C19&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$I$13:$I$64,ROWS(Compose_50pct!$I$13:$I$64)),INDEX(Compose_50pct!$I$13:$I$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1))+(C19-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$I$13:$I$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$I$13:$I$64,MATCH(C19,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$I$15:$I$66,1),IF(C19&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$I$15:$I$66,ROWS(Compose_50pct!$I$15:$I$66)),INDEX(Compose_50pct!$I$15:$I$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1))+(C19-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$I$15:$I$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$I$15:$I$66,MATCH(C19,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I19" s="21">
@@ -13170,11 +13206,11 @@
         <v/>
       </c>
       <c r="C20" s="17">
-        <f>IF(F19&lt;=INDEX(Compose_50pct!$G$13:$G$64,1),INDEX(Compose_50pct!$A$13:$A$64,1),IF(F19&gt;=INDEX(Compose_50pct!$G$13:$G$64,ROWS(Compose_50pct!$G$13:$G$64)),INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$A$13:$A$64,MATCH(F19,Compose_50pct!$G$13:$G$64,1))+(F19-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F19,Compose_50pct!$G$13:$G$64,1)))/(INDEX(Compose_50pct!$G$13:$G$64,MATCH(F19,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F19,Compose_50pct!$G$13:$G$64,1)))*(INDEX(Compose_50pct!$A$13:$A$64,MATCH(F19,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(F19,Compose_50pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F19&lt;=INDEX(Compose_50pct!$G$15:$G$66,1),INDEX(Compose_50pct!$A$15:$A$66,1),IF(F19&gt;=INDEX(Compose_50pct!$G$15:$G$66,ROWS(Compose_50pct!$G$15:$G$66)),INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$A$15:$A$66,MATCH(F19,Compose_50pct!$G$15:$G$66,1))+(F19-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F19,Compose_50pct!$G$15:$G$66,1)))/(INDEX(Compose_50pct!$G$15:$G$66,MATCH(F19,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F19,Compose_50pct!$G$15:$G$66,1)))*(INDEX(Compose_50pct!$A$15:$A$66,MATCH(F19,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(F19,Compose_50pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D20" s="17">
-        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$J$13:$J$64,1),IF(C20&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$J$13:$J$64,ROWS(Compose_50pct!$J$13:$J$64)),INDEX(Compose_50pct!$J$13:$J$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1))+(C20-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$J$13:$J$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$J$13:$J$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$J$15:$J$66,1),IF(C20&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$J$15:$J$66,ROWS(Compose_50pct!$J$15:$J$66)),INDEX(Compose_50pct!$J$15:$J$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1))+(C20-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$J$15:$J$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$J$15:$J$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E20" s="16">
@@ -13186,11 +13222,11 @@
         <v/>
       </c>
       <c r="G20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$H$13:$H$64,1),IF(C20&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$H$13:$H$64,ROWS(Compose_50pct!$H$13:$H$64)),INDEX(Compose_50pct!$H$13:$H$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1))+(C20-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$H$13:$H$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$H$13:$H$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$H$15:$H$66,1),IF(C20&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$H$15:$H$66,ROWS(Compose_50pct!$H$15:$H$66)),INDEX(Compose_50pct!$H$15:$H$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1))+(C20-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$H$15:$H$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$H$15:$H$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$I$13:$I$64,1),IF(C20&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$I$13:$I$64,ROWS(Compose_50pct!$I$13:$I$64)),INDEX(Compose_50pct!$I$13:$I$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1))+(C20-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$I$13:$I$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$I$13:$I$64,MATCH(C20,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$I$15:$I$66,1),IF(C20&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$I$15:$I$66,ROWS(Compose_50pct!$I$15:$I$66)),INDEX(Compose_50pct!$I$15:$I$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1))+(C20-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$I$15:$I$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$I$15:$I$66,MATCH(C20,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I20" s="21">
@@ -13208,11 +13244,11 @@
         <v/>
       </c>
       <c r="C21" s="17">
-        <f>IF(F20&lt;=INDEX(Compose_50pct!$G$13:$G$64,1),INDEX(Compose_50pct!$A$13:$A$64,1),IF(F20&gt;=INDEX(Compose_50pct!$G$13:$G$64,ROWS(Compose_50pct!$G$13:$G$64)),INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$A$13:$A$64,MATCH(F20,Compose_50pct!$G$13:$G$64,1))+(F20-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F20,Compose_50pct!$G$13:$G$64,1)))/(INDEX(Compose_50pct!$G$13:$G$64,MATCH(F20,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F20,Compose_50pct!$G$13:$G$64,1)))*(INDEX(Compose_50pct!$A$13:$A$64,MATCH(F20,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(F20,Compose_50pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F20&lt;=INDEX(Compose_50pct!$G$15:$G$66,1),INDEX(Compose_50pct!$A$15:$A$66,1),IF(F20&gt;=INDEX(Compose_50pct!$G$15:$G$66,ROWS(Compose_50pct!$G$15:$G$66)),INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$A$15:$A$66,MATCH(F20,Compose_50pct!$G$15:$G$66,1))+(F20-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F20,Compose_50pct!$G$15:$G$66,1)))/(INDEX(Compose_50pct!$G$15:$G$66,MATCH(F20,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F20,Compose_50pct!$G$15:$G$66,1)))*(INDEX(Compose_50pct!$A$15:$A$66,MATCH(F20,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(F20,Compose_50pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D21" s="17">
-        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$J$13:$J$64,1),IF(C21&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$J$13:$J$64,ROWS(Compose_50pct!$J$13:$J$64)),INDEX(Compose_50pct!$J$13:$J$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1))+(C21-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$J$13:$J$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$J$13:$J$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$J$15:$J$66,1),IF(C21&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$J$15:$J$66,ROWS(Compose_50pct!$J$15:$J$66)),INDEX(Compose_50pct!$J$15:$J$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1))+(C21-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$J$15:$J$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$J$15:$J$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E21" s="16">
@@ -13224,11 +13260,11 @@
         <v/>
       </c>
       <c r="G21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$H$13:$H$64,1),IF(C21&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$H$13:$H$64,ROWS(Compose_50pct!$H$13:$H$64)),INDEX(Compose_50pct!$H$13:$H$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1))+(C21-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$H$13:$H$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$H$13:$H$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$H$15:$H$66,1),IF(C21&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$H$15:$H$66,ROWS(Compose_50pct!$H$15:$H$66)),INDEX(Compose_50pct!$H$15:$H$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1))+(C21-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$H$15:$H$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$H$15:$H$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$I$13:$I$64,1),IF(C21&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$I$13:$I$64,ROWS(Compose_50pct!$I$13:$I$64)),INDEX(Compose_50pct!$I$13:$I$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1))+(C21-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$I$13:$I$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$I$13:$I$64,MATCH(C21,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$I$15:$I$66,1),IF(C21&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$I$15:$I$66,ROWS(Compose_50pct!$I$15:$I$66)),INDEX(Compose_50pct!$I$15:$I$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1))+(C21-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$I$15:$I$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$I$15:$I$66,MATCH(C21,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I21" s="21">
@@ -13246,11 +13282,11 @@
         <v/>
       </c>
       <c r="C22" s="17">
-        <f>IF(F21&lt;=INDEX(Compose_50pct!$G$13:$G$64,1),INDEX(Compose_50pct!$A$13:$A$64,1),IF(F21&gt;=INDEX(Compose_50pct!$G$13:$G$64,ROWS(Compose_50pct!$G$13:$G$64)),INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$A$13:$A$64,MATCH(F21,Compose_50pct!$G$13:$G$64,1))+(F21-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F21,Compose_50pct!$G$13:$G$64,1)))/(INDEX(Compose_50pct!$G$13:$G$64,MATCH(F21,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F21,Compose_50pct!$G$13:$G$64,1)))*(INDEX(Compose_50pct!$A$13:$A$64,MATCH(F21,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(F21,Compose_50pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F21&lt;=INDEX(Compose_50pct!$G$15:$G$66,1),INDEX(Compose_50pct!$A$15:$A$66,1),IF(F21&gt;=INDEX(Compose_50pct!$G$15:$G$66,ROWS(Compose_50pct!$G$15:$G$66)),INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$A$15:$A$66,MATCH(F21,Compose_50pct!$G$15:$G$66,1))+(F21-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F21,Compose_50pct!$G$15:$G$66,1)))/(INDEX(Compose_50pct!$G$15:$G$66,MATCH(F21,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F21,Compose_50pct!$G$15:$G$66,1)))*(INDEX(Compose_50pct!$A$15:$A$66,MATCH(F21,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(F21,Compose_50pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D22" s="17">
-        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$J$13:$J$64,1),IF(C22&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$J$13:$J$64,ROWS(Compose_50pct!$J$13:$J$64)),INDEX(Compose_50pct!$J$13:$J$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1))+(C22-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$J$13:$J$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$J$13:$J$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$J$15:$J$66,1),IF(C22&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$J$15:$J$66,ROWS(Compose_50pct!$J$15:$J$66)),INDEX(Compose_50pct!$J$15:$J$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1))+(C22-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$J$15:$J$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$J$15:$J$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E22" s="16">
@@ -13262,11 +13298,11 @@
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$H$13:$H$64,1),IF(C22&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$H$13:$H$64,ROWS(Compose_50pct!$H$13:$H$64)),INDEX(Compose_50pct!$H$13:$H$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1))+(C22-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$H$13:$H$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$H$13:$H$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$H$15:$H$66,1),IF(C22&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$H$15:$H$66,ROWS(Compose_50pct!$H$15:$H$66)),INDEX(Compose_50pct!$H$15:$H$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1))+(C22-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$H$15:$H$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$H$15:$H$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$I$13:$I$64,1),IF(C22&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$I$13:$I$64,ROWS(Compose_50pct!$I$13:$I$64)),INDEX(Compose_50pct!$I$13:$I$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1))+(C22-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$I$13:$I$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$I$13:$I$64,MATCH(C22,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$I$15:$I$66,1),IF(C22&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$I$15:$I$66,ROWS(Compose_50pct!$I$15:$I$66)),INDEX(Compose_50pct!$I$15:$I$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1))+(C22-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$I$15:$I$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$I$15:$I$66,MATCH(C22,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I22" s="21">
@@ -13284,11 +13320,11 @@
         <v/>
       </c>
       <c r="C23" s="17">
-        <f>IF(F22&lt;=INDEX(Compose_50pct!$G$13:$G$64,1),INDEX(Compose_50pct!$A$13:$A$64,1),IF(F22&gt;=INDEX(Compose_50pct!$G$13:$G$64,ROWS(Compose_50pct!$G$13:$G$64)),INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$A$13:$A$64,MATCH(F22,Compose_50pct!$G$13:$G$64,1))+(F22-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F22,Compose_50pct!$G$13:$G$64,1)))/(INDEX(Compose_50pct!$G$13:$G$64,MATCH(F22,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F22,Compose_50pct!$G$13:$G$64,1)))*(INDEX(Compose_50pct!$A$13:$A$64,MATCH(F22,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(F22,Compose_50pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F22&lt;=INDEX(Compose_50pct!$G$15:$G$66,1),INDEX(Compose_50pct!$A$15:$A$66,1),IF(F22&gt;=INDEX(Compose_50pct!$G$15:$G$66,ROWS(Compose_50pct!$G$15:$G$66)),INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$A$15:$A$66,MATCH(F22,Compose_50pct!$G$15:$G$66,1))+(F22-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F22,Compose_50pct!$G$15:$G$66,1)))/(INDEX(Compose_50pct!$G$15:$G$66,MATCH(F22,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F22,Compose_50pct!$G$15:$G$66,1)))*(INDEX(Compose_50pct!$A$15:$A$66,MATCH(F22,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(F22,Compose_50pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D23" s="17">
-        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$J$13:$J$64,1),IF(C23&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$J$13:$J$64,ROWS(Compose_50pct!$J$13:$J$64)),INDEX(Compose_50pct!$J$13:$J$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1))+(C23-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$J$13:$J$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$J$13:$J$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$J$15:$J$66,1),IF(C23&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$J$15:$J$66,ROWS(Compose_50pct!$J$15:$J$66)),INDEX(Compose_50pct!$J$15:$J$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1))+(C23-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$J$15:$J$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$J$15:$J$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E23" s="16">
@@ -13300,11 +13336,11 @@
         <v/>
       </c>
       <c r="G23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$H$13:$H$64,1),IF(C23&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$H$13:$H$64,ROWS(Compose_50pct!$H$13:$H$64)),INDEX(Compose_50pct!$H$13:$H$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1))+(C23-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$H$13:$H$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$H$13:$H$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$H$15:$H$66,1),IF(C23&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$H$15:$H$66,ROWS(Compose_50pct!$H$15:$H$66)),INDEX(Compose_50pct!$H$15:$H$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1))+(C23-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$H$15:$H$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$H$15:$H$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$I$13:$I$64,1),IF(C23&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$I$13:$I$64,ROWS(Compose_50pct!$I$13:$I$64)),INDEX(Compose_50pct!$I$13:$I$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1))+(C23-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$I$13:$I$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$I$13:$I$64,MATCH(C23,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$I$15:$I$66,1),IF(C23&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$I$15:$I$66,ROWS(Compose_50pct!$I$15:$I$66)),INDEX(Compose_50pct!$I$15:$I$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1))+(C23-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$I$15:$I$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$I$15:$I$66,MATCH(C23,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I23" s="21">
@@ -13322,11 +13358,11 @@
         <v/>
       </c>
       <c r="C24" s="17">
-        <f>IF(F23&lt;=INDEX(Compose_50pct!$G$13:$G$64,1),INDEX(Compose_50pct!$A$13:$A$64,1),IF(F23&gt;=INDEX(Compose_50pct!$G$13:$G$64,ROWS(Compose_50pct!$G$13:$G$64)),INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$A$13:$A$64,MATCH(F23,Compose_50pct!$G$13:$G$64,1))+(F23-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F23,Compose_50pct!$G$13:$G$64,1)))/(INDEX(Compose_50pct!$G$13:$G$64,MATCH(F23,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F23,Compose_50pct!$G$13:$G$64,1)))*(INDEX(Compose_50pct!$A$13:$A$64,MATCH(F23,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(F23,Compose_50pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F23&lt;=INDEX(Compose_50pct!$G$15:$G$66,1),INDEX(Compose_50pct!$A$15:$A$66,1),IF(F23&gt;=INDEX(Compose_50pct!$G$15:$G$66,ROWS(Compose_50pct!$G$15:$G$66)),INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$A$15:$A$66,MATCH(F23,Compose_50pct!$G$15:$G$66,1))+(F23-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F23,Compose_50pct!$G$15:$G$66,1)))/(INDEX(Compose_50pct!$G$15:$G$66,MATCH(F23,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F23,Compose_50pct!$G$15:$G$66,1)))*(INDEX(Compose_50pct!$A$15:$A$66,MATCH(F23,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(F23,Compose_50pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D24" s="17">
-        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$J$13:$J$64,1),IF(C24&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$J$13:$J$64,ROWS(Compose_50pct!$J$13:$J$64)),INDEX(Compose_50pct!$J$13:$J$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1))+(C24-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$J$13:$J$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$J$13:$J$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$J$15:$J$66,1),IF(C24&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$J$15:$J$66,ROWS(Compose_50pct!$J$15:$J$66)),INDEX(Compose_50pct!$J$15:$J$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1))+(C24-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$J$15:$J$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$J$15:$J$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E24" s="16">
@@ -13338,11 +13374,11 @@
         <v/>
       </c>
       <c r="G24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$H$13:$H$64,1),IF(C24&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$H$13:$H$64,ROWS(Compose_50pct!$H$13:$H$64)),INDEX(Compose_50pct!$H$13:$H$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1))+(C24-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$H$13:$H$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$H$13:$H$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$H$15:$H$66,1),IF(C24&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$H$15:$H$66,ROWS(Compose_50pct!$H$15:$H$66)),INDEX(Compose_50pct!$H$15:$H$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1))+(C24-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$H$15:$H$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$H$15:$H$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$I$13:$I$64,1),IF(C24&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$I$13:$I$64,ROWS(Compose_50pct!$I$13:$I$64)),INDEX(Compose_50pct!$I$13:$I$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1))+(C24-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$I$13:$I$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$I$13:$I$64,MATCH(C24,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$I$15:$I$66,1),IF(C24&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$I$15:$I$66,ROWS(Compose_50pct!$I$15:$I$66)),INDEX(Compose_50pct!$I$15:$I$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1))+(C24-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$I$15:$I$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$I$15:$I$66,MATCH(C24,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I24" s="21">
@@ -13360,11 +13396,11 @@
         <v/>
       </c>
       <c r="C25" s="17">
-        <f>IF(F24&lt;=INDEX(Compose_50pct!$G$13:$G$64,1),INDEX(Compose_50pct!$A$13:$A$64,1),IF(F24&gt;=INDEX(Compose_50pct!$G$13:$G$64,ROWS(Compose_50pct!$G$13:$G$64)),INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$A$13:$A$64,MATCH(F24,Compose_50pct!$G$13:$G$64,1))+(F24-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F24,Compose_50pct!$G$13:$G$64,1)))/(INDEX(Compose_50pct!$G$13:$G$64,MATCH(F24,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F24,Compose_50pct!$G$13:$G$64,1)))*(INDEX(Compose_50pct!$A$13:$A$64,MATCH(F24,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(F24,Compose_50pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F24&lt;=INDEX(Compose_50pct!$G$15:$G$66,1),INDEX(Compose_50pct!$A$15:$A$66,1),IF(F24&gt;=INDEX(Compose_50pct!$G$15:$G$66,ROWS(Compose_50pct!$G$15:$G$66)),INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$A$15:$A$66,MATCH(F24,Compose_50pct!$G$15:$G$66,1))+(F24-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F24,Compose_50pct!$G$15:$G$66,1)))/(INDEX(Compose_50pct!$G$15:$G$66,MATCH(F24,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F24,Compose_50pct!$G$15:$G$66,1)))*(INDEX(Compose_50pct!$A$15:$A$66,MATCH(F24,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(F24,Compose_50pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D25" s="17">
-        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$J$13:$J$64,1),IF(C25&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$J$13:$J$64,ROWS(Compose_50pct!$J$13:$J$64)),INDEX(Compose_50pct!$J$13:$J$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1))+(C25-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$J$13:$J$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$J$13:$J$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$J$15:$J$66,1),IF(C25&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$J$15:$J$66,ROWS(Compose_50pct!$J$15:$J$66)),INDEX(Compose_50pct!$J$15:$J$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1))+(C25-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$J$15:$J$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$J$15:$J$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E25" s="16">
@@ -13376,11 +13412,11 @@
         <v/>
       </c>
       <c r="G25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$H$13:$H$64,1),IF(C25&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$H$13:$H$64,ROWS(Compose_50pct!$H$13:$H$64)),INDEX(Compose_50pct!$H$13:$H$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1))+(C25-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$H$13:$H$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$H$13:$H$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$H$15:$H$66,1),IF(C25&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$H$15:$H$66,ROWS(Compose_50pct!$H$15:$H$66)),INDEX(Compose_50pct!$H$15:$H$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1))+(C25-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$H$15:$H$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$H$15:$H$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$I$13:$I$64,1),IF(C25&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$I$13:$I$64,ROWS(Compose_50pct!$I$13:$I$64)),INDEX(Compose_50pct!$I$13:$I$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1))+(C25-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$I$13:$I$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$I$13:$I$64,MATCH(C25,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$I$15:$I$66,1),IF(C25&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$I$15:$I$66,ROWS(Compose_50pct!$I$15:$I$66)),INDEX(Compose_50pct!$I$15:$I$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1))+(C25-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$I$15:$I$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$I$15:$I$66,MATCH(C25,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I25" s="21">
@@ -13398,11 +13434,11 @@
         <v/>
       </c>
       <c r="C26" s="17">
-        <f>IF(F25&lt;=INDEX(Compose_50pct!$G$13:$G$64,1),INDEX(Compose_50pct!$A$13:$A$64,1),IF(F25&gt;=INDEX(Compose_50pct!$G$13:$G$64,ROWS(Compose_50pct!$G$13:$G$64)),INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$A$13:$A$64,MATCH(F25,Compose_50pct!$G$13:$G$64,1))+(F25-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F25,Compose_50pct!$G$13:$G$64,1)))/(INDEX(Compose_50pct!$G$13:$G$64,MATCH(F25,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F25,Compose_50pct!$G$13:$G$64,1)))*(INDEX(Compose_50pct!$A$13:$A$64,MATCH(F25,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(F25,Compose_50pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F25&lt;=INDEX(Compose_50pct!$G$15:$G$66,1),INDEX(Compose_50pct!$A$15:$A$66,1),IF(F25&gt;=INDEX(Compose_50pct!$G$15:$G$66,ROWS(Compose_50pct!$G$15:$G$66)),INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$A$15:$A$66,MATCH(F25,Compose_50pct!$G$15:$G$66,1))+(F25-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F25,Compose_50pct!$G$15:$G$66,1)))/(INDEX(Compose_50pct!$G$15:$G$66,MATCH(F25,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F25,Compose_50pct!$G$15:$G$66,1)))*(INDEX(Compose_50pct!$A$15:$A$66,MATCH(F25,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(F25,Compose_50pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D26" s="17">
-        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$J$13:$J$64,1),IF(C26&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$J$13:$J$64,ROWS(Compose_50pct!$J$13:$J$64)),INDEX(Compose_50pct!$J$13:$J$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1))+(C26-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$J$13:$J$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$J$13:$J$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$J$15:$J$66,1),IF(C26&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$J$15:$J$66,ROWS(Compose_50pct!$J$15:$J$66)),INDEX(Compose_50pct!$J$15:$J$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1))+(C26-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$J$15:$J$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$J$15:$J$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E26" s="16">
@@ -13414,11 +13450,11 @@
         <v/>
       </c>
       <c r="G26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$H$13:$H$64,1),IF(C26&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$H$13:$H$64,ROWS(Compose_50pct!$H$13:$H$64)),INDEX(Compose_50pct!$H$13:$H$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1))+(C26-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$H$13:$H$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$H$13:$H$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$H$15:$H$66,1),IF(C26&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$H$15:$H$66,ROWS(Compose_50pct!$H$15:$H$66)),INDEX(Compose_50pct!$H$15:$H$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1))+(C26-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$H$15:$H$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$H$15:$H$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$I$13:$I$64,1),IF(C26&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$I$13:$I$64,ROWS(Compose_50pct!$I$13:$I$64)),INDEX(Compose_50pct!$I$13:$I$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1))+(C26-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$I$13:$I$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$I$13:$I$64,MATCH(C26,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$I$15:$I$66,1),IF(C26&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$I$15:$I$66,ROWS(Compose_50pct!$I$15:$I$66)),INDEX(Compose_50pct!$I$15:$I$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1))+(C26-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$I$15:$I$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$I$15:$I$66,MATCH(C26,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I26" s="21">
@@ -13436,11 +13472,11 @@
         <v/>
       </c>
       <c r="C27" s="17">
-        <f>IF(F26&lt;=INDEX(Compose_50pct!$G$13:$G$64,1),INDEX(Compose_50pct!$A$13:$A$64,1),IF(F26&gt;=INDEX(Compose_50pct!$G$13:$G$64,ROWS(Compose_50pct!$G$13:$G$64)),INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$A$13:$A$64,MATCH(F26,Compose_50pct!$G$13:$G$64,1))+(F26-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F26,Compose_50pct!$G$13:$G$64,1)))/(INDEX(Compose_50pct!$G$13:$G$64,MATCH(F26,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$G$13:$G$64,MATCH(F26,Compose_50pct!$G$13:$G$64,1)))*(INDEX(Compose_50pct!$A$13:$A$64,MATCH(F26,Compose_50pct!$G$13:$G$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(F26,Compose_50pct!$G$13:$G$64,1)))))</f>
+        <f>IF(F26&lt;=INDEX(Compose_50pct!$G$15:$G$66,1),INDEX(Compose_50pct!$A$15:$A$66,1),IF(F26&gt;=INDEX(Compose_50pct!$G$15:$G$66,ROWS(Compose_50pct!$G$15:$G$66)),INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$A$15:$A$66,MATCH(F26,Compose_50pct!$G$15:$G$66,1))+(F26-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F26,Compose_50pct!$G$15:$G$66,1)))/(INDEX(Compose_50pct!$G$15:$G$66,MATCH(F26,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$G$15:$G$66,MATCH(F26,Compose_50pct!$G$15:$G$66,1)))*(INDEX(Compose_50pct!$A$15:$A$66,MATCH(F26,Compose_50pct!$G$15:$G$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(F26,Compose_50pct!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D27" s="17">
-        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$J$13:$J$64,1),IF(C27&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$J$13:$J$64,ROWS(Compose_50pct!$J$13:$J$64)),INDEX(Compose_50pct!$J$13:$J$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1))+(C27-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$J$13:$J$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$J$13:$J$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1))))))</f>
+        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$J$15:$J$66,1),IF(C27&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$J$15:$J$66,ROWS(Compose_50pct!$J$15:$J$66)),INDEX(Compose_50pct!$J$15:$J$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1))+(C27-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$J$15:$J$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$J$15:$J$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E27" s="16">
@@ -13452,11 +13488,11 @@
         <v/>
       </c>
       <c r="G27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$H$13:$H$64,1),IF(C27&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$H$13:$H$64,ROWS(Compose_50pct!$H$13:$H$64)),INDEX(Compose_50pct!$H$13:$H$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1))+(C27-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$H$13:$H$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$H$13:$H$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$H$15:$H$66,1),IF(C27&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$H$15:$H$66,ROWS(Compose_50pct!$H$15:$H$66)),INDEX(Compose_50pct!$H$15:$H$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1))+(C27-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$H$15:$H$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$H$15:$H$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_50pct!$A$13:$A$64,1),INDEX(Compose_50pct!$I$13:$I$64,1),IF(C27&gt;=INDEX(Compose_50pct!$A$13:$A$64,ROWS(Compose_50pct!$A$13:$A$64)),INDEX(Compose_50pct!$I$13:$I$64,ROWS(Compose_50pct!$I$13:$I$64)),INDEX(Compose_50pct!$I$13:$I$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1))+(C27-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1)))/(INDEX(Compose_50pct!$A$13:$A$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$A$13:$A$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1)))*(INDEX(Compose_50pct!$I$13:$I$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1)+1)-INDEX(Compose_50pct!$I$13:$I$64,MATCH(C27,Compose_50pct!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_50pct!$A$15:$A$66,1),INDEX(Compose_50pct!$I$15:$I$66,1),IF(C27&gt;=INDEX(Compose_50pct!$A$15:$A$66,ROWS(Compose_50pct!$A$15:$A$66)),INDEX(Compose_50pct!$I$15:$I$66,ROWS(Compose_50pct!$I$15:$I$66)),INDEX(Compose_50pct!$I$15:$I$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1))+(C27-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1)))/(INDEX(Compose_50pct!$A$15:$A$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$A$15:$A$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1)))*(INDEX(Compose_50pct!$I$15:$I$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1)+1)-INDEX(Compose_50pct!$I$15:$I$66,MATCH(C27,Compose_50pct!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I27" s="21">
@@ -13479,7 +13515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13492,7 +13528,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colonnes = formules Excel. Crest / facteur pipe en jaune.</t>
+          <t>Colonnes = formules Excel. Crest / facteur pipe / plafond Q en jaune.</t>
         </is>
       </c>
     </row>
@@ -13585,142 +13621,72 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q_cap (m3/s)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>WSE</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>HW</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>y_ov</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>A_ditch</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>V_ditch</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>V_pond</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>V_total</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Q_1200</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>Q_overflow</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>Qout</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="B13" s="19">
-        <f>A13-$B$10</f>
-        <v/>
-      </c>
-      <c r="C13" s="19">
-        <f>MAX(0,A13-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D13" s="17">
-        <f>IF(C13&lt;=0,0,($B$5+$B$7*C13)*C13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>D13*$B$9</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>IF(A13&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A13&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1))+(A13-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G13" s="14">
-        <f>E13+F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
-        <f>($B$11)*(IF(B13&lt;=0,0,IF(B13&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))+(B13-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I13" s="17">
-        <f>IF(C13&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D13*IF(($B$5+2*C13*SQRT(1+$B$7^2))&lt;=0,0,((D13/($B$5+2*C13*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J13" s="8">
-        <f>H13+I13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="n">
-        <v>34.98</v>
-      </c>
-      <c r="B14" s="19">
-        <f>A14-$B$10</f>
-        <v/>
-      </c>
-      <c r="C14" s="19">
-        <f>MAX(0,A14-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D14" s="17">
-        <f>IF(C14&lt;=0,0,($B$5+$B$7*C14)*C14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>D14*$B$9</f>
-        <v/>
-      </c>
-      <c r="F14" s="16">
-        <f>IF(A14&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A14&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1))+(A14-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G14" s="14">
-        <f>E14+F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
-        <f>($B$11)*(IF(B14&lt;=0,0,IF(B14&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))+(B14-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
-        <f>IF(C14&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D14*IF(($B$5+2*C14*SQRT(1+$B$7^2))&lt;=0,0,((D14/($B$5+2*C14*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J14" s="8">
-        <f>H14+I14</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="n">
-        <v>35.08</v>
+        <v>34.88</v>
       </c>
       <c r="B15" s="19">
         <f>A15-$B$10</f>
@@ -13747,7 +13713,7 @@
         <v/>
       </c>
       <c r="H15" s="17">
-        <f>($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I15" s="17">
@@ -13761,7 +13727,7 @@
     </row>
     <row r="16">
       <c r="A16" s="19" t="n">
-        <v>35.18</v>
+        <v>34.98</v>
       </c>
       <c r="B16" s="19">
         <f>A16-$B$10</f>
@@ -13788,7 +13754,7 @@
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I16" s="17">
@@ -13802,7 +13768,7 @@
     </row>
     <row r="17">
       <c r="A17" s="19" t="n">
-        <v>35.28</v>
+        <v>35.08</v>
       </c>
       <c r="B17" s="19">
         <f>A17-$B$10</f>
@@ -13829,7 +13795,7 @@
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I17" s="17">
@@ -13843,7 +13809,7 @@
     </row>
     <row r="18">
       <c r="A18" s="19" t="n">
-        <v>35.38</v>
+        <v>35.18</v>
       </c>
       <c r="B18" s="19">
         <f>A18-$B$10</f>
@@ -13870,7 +13836,7 @@
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I18" s="17">
@@ -13884,7 +13850,7 @@
     </row>
     <row r="19">
       <c r="A19" s="19" t="n">
-        <v>35.48</v>
+        <v>35.28</v>
       </c>
       <c r="B19" s="19">
         <f>A19-$B$10</f>
@@ -13911,7 +13877,7 @@
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I19" s="17">
@@ -13925,7 +13891,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="n">
-        <v>35.58</v>
+        <v>35.38</v>
       </c>
       <c r="B20" s="19">
         <f>A20-$B$10</f>
@@ -13952,7 +13918,7 @@
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I20" s="17">
@@ -13966,7 +13932,7 @@
     </row>
     <row r="21">
       <c r="A21" s="19" t="n">
-        <v>35.68</v>
+        <v>35.48</v>
       </c>
       <c r="B21" s="19">
         <f>A21-$B$10</f>
@@ -13993,7 +13959,7 @@
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I21" s="17">
@@ -14007,7 +13973,7 @@
     </row>
     <row r="22">
       <c r="A22" s="19" t="n">
-        <v>35.78</v>
+        <v>35.58</v>
       </c>
       <c r="B22" s="19">
         <f>A22-$B$10</f>
@@ -14034,7 +14000,7 @@
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I22" s="17">
@@ -14048,7 +14014,7 @@
     </row>
     <row r="23">
       <c r="A23" s="19" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="B23" s="19">
         <f>A23-$B$10</f>
@@ -14075,7 +14041,7 @@
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I23" s="17">
@@ -14089,7 +14055,7 @@
     </row>
     <row r="24">
       <c r="A24" s="19" t="n">
-        <v>35.98</v>
+        <v>35.78</v>
       </c>
       <c r="B24" s="19">
         <f>A24-$B$10</f>
@@ -14116,7 +14082,7 @@
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I24" s="17">
@@ -14130,7 +14096,7 @@
     </row>
     <row r="25">
       <c r="A25" s="19" t="n">
-        <v>36.08</v>
+        <v>35.88</v>
       </c>
       <c r="B25" s="19">
         <f>A25-$B$10</f>
@@ -14157,7 +14123,7 @@
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I25" s="17">
@@ -14171,7 +14137,7 @@
     </row>
     <row r="26">
       <c r="A26" s="19" t="n">
-        <v>36.18</v>
+        <v>35.98</v>
       </c>
       <c r="B26" s="19">
         <f>A26-$B$10</f>
@@ -14198,7 +14164,7 @@
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I26" s="17">
@@ -14212,7 +14178,7 @@
     </row>
     <row r="27">
       <c r="A27" s="19" t="n">
-        <v>36.28</v>
+        <v>36.08</v>
       </c>
       <c r="B27" s="19">
         <f>A27-$B$10</f>
@@ -14239,7 +14205,7 @@
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I27" s="17">
@@ -14253,7 +14219,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="n">
-        <v>36.38</v>
+        <v>36.18</v>
       </c>
       <c r="B28" s="19">
         <f>A28-$B$10</f>
@@ -14280,7 +14246,7 @@
         <v/>
       </c>
       <c r="H28" s="17">
-        <f>($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I28" s="17">
@@ -14294,7 +14260,7 @@
     </row>
     <row r="29">
       <c r="A29" s="19" t="n">
-        <v>36.48</v>
+        <v>36.28</v>
       </c>
       <c r="B29" s="19">
         <f>A29-$B$10</f>
@@ -14321,7 +14287,7 @@
         <v/>
       </c>
       <c r="H29" s="17">
-        <f>($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I29" s="17">
@@ -14335,7 +14301,7 @@
     </row>
     <row r="30">
       <c r="A30" s="19" t="n">
-        <v>36.58</v>
+        <v>36.38</v>
       </c>
       <c r="B30" s="19">
         <f>A30-$B$10</f>
@@ -14362,7 +14328,7 @@
         <v/>
       </c>
       <c r="H30" s="17">
-        <f>($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I30" s="17">
@@ -14376,7 +14342,7 @@
     </row>
     <row r="31">
       <c r="A31" s="19" t="n">
-        <v>36.68</v>
+        <v>36.48</v>
       </c>
       <c r="B31" s="19">
         <f>A31-$B$10</f>
@@ -14403,7 +14369,7 @@
         <v/>
       </c>
       <c r="H31" s="17">
-        <f>($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I31" s="17">
@@ -14417,7 +14383,7 @@
     </row>
     <row r="32">
       <c r="A32" s="19" t="n">
-        <v>36.78</v>
+        <v>36.58</v>
       </c>
       <c r="B32" s="19">
         <f>A32-$B$10</f>
@@ -14444,7 +14410,7 @@
         <v/>
       </c>
       <c r="H32" s="17">
-        <f>($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I32" s="17">
@@ -14458,7 +14424,7 @@
     </row>
     <row r="33">
       <c r="A33" s="19" t="n">
-        <v>36.88</v>
+        <v>36.68</v>
       </c>
       <c r="B33" s="19">
         <f>A33-$B$10</f>
@@ -14485,7 +14451,7 @@
         <v/>
       </c>
       <c r="H33" s="17">
-        <f>($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I33" s="17">
@@ -14499,7 +14465,7 @@
     </row>
     <row r="34">
       <c r="A34" s="19" t="n">
-        <v>36.98</v>
+        <v>36.78</v>
       </c>
       <c r="B34" s="19">
         <f>A34-$B$10</f>
@@ -14526,7 +14492,7 @@
         <v/>
       </c>
       <c r="H34" s="17">
-        <f>($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I34" s="17">
@@ -14540,7 +14506,7 @@
     </row>
     <row r="35">
       <c r="A35" s="19" t="n">
-        <v>37.08</v>
+        <v>36.88</v>
       </c>
       <c r="B35" s="19">
         <f>A35-$B$10</f>
@@ -14567,7 +14533,7 @@
         <v/>
       </c>
       <c r="H35" s="17">
-        <f>($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I35" s="17">
@@ -14581,7 +14547,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="n">
-        <v>37.18</v>
+        <v>36.98</v>
       </c>
       <c r="B36" s="19">
         <f>A36-$B$10</f>
@@ -14608,7 +14574,7 @@
         <v/>
       </c>
       <c r="H36" s="17">
-        <f>($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I36" s="17">
@@ -14622,7 +14588,7 @@
     </row>
     <row r="37">
       <c r="A37" s="19" t="n">
-        <v>37.28</v>
+        <v>37.08</v>
       </c>
       <c r="B37" s="19">
         <f>A37-$B$10</f>
@@ -14649,7 +14615,7 @@
         <v/>
       </c>
       <c r="H37" s="17">
-        <f>($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I37" s="17">
@@ -14663,7 +14629,7 @@
     </row>
     <row r="38">
       <c r="A38" s="19" t="n">
-        <v>37.38</v>
+        <v>37.18</v>
       </c>
       <c r="B38" s="19">
         <f>A38-$B$10</f>
@@ -14690,7 +14656,7 @@
         <v/>
       </c>
       <c r="H38" s="17">
-        <f>($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I38" s="17">
@@ -14704,7 +14670,7 @@
     </row>
     <row r="39">
       <c r="A39" s="19" t="n">
-        <v>37.48</v>
+        <v>37.28</v>
       </c>
       <c r="B39" s="19">
         <f>A39-$B$10</f>
@@ -14731,7 +14697,7 @@
         <v/>
       </c>
       <c r="H39" s="17">
-        <f>($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I39" s="17">
@@ -14745,7 +14711,7 @@
     </row>
     <row r="40">
       <c r="A40" s="19" t="n">
-        <v>37.58</v>
+        <v>37.38</v>
       </c>
       <c r="B40" s="19">
         <f>A40-$B$10</f>
@@ -14772,7 +14738,7 @@
         <v/>
       </c>
       <c r="H40" s="17">
-        <f>($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I40" s="17">
@@ -14786,7 +14752,7 @@
     </row>
     <row r="41">
       <c r="A41" s="19" t="n">
-        <v>37.68</v>
+        <v>37.48</v>
       </c>
       <c r="B41" s="19">
         <f>A41-$B$10</f>
@@ -14813,7 +14779,7 @@
         <v/>
       </c>
       <c r="H41" s="17">
-        <f>($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I41" s="17">
@@ -14827,7 +14793,7 @@
     </row>
     <row r="42">
       <c r="A42" s="19" t="n">
-        <v>37.78</v>
+        <v>37.58</v>
       </c>
       <c r="B42" s="19">
         <f>A42-$B$10</f>
@@ -14854,7 +14820,7 @@
         <v/>
       </c>
       <c r="H42" s="17">
-        <f>($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I42" s="17">
@@ -14868,7 +14834,7 @@
     </row>
     <row r="43">
       <c r="A43" s="19" t="n">
-        <v>37.88</v>
+        <v>37.68</v>
       </c>
       <c r="B43" s="19">
         <f>A43-$B$10</f>
@@ -14895,7 +14861,7 @@
         <v/>
       </c>
       <c r="H43" s="17">
-        <f>($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I43" s="17">
@@ -14909,7 +14875,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="n">
-        <v>37.98</v>
+        <v>37.78</v>
       </c>
       <c r="B44" s="19">
         <f>A44-$B$10</f>
@@ -14936,7 +14902,7 @@
         <v/>
       </c>
       <c r="H44" s="17">
-        <f>($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I44" s="17">
@@ -14950,7 +14916,7 @@
     </row>
     <row r="45">
       <c r="A45" s="19" t="n">
-        <v>38.08</v>
+        <v>37.88</v>
       </c>
       <c r="B45" s="19">
         <f>A45-$B$10</f>
@@ -14977,7 +14943,7 @@
         <v/>
       </c>
       <c r="H45" s="17">
-        <f>($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I45" s="17">
@@ -14991,7 +14957,7 @@
     </row>
     <row r="46">
       <c r="A46" s="19" t="n">
-        <v>38.18</v>
+        <v>37.98</v>
       </c>
       <c r="B46" s="19">
         <f>A46-$B$10</f>
@@ -15018,7 +14984,7 @@
         <v/>
       </c>
       <c r="H46" s="17">
-        <f>($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I46" s="17">
@@ -15032,7 +14998,7 @@
     </row>
     <row r="47">
       <c r="A47" s="19" t="n">
-        <v>38.28</v>
+        <v>38.08</v>
       </c>
       <c r="B47" s="19">
         <f>A47-$B$10</f>
@@ -15059,7 +15025,7 @@
         <v/>
       </c>
       <c r="H47" s="17">
-        <f>($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I47" s="17">
@@ -15073,7 +15039,7 @@
     </row>
     <row r="48">
       <c r="A48" s="19" t="n">
-        <v>38.38</v>
+        <v>38.18</v>
       </c>
       <c r="B48" s="19">
         <f>A48-$B$10</f>
@@ -15100,7 +15066,7 @@
         <v/>
       </c>
       <c r="H48" s="17">
-        <f>($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I48" s="17">
@@ -15114,7 +15080,7 @@
     </row>
     <row r="49">
       <c r="A49" s="19" t="n">
-        <v>38.48</v>
+        <v>38.28</v>
       </c>
       <c r="B49" s="19">
         <f>A49-$B$10</f>
@@ -15141,7 +15107,7 @@
         <v/>
       </c>
       <c r="H49" s="17">
-        <f>($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I49" s="17">
@@ -15155,7 +15121,7 @@
     </row>
     <row r="50">
       <c r="A50" s="19" t="n">
-        <v>38.58</v>
+        <v>38.38</v>
       </c>
       <c r="B50" s="19">
         <f>A50-$B$10</f>
@@ -15182,7 +15148,7 @@
         <v/>
       </c>
       <c r="H50" s="17">
-        <f>($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I50" s="17">
@@ -15196,7 +15162,7 @@
     </row>
     <row r="51">
       <c r="A51" s="19" t="n">
-        <v>38.68</v>
+        <v>38.48</v>
       </c>
       <c r="B51" s="19">
         <f>A51-$B$10</f>
@@ -15223,7 +15189,7 @@
         <v/>
       </c>
       <c r="H51" s="17">
-        <f>($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I51" s="17">
@@ -15237,7 +15203,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="n">
-        <v>38.78</v>
+        <v>38.58</v>
       </c>
       <c r="B52" s="19">
         <f>A52-$B$10</f>
@@ -15264,7 +15230,7 @@
         <v/>
       </c>
       <c r="H52" s="17">
-        <f>($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I52" s="17">
@@ -15278,7 +15244,7 @@
     </row>
     <row r="53">
       <c r="A53" s="19" t="n">
-        <v>38.88</v>
+        <v>38.68</v>
       </c>
       <c r="B53" s="19">
         <f>A53-$B$10</f>
@@ -15305,7 +15271,7 @@
         <v/>
       </c>
       <c r="H53" s="17">
-        <f>($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I53" s="17">
@@ -15319,7 +15285,7 @@
     </row>
     <row r="54">
       <c r="A54" s="19" t="n">
-        <v>38.98</v>
+        <v>38.78</v>
       </c>
       <c r="B54" s="19">
         <f>A54-$B$10</f>
@@ -15346,7 +15312,7 @@
         <v/>
       </c>
       <c r="H54" s="17">
-        <f>($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I54" s="17">
@@ -15360,7 +15326,7 @@
     </row>
     <row r="55">
       <c r="A55" s="19" t="n">
-        <v>39.08</v>
+        <v>38.88</v>
       </c>
       <c r="B55" s="19">
         <f>A55-$B$10</f>
@@ -15387,7 +15353,7 @@
         <v/>
       </c>
       <c r="H55" s="17">
-        <f>($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I55" s="17">
@@ -15401,7 +15367,7 @@
     </row>
     <row r="56">
       <c r="A56" s="19" t="n">
-        <v>39.18</v>
+        <v>38.98</v>
       </c>
       <c r="B56" s="19">
         <f>A56-$B$10</f>
@@ -15428,7 +15394,7 @@
         <v/>
       </c>
       <c r="H56" s="17">
-        <f>($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I56" s="17">
@@ -15442,7 +15408,7 @@
     </row>
     <row r="57">
       <c r="A57" s="19" t="n">
-        <v>39.28</v>
+        <v>39.08</v>
       </c>
       <c r="B57" s="19">
         <f>A57-$B$10</f>
@@ -15469,7 +15435,7 @@
         <v/>
       </c>
       <c r="H57" s="17">
-        <f>($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I57" s="17">
@@ -15483,7 +15449,7 @@
     </row>
     <row r="58">
       <c r="A58" s="19" t="n">
-        <v>39.38</v>
+        <v>39.18</v>
       </c>
       <c r="B58" s="19">
         <f>A58-$B$10</f>
@@ -15510,7 +15476,7 @@
         <v/>
       </c>
       <c r="H58" s="17">
-        <f>($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I58" s="17">
@@ -15524,7 +15490,7 @@
     </row>
     <row r="59">
       <c r="A59" s="19" t="n">
-        <v>39.48</v>
+        <v>39.28</v>
       </c>
       <c r="B59" s="19">
         <f>A59-$B$10</f>
@@ -15551,7 +15517,7 @@
         <v/>
       </c>
       <c r="H59" s="17">
-        <f>($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I59" s="17">
@@ -15565,7 +15531,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="n">
-        <v>39.58</v>
+        <v>39.38</v>
       </c>
       <c r="B60" s="19">
         <f>A60-$B$10</f>
@@ -15592,7 +15558,7 @@
         <v/>
       </c>
       <c r="H60" s="17">
-        <f>($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I60" s="17">
@@ -15606,7 +15572,7 @@
     </row>
     <row r="61">
       <c r="A61" s="19" t="n">
-        <v>39.68</v>
+        <v>39.48</v>
       </c>
       <c r="B61" s="19">
         <f>A61-$B$10</f>
@@ -15633,7 +15599,7 @@
         <v/>
       </c>
       <c r="H61" s="17">
-        <f>($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I61" s="17">
@@ -15647,7 +15613,7 @@
     </row>
     <row r="62">
       <c r="A62" s="19" t="n">
-        <v>39.78</v>
+        <v>39.58</v>
       </c>
       <c r="B62" s="19">
         <f>A62-$B$10</f>
@@ -15674,7 +15640,7 @@
         <v/>
       </c>
       <c r="H62" s="17">
-        <f>($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I62" s="17">
@@ -15688,7 +15654,7 @@
     </row>
     <row r="63">
       <c r="A63" s="19" t="n">
-        <v>39.88</v>
+        <v>39.68</v>
       </c>
       <c r="B63" s="19">
         <f>A63-$B$10</f>
@@ -15715,7 +15681,7 @@
         <v/>
       </c>
       <c r="H63" s="17">
-        <f>($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I63" s="17">
@@ -15729,7 +15695,7 @@
     </row>
     <row r="64">
       <c r="A64" s="19" t="n">
-        <v>39.98</v>
+        <v>39.78</v>
       </c>
       <c r="B64" s="19">
         <f>A64-$B$10</f>
@@ -15756,7 +15722,7 @@
         <v/>
       </c>
       <c r="H64" s="17">
-        <f>($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I64" s="17">
@@ -15765,6 +15731,88 @@
       </c>
       <c r="J64" s="8">
         <f>H64+I64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="B65" s="19">
+        <f>A65-$B$10</f>
+        <v/>
+      </c>
+      <c r="C65" s="19">
+        <f>MAX(0,A65-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D65" s="17">
+        <f>IF(C65&lt;=0,0,($B$5+$B$7*C65)*C65)</f>
+        <v/>
+      </c>
+      <c r="E65" s="16">
+        <f>D65*$B$9</f>
+        <v/>
+      </c>
+      <c r="F65" s="16">
+        <f>IF(A65&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A65&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1))+(A65-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G65" s="14">
+        <f>E65+F65</f>
+        <v/>
+      </c>
+      <c r="H65" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B65&lt;=0,0,IF(B65&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1))+(B65-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I65" s="17">
+        <f>IF(C65&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D65*IF(($B$5+2*C65*SQRT(1+$B$7^2))&lt;=0,0,((D65/($B$5+2*C65*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J65" s="8">
+        <f>H65+I65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="B66" s="19">
+        <f>A66-$B$10</f>
+        <v/>
+      </c>
+      <c r="C66" s="19">
+        <f>MAX(0,A66-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D66" s="17">
+        <f>IF(C66&lt;=0,0,($B$5+$B$7*C66)*C66)</f>
+        <v/>
+      </c>
+      <c r="E66" s="16">
+        <f>D66*$B$9</f>
+        <v/>
+      </c>
+      <c r="F66" s="16">
+        <f>IF(A66&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A66&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1))+(A66-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G66" s="14">
+        <f>E66+F66</f>
+        <v/>
+      </c>
+      <c r="H66" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B66&lt;=0,0,IF(B66&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1))+(B66-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I66" s="17">
+        <f>IF(C66&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D66*IF(($B$5+2*C66*SQRT(1+$B$7^2))&lt;=0,0,((D66/($B$5+2*C66*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J66" s="8">
+        <f>H66+I66</f>
         <v/>
       </c>
     </row>
